--- a/research/traditional_assets/database/data/philippines/philippines_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_furn_home_furnishings.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="pse_pmpc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0767</v>
+        <v>0.05889999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.33</v>
+        <v>0.08130000000000001</v>
       </c>
       <c r="G2">
-        <v>0.03544457978075518</v>
+        <v>0.02552003081664098</v>
       </c>
       <c r="H2">
-        <v>0.02882663418595209</v>
+        <v>0.02438366718027735</v>
       </c>
       <c r="I2">
-        <v>0.002634997969955339</v>
+        <v>0.01363636363636364</v>
       </c>
       <c r="J2">
-        <v>0.001497373097896777</v>
+        <v>0.01061331013484123</v>
       </c>
       <c r="K2">
-        <v>0.957</v>
+        <v>4.87</v>
       </c>
       <c r="L2">
-        <v>0.003885505481120584</v>
+        <v>0.01875963020030817</v>
       </c>
       <c r="M2">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="N2">
-        <v>0.04387254901960785</v>
+        <v>0.04379232505643341</v>
       </c>
       <c r="O2">
-        <v>1.87042842215256</v>
+        <v>0.3983572895277207</v>
       </c>
       <c r="P2">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="Q2">
-        <v>0.04387254901960785</v>
+        <v>0.04379232505643341</v>
       </c>
       <c r="R2">
-        <v>1.87042842215256</v>
+        <v>0.3983572895277207</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>51.9</v>
+        <v>63.6</v>
       </c>
       <c r="V2">
-        <v>1.272058823529412</v>
+        <v>1.435665914221219</v>
       </c>
       <c r="W2">
-        <v>0.01057458563535912</v>
+        <v>0.06243589743589744</v>
       </c>
       <c r="X2">
-        <v>0.1394008558861743</v>
+        <v>0.1078073419803126</v>
       </c>
       <c r="Y2">
-        <v>-0.1288262702508152</v>
+        <v>-0.04537144454441514</v>
       </c>
       <c r="Z2">
-        <v>17.48420529566267</v>
+        <v>9.914072942524349</v>
       </c>
       <c r="AA2">
-        <v>0.02618037864782963</v>
+        <v>0.1052211308384489</v>
       </c>
       <c r="AB2">
-        <v>0.1392211193702844</v>
+        <v>0.1078073419803126</v>
       </c>
       <c r="AC2">
-        <v>-0.1130407407224548</v>
+        <v>-0.002586211141863651</v>
       </c>
       <c r="AD2">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-51.815</v>
+        <v>-63.6</v>
       </c>
       <c r="AH2">
-        <v>0.002079002079002079</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.00107073124645714</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>4.704039945528824</v>
+        <v>3.295336787564766</v>
       </c>
       <c r="AK2">
-        <v>-1.885210114607968</v>
+        <v>-2.97196261682243</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AM2">
-        <v>-0.621</v>
+        <v>-1.044</v>
       </c>
       <c r="AN2">
-        <v>0.02043269230769231</v>
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>590</v>
       </c>
       <c r="AP2">
-        <v>-12.45552884615384</v>
+        <v>-9.03409090909091</v>
       </c>
       <c r="AQ2">
-        <v>-1.045088566827697</v>
+        <v>-3.390804597701149</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0767</v>
+        <v>0.05889999999999999</v>
       </c>
       <c r="E3">
-        <v>-0.33</v>
+        <v>0.08130000000000001</v>
       </c>
       <c r="G3">
-        <v>0.03544457978075518</v>
+        <v>0.02552003081664098</v>
       </c>
       <c r="H3">
-        <v>0.02882663418595209</v>
+        <v>0.02438366718027735</v>
       </c>
       <c r="I3">
-        <v>0.002634997969955339</v>
+        <v>0.01363636363636364</v>
       </c>
       <c r="J3">
-        <v>0.001497373097896777</v>
+        <v>0.01061331013484123</v>
       </c>
       <c r="K3">
-        <v>0.957</v>
+        <v>4.87</v>
       </c>
       <c r="L3">
-        <v>0.003885505481120584</v>
+        <v>0.01875963020030817</v>
       </c>
       <c r="M3">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="N3">
-        <v>0.04387254901960785</v>
+        <v>0.04379232505643341</v>
       </c>
       <c r="O3">
-        <v>1.87042842215256</v>
+        <v>0.3983572895277207</v>
       </c>
       <c r="P3">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="Q3">
-        <v>0.04387254901960785</v>
+        <v>0.04379232505643341</v>
       </c>
       <c r="R3">
-        <v>1.87042842215256</v>
+        <v>0.3983572895277207</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,70 +772,8845 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>51.9</v>
+        <v>63.6</v>
       </c>
       <c r="V3">
-        <v>1.272058823529412</v>
+        <v>1.435665914221219</v>
       </c>
       <c r="W3">
-        <v>0.01057458563535912</v>
+        <v>0.06243589743589744</v>
       </c>
       <c r="X3">
-        <v>0.1394008558861743</v>
+        <v>0.1078073419803126</v>
       </c>
       <c r="Y3">
-        <v>-0.1288262702508152</v>
+        <v>-0.04537144454441514</v>
       </c>
       <c r="Z3">
-        <v>17.48420529566267</v>
+        <v>9.914072942524349</v>
       </c>
       <c r="AA3">
-        <v>0.02618037864782963</v>
+        <v>0.1052211308384489</v>
       </c>
       <c r="AB3">
-        <v>0.1392211193702844</v>
+        <v>0.1078073419803126</v>
       </c>
       <c r="AC3">
-        <v>-0.1130407407224548</v>
+        <v>-0.002586211141863651</v>
       </c>
       <c r="AD3">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-51.815</v>
+        <v>-63.6</v>
       </c>
       <c r="AH3">
-        <v>0.002079002079002079</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.00107073124645714</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>4.704039945528824</v>
+        <v>3.295336787564766</v>
       </c>
       <c r="AK3">
-        <v>-1.885210114607968</v>
+        <v>-2.97196261682243</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AM3">
-        <v>-0.621</v>
+        <v>-1.044</v>
       </c>
       <c r="AN3">
-        <v>0.02043269230769231</v>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>590</v>
       </c>
       <c r="AP3">
-        <v>-12.45552884615384</v>
+        <v>-9.03409090909091</v>
       </c>
       <c r="AQ3">
-        <v>-1.045088566827697</v>
+        <v>-3.390804597701149</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Panasonic Manufacturing Philippines Corporation (PSE:PMPC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PSE:PMPC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Furn/Home Furnishings</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>590</v>
+      </c>
+      <c r="F2">
+        <v>0.338010365574824</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>6.2296875</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.99</v>
+      </c>
+      <c r="K2">
+        <v>44.3</v>
+      </c>
+      <c r="L2">
+        <v>14.2225711977508</v>
+      </c>
+      <c r="M2">
+        <v>-19.3</v>
+      </c>
+      <c r="N2">
+        <v>-5.5204288022492</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>43.857</v>
+      </c>
+      <c r="Q2">
+        <v>0.107807341980313</v>
+      </c>
+      <c r="R2">
+        <v>0.280056929113441</v>
+      </c>
+      <c r="S2">
+        <v>0.0493396777832879</v>
+      </c>
+      <c r="T2">
+        <v>0.218620781175183</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.107807341980313</v>
+      </c>
+      <c r="X2">
+        <v>6.36223557500097</v>
+      </c>
+      <c r="Y2">
+        <v>0.934469503646095</v>
+      </c>
+      <c r="Z2">
+        <v>85.62940599559739</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0.06578623704438383</v>
+      </c>
+      <c r="AC2">
+        <v>590</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0.006</v>
+      </c>
+      <c r="AF2">
+        <v>3.5</v>
+      </c>
+      <c r="AG2">
+        <v>7.04</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>44.3</v>
+      </c>
+      <c r="AK2">
+        <v>0.07384654256887045</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>7.27</v>
+      </c>
+      <c r="AR2">
+        <v>0.006</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>63.6</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1078073419803126</v>
+      </c>
+      <c r="C2">
+        <v>44.3</v>
+      </c>
+      <c r="D2">
+        <v>-19.3</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>63.6</v>
+      </c>
+      <c r="H2">
+        <v>44.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>7.04</v>
+      </c>
+      <c r="K2">
+        <v>3.5</v>
+      </c>
+      <c r="L2">
+        <v>3.54</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>3.54</v>
+      </c>
+      <c r="O2">
+        <v>0.885</v>
+      </c>
+      <c r="P2">
+        <v>2.655</v>
+      </c>
+      <c r="Q2">
+        <v>6.155</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1078073419803126</v>
+      </c>
+      <c r="T2">
+        <v>0.9344695036460947</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.033525</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1075820736253618</v>
+      </c>
+      <c r="C3">
+        <v>43.7937905179156</v>
+      </c>
+      <c r="D3">
+        <v>-19.36320948208441</v>
+      </c>
+      <c r="E3">
+        <v>0.443</v>
+      </c>
+      <c r="F3">
+        <v>0.443</v>
+      </c>
+      <c r="G3">
+        <v>63.6</v>
+      </c>
+      <c r="H3">
+        <v>44.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>7.04</v>
+      </c>
+      <c r="K3">
+        <v>3.5</v>
+      </c>
+      <c r="L3">
+        <v>3.54</v>
+      </c>
+      <c r="M3">
+        <v>0.0198021</v>
+      </c>
+      <c r="N3">
+        <v>3.5201979</v>
+      </c>
+      <c r="O3">
+        <v>0.880049475</v>
+      </c>
+      <c r="P3">
+        <v>2.640148425</v>
+      </c>
+      <c r="Q3">
+        <v>6.140148425</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1083301248741028</v>
+      </c>
+      <c r="T3">
+        <v>0.941548818067656</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.033525</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>178.7689184480434</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.107356805270411</v>
+      </c>
+      <c r="C4">
+        <v>43.28716564027739</v>
+      </c>
+      <c r="D4">
+        <v>-19.42683435972262</v>
+      </c>
+      <c r="E4">
+        <v>0.886</v>
+      </c>
+      <c r="F4">
+        <v>0.886</v>
+      </c>
+      <c r="G4">
+        <v>63.6</v>
+      </c>
+      <c r="H4">
+        <v>44.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>7.04</v>
+      </c>
+      <c r="K4">
+        <v>3.5</v>
+      </c>
+      <c r="L4">
+        <v>3.54</v>
+      </c>
+      <c r="M4">
+        <v>0.03960420000000001</v>
+      </c>
+      <c r="N4">
+        <v>3.5003958</v>
+      </c>
+      <c r="O4">
+        <v>0.87509895</v>
+      </c>
+      <c r="P4">
+        <v>2.62529685</v>
+      </c>
+      <c r="Q4">
+        <v>6.12529685</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1088635768065419</v>
+      </c>
+      <c r="T4">
+        <v>0.9487726082937391</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.033525</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>89.38445922402168</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1071315369154602</v>
+      </c>
+      <c r="C5">
+        <v>42.78012125878586</v>
+      </c>
+      <c r="D5">
+        <v>-19.49087874121414</v>
+      </c>
+      <c r="E5">
+        <v>1.329</v>
+      </c>
+      <c r="F5">
+        <v>1.329</v>
+      </c>
+      <c r="G5">
+        <v>63.6</v>
+      </c>
+      <c r="H5">
+        <v>44.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>7.04</v>
+      </c>
+      <c r="K5">
+        <v>3.5</v>
+      </c>
+      <c r="L5">
+        <v>3.54</v>
+      </c>
+      <c r="M5">
+        <v>0.0594063</v>
+      </c>
+      <c r="N5">
+        <v>3.4805937</v>
+      </c>
+      <c r="O5">
+        <v>0.870148425</v>
+      </c>
+      <c r="P5">
+        <v>2.610445275</v>
+      </c>
+      <c r="Q5">
+        <v>6.110445275</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1094080277478971</v>
+      </c>
+      <c r="T5">
+        <v>0.9561453426481947</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.033525</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>59.58963948268113</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1069062685605094</v>
+      </c>
+      <c r="C6">
+        <v>42.27265321078705</v>
+      </c>
+      <c r="D6">
+        <v>-19.55534678921295</v>
+      </c>
+      <c r="E6">
+        <v>1.772</v>
+      </c>
+      <c r="F6">
+        <v>1.772</v>
+      </c>
+      <c r="G6">
+        <v>63.6</v>
+      </c>
+      <c r="H6">
+        <v>44.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>7.04</v>
+      </c>
+      <c r="K6">
+        <v>3.5</v>
+      </c>
+      <c r="L6">
+        <v>3.54</v>
+      </c>
+      <c r="M6">
+        <v>0.07920840000000001</v>
+      </c>
+      <c r="N6">
+        <v>3.4607916</v>
+      </c>
+      <c r="O6">
+        <v>0.8651979</v>
+      </c>
+      <c r="P6">
+        <v>2.5955937</v>
+      </c>
+      <c r="Q6">
+        <v>6.0955937</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1099638214171973</v>
+      </c>
+      <c r="T6">
+        <v>0.9636716756350352</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.033525</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>44.69222961201084</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1066810002055587</v>
+      </c>
+      <c r="C7">
+        <v>41.76475727837065</v>
+      </c>
+      <c r="D7">
+        <v>-19.62024272162935</v>
+      </c>
+      <c r="E7">
+        <v>2.215</v>
+      </c>
+      <c r="F7">
+        <v>2.215</v>
+      </c>
+      <c r="G7">
+        <v>63.6</v>
+      </c>
+      <c r="H7">
+        <v>44.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>7.04</v>
+      </c>
+      <c r="K7">
+        <v>3.5</v>
+      </c>
+      <c r="L7">
+        <v>3.54</v>
+      </c>
+      <c r="M7">
+        <v>0.0990105</v>
+      </c>
+      <c r="N7">
+        <v>3.4409895</v>
+      </c>
+      <c r="O7">
+        <v>0.860247375</v>
+      </c>
+      <c r="P7">
+        <v>2.580742125</v>
+      </c>
+      <c r="Q7">
+        <v>6.080742125</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1105313160058512</v>
+      </c>
+      <c r="T7">
+        <v>0.971356457737388</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.033525</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>35.75378368960868</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1064557318506079</v>
+      </c>
+      <c r="C8">
+        <v>41.25642918745004</v>
+      </c>
+      <c r="D8">
+        <v>-19.68557081254996</v>
+      </c>
+      <c r="E8">
+        <v>2.658</v>
+      </c>
+      <c r="F8">
+        <v>2.658</v>
+      </c>
+      <c r="G8">
+        <v>63.6</v>
+      </c>
+      <c r="H8">
+        <v>44.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>7.04</v>
+      </c>
+      <c r="K8">
+        <v>3.5</v>
+      </c>
+      <c r="L8">
+        <v>3.54</v>
+      </c>
+      <c r="M8">
+        <v>0.1188126</v>
+      </c>
+      <c r="N8">
+        <v>3.4211874</v>
+      </c>
+      <c r="O8">
+        <v>0.85529685</v>
+      </c>
+      <c r="P8">
+        <v>2.56589055</v>
+      </c>
+      <c r="Q8">
+        <v>6.06589055</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1111108849474552</v>
+      </c>
+      <c r="T8">
+        <v>0.9792047458419184</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.033525</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>29.79481974134056</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1062304634956571</v>
+      </c>
+      <c r="C9">
+        <v>40.74766460682402</v>
+      </c>
+      <c r="D9">
+        <v>-19.75133539317598</v>
+      </c>
+      <c r="E9">
+        <v>3.101</v>
+      </c>
+      <c r="F9">
+        <v>3.101</v>
+      </c>
+      <c r="G9">
+        <v>63.6</v>
+      </c>
+      <c r="H9">
+        <v>44.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>7.04</v>
+      </c>
+      <c r="K9">
+        <v>3.5</v>
+      </c>
+      <c r="L9">
+        <v>3.54</v>
+      </c>
+      <c r="M9">
+        <v>0.1386147</v>
+      </c>
+      <c r="N9">
+        <v>3.4013853</v>
+      </c>
+      <c r="O9">
+        <v>0.850346325</v>
+      </c>
+      <c r="P9">
+        <v>2.551038975</v>
+      </c>
+      <c r="Q9">
+        <v>6.051038975</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1117029177372657</v>
+      </c>
+      <c r="T9">
+        <v>0.9872218143357936</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.033525</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>25.53841692114905</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1060051951407063</v>
+      </c>
+      <c r="C10">
+        <v>40.23845914721951</v>
+      </c>
+      <c r="D10">
+        <v>-19.8175408527805</v>
+      </c>
+      <c r="E10">
+        <v>3.544</v>
+      </c>
+      <c r="F10">
+        <v>3.544</v>
+      </c>
+      <c r="G10">
+        <v>63.6</v>
+      </c>
+      <c r="H10">
+        <v>44.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>7.04</v>
+      </c>
+      <c r="K10">
+        <v>3.5</v>
+      </c>
+      <c r="L10">
+        <v>3.54</v>
+      </c>
+      <c r="M10">
+        <v>0.1584168</v>
+      </c>
+      <c r="N10">
+        <v>3.3815832</v>
+      </c>
+      <c r="O10">
+        <v>0.8453958</v>
+      </c>
+      <c r="P10">
+        <v>2.5361874</v>
+      </c>
+      <c r="Q10">
+        <v>6.0361874</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1123078208051156</v>
+      </c>
+      <c r="T10">
+        <v>0.9954131669273618</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.033525</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>22.34611480600542</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1057799267857556</v>
+      </c>
+      <c r="C11">
+        <v>39.72880836031501</v>
+      </c>
+      <c r="D11">
+        <v>-19.88419163968499</v>
+      </c>
+      <c r="E11">
+        <v>3.987</v>
+      </c>
+      <c r="F11">
+        <v>3.987</v>
+      </c>
+      <c r="G11">
+        <v>63.6</v>
+      </c>
+      <c r="H11">
+        <v>44.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>7.04</v>
+      </c>
+      <c r="K11">
+        <v>3.5</v>
+      </c>
+      <c r="L11">
+        <v>3.54</v>
+      </c>
+      <c r="M11">
+        <v>0.1782189</v>
+      </c>
+      <c r="N11">
+        <v>3.3617811</v>
+      </c>
+      <c r="O11">
+        <v>0.840445275</v>
+      </c>
+      <c r="P11">
+        <v>2.521335825</v>
+      </c>
+      <c r="Q11">
+        <v>6.021335825</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1129260184458852</v>
+      </c>
+      <c r="T11">
+        <v>1.003784549246217</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.033525</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>19.86321316089371</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1055546584308047</v>
+      </c>
+      <c r="C12">
+        <v>39.21870773774436</v>
+      </c>
+      <c r="D12">
+        <v>-19.95129226225564</v>
+      </c>
+      <c r="E12">
+        <v>4.43</v>
+      </c>
+      <c r="F12">
+        <v>4.43</v>
+      </c>
+      <c r="G12">
+        <v>63.6</v>
+      </c>
+      <c r="H12">
+        <v>44.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>7.04</v>
+      </c>
+      <c r="K12">
+        <v>3.5</v>
+      </c>
+      <c r="L12">
+        <v>3.54</v>
+      </c>
+      <c r="M12">
+        <v>0.198021</v>
+      </c>
+      <c r="N12">
+        <v>3.341979</v>
+      </c>
+      <c r="O12">
+        <v>0.8354947500000001</v>
+      </c>
+      <c r="P12">
+        <v>2.50648425</v>
+      </c>
+      <c r="Q12">
+        <v>6.00648425</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1135579538120053</v>
+      </c>
+      <c r="T12">
+        <v>1.012341962283269</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.033525</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>17.87689184480434</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.105329390075854</v>
+      </c>
+      <c r="C13">
+        <v>38.70815271008011</v>
+      </c>
+      <c r="D13">
+        <v>-20.01884728991989</v>
+      </c>
+      <c r="E13">
+        <v>4.872999999999999</v>
+      </c>
+      <c r="F13">
+        <v>4.872999999999999</v>
+      </c>
+      <c r="G13">
+        <v>63.6</v>
+      </c>
+      <c r="H13">
+        <v>44.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>7.04</v>
+      </c>
+      <c r="K13">
+        <v>3.5</v>
+      </c>
+      <c r="L13">
+        <v>3.54</v>
+      </c>
+      <c r="M13">
+        <v>0.2178231</v>
+      </c>
+      <c r="N13">
+        <v>3.3221769</v>
+      </c>
+      <c r="O13">
+        <v>0.830544225</v>
+      </c>
+      <c r="P13">
+        <v>2.491632675</v>
+      </c>
+      <c r="Q13">
+        <v>5.991632675</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1142040899728697</v>
+      </c>
+      <c r="T13">
+        <v>1.021091676736885</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.033525</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>16.25171985891303</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1051041217209032</v>
+      </c>
+      <c r="C14">
+        <v>38.19713864579623</v>
+      </c>
+      <c r="D14">
+        <v>-20.08686135420377</v>
+      </c>
+      <c r="E14">
+        <v>5.316</v>
+      </c>
+      <c r="F14">
+        <v>5.316</v>
+      </c>
+      <c r="G14">
+        <v>63.6</v>
+      </c>
+      <c r="H14">
+        <v>44.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>7.04</v>
+      </c>
+      <c r="K14">
+        <v>3.5</v>
+      </c>
+      <c r="L14">
+        <v>3.54</v>
+      </c>
+      <c r="M14">
+        <v>0.2376252</v>
+      </c>
+      <c r="N14">
+        <v>3.3023748</v>
+      </c>
+      <c r="O14">
+        <v>0.8255937</v>
+      </c>
+      <c r="P14">
+        <v>2.4767811</v>
+      </c>
+      <c r="Q14">
+        <v>5.9767811</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1148649110464809</v>
+      </c>
+      <c r="T14">
+        <v>1.030040248337173</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.033525</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>14.89740987067028</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1048788533659524</v>
+      </c>
+      <c r="C15">
+        <v>37.6856608502097</v>
+      </c>
+      <c r="D15">
+        <v>-20.1553391497903</v>
+      </c>
+      <c r="E15">
+        <v>5.758999999999999</v>
+      </c>
+      <c r="F15">
+        <v>5.758999999999999</v>
+      </c>
+      <c r="G15">
+        <v>63.6</v>
+      </c>
+      <c r="H15">
+        <v>44.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>7.04</v>
+      </c>
+      <c r="K15">
+        <v>3.5</v>
+      </c>
+      <c r="L15">
+        <v>3.54</v>
+      </c>
+      <c r="M15">
+        <v>0.2574273</v>
+      </c>
+      <c r="N15">
+        <v>3.2825727</v>
+      </c>
+      <c r="O15">
+        <v>0.8206431750000001</v>
+      </c>
+      <c r="P15">
+        <v>2.461929525</v>
+      </c>
+      <c r="Q15">
+        <v>5.961929525</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1155409234091407</v>
+      </c>
+      <c r="T15">
+        <v>1.039194534227122</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.033525</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>13.75145526523411</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1047690850110016</v>
+      </c>
+      <c r="C16">
+        <v>37.20912364984413</v>
+      </c>
+      <c r="D16">
+        <v>-20.18887635015588</v>
+      </c>
+      <c r="E16">
+        <v>6.202</v>
+      </c>
+      <c r="F16">
+        <v>6.202</v>
+      </c>
+      <c r="G16">
+        <v>63.6</v>
+      </c>
+      <c r="H16">
+        <v>44.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>7.04</v>
+      </c>
+      <c r="K16">
+        <v>3.5</v>
+      </c>
+      <c r="L16">
+        <v>3.54</v>
+      </c>
+      <c r="M16">
+        <v>0.2840516</v>
+      </c>
+      <c r="N16">
+        <v>3.2559484</v>
+      </c>
+      <c r="O16">
+        <v>0.8139871</v>
+      </c>
+      <c r="P16">
+        <v>2.4419613</v>
+      </c>
+      <c r="Q16">
+        <v>5.9419613</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1162326569895368</v>
+      </c>
+      <c r="T16">
+        <v>1.048561710486606</v>
+      </c>
+      <c r="U16">
+        <v>0.0458</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.03435</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>12.4625244145782</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1045520666560508</v>
+      </c>
+      <c r="C17">
+        <v>36.69948913998553</v>
+      </c>
+      <c r="D17">
+        <v>-20.25551086001447</v>
+      </c>
+      <c r="E17">
+        <v>6.645</v>
+      </c>
+      <c r="F17">
+        <v>6.645</v>
+      </c>
+      <c r="G17">
+        <v>63.6</v>
+      </c>
+      <c r="H17">
+        <v>44.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>7.04</v>
+      </c>
+      <c r="K17">
+        <v>3.5</v>
+      </c>
+      <c r="L17">
+        <v>3.54</v>
+      </c>
+      <c r="M17">
+        <v>0.304341</v>
+      </c>
+      <c r="N17">
+        <v>3.235659</v>
+      </c>
+      <c r="O17">
+        <v>0.80891475</v>
+      </c>
+      <c r="P17">
+        <v>2.42674425</v>
+      </c>
+      <c r="Q17">
+        <v>5.92674425</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1169406666541775</v>
+      </c>
+      <c r="T17">
+        <v>1.058149290893372</v>
+      </c>
+      <c r="U17">
+        <v>0.0458</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.03435</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>11.63168945360632</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1043350483011001</v>
+      </c>
+      <c r="C18">
+        <v>36.18941331171526</v>
+      </c>
+      <c r="D18">
+        <v>-20.32258668828473</v>
+      </c>
+      <c r="E18">
+        <v>7.088</v>
+      </c>
+      <c r="F18">
+        <v>7.088</v>
+      </c>
+      <c r="G18">
+        <v>63.6</v>
+      </c>
+      <c r="H18">
+        <v>44.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>7.04</v>
+      </c>
+      <c r="K18">
+        <v>3.5</v>
+      </c>
+      <c r="L18">
+        <v>3.54</v>
+      </c>
+      <c r="M18">
+        <v>0.3246304</v>
+      </c>
+      <c r="N18">
+        <v>3.2153696</v>
+      </c>
+      <c r="O18">
+        <v>0.8038424</v>
+      </c>
+      <c r="P18">
+        <v>2.4115272</v>
+      </c>
+      <c r="Q18">
+        <v>5.9115272</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1176655336917858</v>
+      </c>
+      <c r="T18">
+        <v>1.067965147024108</v>
+      </c>
+      <c r="U18">
+        <v>0.0458</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.03435</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>10.90470886275592</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1041180299461493</v>
+      </c>
+      <c r="C19">
+        <v>35.67889176620828</v>
+      </c>
+      <c r="D19">
+        <v>-20.39010823379172</v>
+      </c>
+      <c r="E19">
+        <v>7.531</v>
+      </c>
+      <c r="F19">
+        <v>7.531</v>
+      </c>
+      <c r="G19">
+        <v>63.6</v>
+      </c>
+      <c r="H19">
+        <v>44.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>7.04</v>
+      </c>
+      <c r="K19">
+        <v>3.5</v>
+      </c>
+      <c r="L19">
+        <v>3.54</v>
+      </c>
+      <c r="M19">
+        <v>0.3449198</v>
+      </c>
+      <c r="N19">
+        <v>3.1950802</v>
+      </c>
+      <c r="O19">
+        <v>0.79877005</v>
+      </c>
+      <c r="P19">
+        <v>2.39631015</v>
+      </c>
+      <c r="Q19">
+        <v>5.89631015</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1184078674049992</v>
+      </c>
+      <c r="T19">
+        <v>1.078017529808597</v>
+      </c>
+      <c r="U19">
+        <v>0.0458</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.03435</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>10.26325540024087</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1041980115911985</v>
+      </c>
+      <c r="C20">
+        <v>35.26082883018913</v>
+      </c>
+      <c r="D20">
+        <v>-20.36517116981087</v>
+      </c>
+      <c r="E20">
+        <v>7.973999999999999</v>
+      </c>
+      <c r="F20">
+        <v>7.973999999999999</v>
+      </c>
+      <c r="G20">
+        <v>63.6</v>
+      </c>
+      <c r="H20">
+        <v>44.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>7.04</v>
+      </c>
+      <c r="K20">
+        <v>3.5</v>
+      </c>
+      <c r="L20">
+        <v>3.54</v>
+      </c>
+      <c r="M20">
+        <v>0.382752</v>
+      </c>
+      <c r="N20">
+        <v>3.157248</v>
+      </c>
+      <c r="O20">
+        <v>0.789312</v>
+      </c>
+      <c r="P20">
+        <v>2.367936</v>
+      </c>
+      <c r="Q20">
+        <v>5.867936</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1191683068185348</v>
+      </c>
+      <c r="T20">
+        <v>1.088315092661001</v>
+      </c>
+      <c r="U20">
+        <v>0.048</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.036</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>9.248808628041134</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1039974932362477</v>
+      </c>
+      <c r="C21">
+        <v>34.75519466407995</v>
+      </c>
+      <c r="D21">
+        <v>-20.42780533592005</v>
+      </c>
+      <c r="E21">
+        <v>8.417</v>
+      </c>
+      <c r="F21">
+        <v>8.417</v>
+      </c>
+      <c r="G21">
+        <v>63.6</v>
+      </c>
+      <c r="H21">
+        <v>44.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>7.04</v>
+      </c>
+      <c r="K21">
+        <v>3.5</v>
+      </c>
+      <c r="L21">
+        <v>3.54</v>
+      </c>
+      <c r="M21">
+        <v>0.404016</v>
+      </c>
+      <c r="N21">
+        <v>3.135984</v>
+      </c>
+      <c r="O21">
+        <v>0.783996</v>
+      </c>
+      <c r="P21">
+        <v>2.351988</v>
+      </c>
+      <c r="Q21">
+        <v>5.851988</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1199475225138861</v>
+      </c>
+      <c r="T21">
+        <v>1.098866916324574</v>
+      </c>
+      <c r="U21">
+        <v>0.048</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.036</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>8.762029226565286</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.103796974881297</v>
+      </c>
+      <c r="C22">
+        <v>34.24917403998637</v>
+      </c>
+      <c r="D22">
+        <v>-20.49082596001363</v>
+      </c>
+      <c r="E22">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="F22">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="G22">
+        <v>63.6</v>
+      </c>
+      <c r="H22">
+        <v>44.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>7.04</v>
+      </c>
+      <c r="K22">
+        <v>3.5</v>
+      </c>
+      <c r="L22">
+        <v>3.54</v>
+      </c>
+      <c r="M22">
+        <v>0.42528</v>
+      </c>
+      <c r="N22">
+        <v>3.11472</v>
+      </c>
+      <c r="O22">
+        <v>0.77868</v>
+      </c>
+      <c r="P22">
+        <v>2.33604</v>
+      </c>
+      <c r="Q22">
+        <v>5.836040000000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1207462186016212</v>
+      </c>
+      <c r="T22">
+        <v>1.109682535579738</v>
+      </c>
+      <c r="U22">
+        <v>0.048</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.036</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>8.32392776523702</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1035964565263462</v>
+      </c>
+      <c r="C23">
+        <v>33.74276337012337</v>
+      </c>
+      <c r="D23">
+        <v>-20.55423662987663</v>
+      </c>
+      <c r="E23">
+        <v>9.302999999999999</v>
+      </c>
+      <c r="F23">
+        <v>9.302999999999999</v>
+      </c>
+      <c r="G23">
+        <v>63.6</v>
+      </c>
+      <c r="H23">
+        <v>44.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>7.04</v>
+      </c>
+      <c r="K23">
+        <v>3.5</v>
+      </c>
+      <c r="L23">
+        <v>3.54</v>
+      </c>
+      <c r="M23">
+        <v>0.4465439999999999</v>
+      </c>
+      <c r="N23">
+        <v>3.093456</v>
+      </c>
+      <c r="O23">
+        <v>0.7733640000000001</v>
+      </c>
+      <c r="P23">
+        <v>2.320092</v>
+      </c>
+      <c r="Q23">
+        <v>5.820092000000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1215651348434762</v>
+      </c>
+      <c r="T23">
+        <v>1.120771967980601</v>
+      </c>
+      <c r="U23">
+        <v>0.048</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.036</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>7.927550252606688</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1036434381713954</v>
+      </c>
+      <c r="C24">
+        <v>33.31465573050454</v>
+      </c>
+      <c r="D24">
+        <v>-20.53934426949547</v>
+      </c>
+      <c r="E24">
+        <v>9.745999999999999</v>
+      </c>
+      <c r="F24">
+        <v>9.745999999999999</v>
+      </c>
+      <c r="G24">
+        <v>63.6</v>
+      </c>
+      <c r="H24">
+        <v>44.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>7.04</v>
+      </c>
+      <c r="K24">
+        <v>3.5</v>
+      </c>
+      <c r="L24">
+        <v>3.54</v>
+      </c>
+      <c r="M24">
+        <v>0.4824269999999999</v>
+      </c>
+      <c r="N24">
+        <v>3.057573</v>
+      </c>
+      <c r="O24">
+        <v>0.76439325</v>
+      </c>
+      <c r="P24">
+        <v>2.29317975</v>
+      </c>
+      <c r="Q24">
+        <v>5.79317975</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1224050489376864</v>
+      </c>
+      <c r="T24">
+        <v>1.132145744801999</v>
+      </c>
+      <c r="U24">
+        <v>0.0495</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>7.337897754478917</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1034541698164446</v>
+      </c>
+      <c r="C25">
+        <v>32.8115289372491</v>
+      </c>
+      <c r="D25">
+        <v>-20.5994710627509</v>
+      </c>
+      <c r="E25">
+        <v>10.189</v>
+      </c>
+      <c r="F25">
+        <v>10.189</v>
+      </c>
+      <c r="G25">
+        <v>63.6</v>
+      </c>
+      <c r="H25">
+        <v>44.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>7.04</v>
+      </c>
+      <c r="K25">
+        <v>3.5</v>
+      </c>
+      <c r="L25">
+        <v>3.54</v>
+      </c>
+      <c r="M25">
+        <v>0.5043555000000001</v>
+      </c>
+      <c r="N25">
+        <v>3.0356445</v>
+      </c>
+      <c r="O25">
+        <v>0.758911125</v>
+      </c>
+      <c r="P25">
+        <v>2.276733375</v>
+      </c>
+      <c r="Q25">
+        <v>5.776733375</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1232667789823956</v>
+      </c>
+      <c r="T25">
+        <v>1.143814944397979</v>
+      </c>
+      <c r="U25">
+        <v>0.0495</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>7.018858721675485</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1032649014614938</v>
+      </c>
+      <c r="C26">
+        <v>32.30804908057497</v>
+      </c>
+      <c r="D26">
+        <v>-20.65995091942503</v>
+      </c>
+      <c r="E26">
+        <v>10.632</v>
+      </c>
+      <c r="F26">
+        <v>10.632</v>
+      </c>
+      <c r="G26">
+        <v>63.6</v>
+      </c>
+      <c r="H26">
+        <v>44.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>7.04</v>
+      </c>
+      <c r="K26">
+        <v>3.5</v>
+      </c>
+      <c r="L26">
+        <v>3.54</v>
+      </c>
+      <c r="M26">
+        <v>0.526284</v>
+      </c>
+      <c r="N26">
+        <v>3.013716</v>
+      </c>
+      <c r="O26">
+        <v>0.753429</v>
+      </c>
+      <c r="P26">
+        <v>2.260287</v>
+      </c>
+      <c r="Q26">
+        <v>5.760287</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1241511861335445</v>
+      </c>
+      <c r="T26">
+        <v>1.155791228193854</v>
+      </c>
+      <c r="U26">
+        <v>0.0495</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>6.726406274939007</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.103075633106543</v>
+      </c>
+      <c r="C27">
+        <v>31.80421304155219</v>
+      </c>
+      <c r="D27">
+        <v>-20.72078695844781</v>
+      </c>
+      <c r="E27">
+        <v>11.075</v>
+      </c>
+      <c r="F27">
+        <v>11.075</v>
+      </c>
+      <c r="G27">
+        <v>63.6</v>
+      </c>
+      <c r="H27">
+        <v>44.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>7.04</v>
+      </c>
+      <c r="K27">
+        <v>3.5</v>
+      </c>
+      <c r="L27">
+        <v>3.54</v>
+      </c>
+      <c r="M27">
+        <v>0.5482125</v>
+      </c>
+      <c r="N27">
+        <v>2.9917875</v>
+      </c>
+      <c r="O27">
+        <v>0.747946875</v>
+      </c>
+      <c r="P27">
+        <v>2.243840625</v>
+      </c>
+      <c r="Q27">
+        <v>5.743840625</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1250591774753907</v>
+      </c>
+      <c r="T27">
+        <v>1.168086879557618</v>
+      </c>
+      <c r="U27">
+        <v>0.0495</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>6.457350023941446</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1028863647515923</v>
+      </c>
+      <c r="C28">
+        <v>31.30001766440586</v>
+      </c>
+      <c r="D28">
+        <v>-20.78198233559414</v>
+      </c>
+      <c r="E28">
+        <v>11.518</v>
+      </c>
+      <c r="F28">
+        <v>11.518</v>
+      </c>
+      <c r="G28">
+        <v>63.6</v>
+      </c>
+      <c r="H28">
+        <v>44.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>7.04</v>
+      </c>
+      <c r="K28">
+        <v>3.5</v>
+      </c>
+      <c r="L28">
+        <v>3.54</v>
+      </c>
+      <c r="M28">
+        <v>0.570141</v>
+      </c>
+      <c r="N28">
+        <v>2.969859</v>
+      </c>
+      <c r="O28">
+        <v>0.74246475</v>
+      </c>
+      <c r="P28">
+        <v>2.22739425</v>
+      </c>
+      <c r="Q28">
+        <v>5.72739425</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1259917091237733</v>
+      </c>
+      <c r="T28">
+        <v>1.180714845823106</v>
+      </c>
+      <c r="U28">
+        <v>0.0495</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>6.208990407636006</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1029805963966415</v>
+      </c>
+      <c r="C29">
+        <v>30.88753031920834</v>
+      </c>
+      <c r="D29">
+        <v>-20.75146968079167</v>
+      </c>
+      <c r="E29">
+        <v>11.961</v>
+      </c>
+      <c r="F29">
+        <v>11.961</v>
+      </c>
+      <c r="G29">
+        <v>63.6</v>
+      </c>
+      <c r="H29">
+        <v>44.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>7.04</v>
+      </c>
+      <c r="K29">
+        <v>3.5</v>
+      </c>
+      <c r="L29">
+        <v>3.54</v>
+      </c>
+      <c r="M29">
+        <v>0.6088149</v>
+      </c>
+      <c r="N29">
+        <v>2.9311851</v>
+      </c>
+      <c r="O29">
+        <v>0.732796275</v>
+      </c>
+      <c r="P29">
+        <v>2.198388825</v>
+      </c>
+      <c r="Q29">
+        <v>5.698388825</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1269497895844404</v>
+      </c>
+      <c r="T29">
+        <v>1.193688783767101</v>
+      </c>
+      <c r="U29">
+        <v>0.0509</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.038175</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.814575168906017</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1028018280416907</v>
+      </c>
+      <c r="C30">
+        <v>30.38656781702433</v>
+      </c>
+      <c r="D30">
+        <v>-20.80943218297567</v>
+      </c>
+      <c r="E30">
+        <v>12.404</v>
+      </c>
+      <c r="F30">
+        <v>12.404</v>
+      </c>
+      <c r="G30">
+        <v>63.6</v>
+      </c>
+      <c r="H30">
+        <v>44.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>7.04</v>
+      </c>
+      <c r="K30">
+        <v>3.5</v>
+      </c>
+      <c r="L30">
+        <v>3.54</v>
+      </c>
+      <c r="M30">
+        <v>0.6313636</v>
+      </c>
+      <c r="N30">
+        <v>2.9086364</v>
+      </c>
+      <c r="O30">
+        <v>0.7271590999999999</v>
+      </c>
+      <c r="P30">
+        <v>2.1814773</v>
+      </c>
+      <c r="Q30">
+        <v>5.6814773</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1279344833912371</v>
+      </c>
+      <c r="T30">
+        <v>1.207023108876206</v>
+      </c>
+      <c r="U30">
+        <v>0.0509</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.038175</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.606911770016517</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1026230596867399</v>
+      </c>
+      <c r="C31">
+        <v>29.88528060896709</v>
+      </c>
+      <c r="D31">
+        <v>-20.86771939103291</v>
+      </c>
+      <c r="E31">
+        <v>12.847</v>
+      </c>
+      <c r="F31">
+        <v>12.847</v>
+      </c>
+      <c r="G31">
+        <v>63.6</v>
+      </c>
+      <c r="H31">
+        <v>44.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>7.04</v>
+      </c>
+      <c r="K31">
+        <v>3.5</v>
+      </c>
+      <c r="L31">
+        <v>3.54</v>
+      </c>
+      <c r="M31">
+        <v>0.6539122999999999</v>
+      </c>
+      <c r="N31">
+        <v>2.8860877</v>
+      </c>
+      <c r="O31">
+        <v>0.721521925</v>
+      </c>
+      <c r="P31">
+        <v>2.164565775</v>
+      </c>
+      <c r="Q31">
+        <v>5.664565775</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1289469150517464</v>
+      </c>
+      <c r="T31">
+        <v>1.220733048777117</v>
+      </c>
+      <c r="U31">
+        <v>0.0509</v>
+      </c>
+      <c r="V31">
+        <v>0.25</v>
+      </c>
+      <c r="W31">
+        <v>0.038175</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>5.413569984843534</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1024442913317891</v>
+      </c>
+      <c r="C32">
+        <v>29.38366595886971</v>
+      </c>
+      <c r="D32">
+        <v>-20.9263340411303</v>
+      </c>
+      <c r="E32">
+        <v>13.29</v>
+      </c>
+      <c r="F32">
+        <v>13.29</v>
+      </c>
+      <c r="G32">
+        <v>63.6</v>
+      </c>
+      <c r="H32">
+        <v>44.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>7.04</v>
+      </c>
+      <c r="K32">
+        <v>3.5</v>
+      </c>
+      <c r="L32">
+        <v>3.54</v>
+      </c>
+      <c r="M32">
+        <v>0.676461</v>
+      </c>
+      <c r="N32">
+        <v>2.863539</v>
+      </c>
+      <c r="O32">
+        <v>0.7158847500000001</v>
+      </c>
+      <c r="P32">
+        <v>2.14765425</v>
+      </c>
+      <c r="Q32">
+        <v>5.64765425</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1299882733311273</v>
+      </c>
+      <c r="T32">
+        <v>1.234834701246625</v>
+      </c>
+      <c r="U32">
+        <v>0.0509</v>
+      </c>
+      <c r="V32">
+        <v>0.25</v>
+      </c>
+      <c r="W32">
+        <v>0.038175</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>5.233117652015416</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1022655229768384</v>
+      </c>
+      <c r="C33">
+        <v>28.88172109973652</v>
+      </c>
+      <c r="D33">
+        <v>-20.98527890026348</v>
+      </c>
+      <c r="E33">
+        <v>13.733</v>
+      </c>
+      <c r="F33">
+        <v>13.733</v>
+      </c>
+      <c r="G33">
+        <v>63.6</v>
+      </c>
+      <c r="H33">
+        <v>44.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>7.04</v>
+      </c>
+      <c r="K33">
+        <v>3.5</v>
+      </c>
+      <c r="L33">
+        <v>3.54</v>
+      </c>
+      <c r="M33">
+        <v>0.6990097</v>
+      </c>
+      <c r="N33">
+        <v>2.8409903</v>
+      </c>
+      <c r="O33">
+        <v>0.710247575</v>
+      </c>
+      <c r="P33">
+        <v>2.130742725</v>
+      </c>
+      <c r="Q33">
+        <v>5.630742725</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1310598159084614</v>
+      </c>
+      <c r="T33">
+        <v>1.249345097265974</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.25</v>
+      </c>
+      <c r="W33">
+        <v>0.038175</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.064307405176209</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1020867546218876</v>
+      </c>
+      <c r="C34">
+        <v>28.37944323330779</v>
+      </c>
+      <c r="D34">
+        <v>-21.04455676669221</v>
+      </c>
+      <c r="E34">
+        <v>14.176</v>
+      </c>
+      <c r="F34">
+        <v>14.176</v>
+      </c>
+      <c r="G34">
+        <v>63.6</v>
+      </c>
+      <c r="H34">
+        <v>44.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>7.04</v>
+      </c>
+      <c r="K34">
+        <v>3.5</v>
+      </c>
+      <c r="L34">
+        <v>3.54</v>
+      </c>
+      <c r="M34">
+        <v>0.7215584</v>
+      </c>
+      <c r="N34">
+        <v>2.8184416</v>
+      </c>
+      <c r="O34">
+        <v>0.7046104</v>
+      </c>
+      <c r="P34">
+        <v>2.1138312</v>
+      </c>
+      <c r="Q34">
+        <v>5.6138312</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1321628744439523</v>
+      </c>
+      <c r="T34">
+        <v>1.264282269638834</v>
+      </c>
+      <c r="U34">
+        <v>0.0509</v>
+      </c>
+      <c r="V34">
+        <v>0.25</v>
+      </c>
+      <c r="W34">
+        <v>0.038175</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.906047798764451</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1019079862669368</v>
+      </c>
+      <c r="C35">
+        <v>27.87682952961684</v>
+      </c>
+      <c r="D35">
+        <v>-21.10417047038316</v>
+      </c>
+      <c r="E35">
+        <v>14.619</v>
+      </c>
+      <c r="F35">
+        <v>14.619</v>
+      </c>
+      <c r="G35">
+        <v>63.6</v>
+      </c>
+      <c r="H35">
+        <v>44.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>7.04</v>
+      </c>
+      <c r="K35">
+        <v>3.5</v>
+      </c>
+      <c r="L35">
+        <v>3.54</v>
+      </c>
+      <c r="M35">
+        <v>0.7441071</v>
+      </c>
+      <c r="N35">
+        <v>2.7958929</v>
+      </c>
+      <c r="O35">
+        <v>0.698973225</v>
+      </c>
+      <c r="P35">
+        <v>2.096919675</v>
+      </c>
+      <c r="Q35">
+        <v>5.596919675000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1332988600999057</v>
+      </c>
+      <c r="T35">
+        <v>1.279665327754167</v>
+      </c>
+      <c r="U35">
+        <v>0.0509</v>
+      </c>
+      <c r="V35">
+        <v>0.25</v>
+      </c>
+      <c r="W35">
+        <v>0.038175</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.757379683650377</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.101729217911986</v>
+      </c>
+      <c r="C36">
+        <v>27.37387712653966</v>
+      </c>
+      <c r="D36">
+        <v>-21.16412287346034</v>
+      </c>
+      <c r="E36">
+        <v>15.062</v>
+      </c>
+      <c r="F36">
+        <v>15.062</v>
+      </c>
+      <c r="G36">
+        <v>63.6</v>
+      </c>
+      <c r="H36">
+        <v>44.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>7.04</v>
+      </c>
+      <c r="K36">
+        <v>3.5</v>
+      </c>
+      <c r="L36">
+        <v>3.54</v>
+      </c>
+      <c r="M36">
+        <v>0.7666558</v>
+      </c>
+      <c r="N36">
+        <v>2.7733442</v>
+      </c>
+      <c r="O36">
+        <v>0.69333605</v>
+      </c>
+      <c r="P36">
+        <v>2.08000815</v>
+      </c>
+      <c r="Q36">
+        <v>5.580008149999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1344692695636152</v>
+      </c>
+      <c r="T36">
+        <v>1.295514539145722</v>
+      </c>
+      <c r="U36">
+        <v>0.0509</v>
+      </c>
+      <c r="V36">
+        <v>0.25</v>
+      </c>
+      <c r="W36">
+        <v>0.038175</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.617456751778308</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1022329495570352</v>
+      </c>
+      <c r="C37">
+        <v>27.09894496045752</v>
+      </c>
+      <c r="D37">
+        <v>-20.99605503954247</v>
+      </c>
+      <c r="E37">
+        <v>15.505</v>
+      </c>
+      <c r="F37">
+        <v>15.505</v>
+      </c>
+      <c r="G37">
+        <v>63.6</v>
+      </c>
+      <c r="H37">
+        <v>44.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>7.04</v>
+      </c>
+      <c r="K37">
+        <v>3.5</v>
+      </c>
+      <c r="L37">
+        <v>3.54</v>
+      </c>
+      <c r="M37">
+        <v>0.8295175</v>
+      </c>
+      <c r="N37">
+        <v>2.7104825</v>
+      </c>
+      <c r="O37">
+        <v>0.677620625</v>
+      </c>
+      <c r="P37">
+        <v>2.032861875</v>
+      </c>
+      <c r="Q37">
+        <v>5.532861875</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1356756916262081</v>
+      </c>
+      <c r="T37">
+        <v>1.311851418580095</v>
+      </c>
+      <c r="U37">
+        <v>0.0535</v>
+      </c>
+      <c r="V37">
+        <v>0.25</v>
+      </c>
+      <c r="W37">
+        <v>0.040125</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>4.267541070562103</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1020736812020844</v>
+      </c>
+      <c r="C38">
+        <v>26.60309506958546</v>
+      </c>
+      <c r="D38">
+        <v>-21.04890493041454</v>
+      </c>
+      <c r="E38">
+        <v>15.948</v>
+      </c>
+      <c r="F38">
+        <v>15.948</v>
+      </c>
+      <c r="G38">
+        <v>63.6</v>
+      </c>
+      <c r="H38">
+        <v>44.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>7.04</v>
+      </c>
+      <c r="K38">
+        <v>3.5</v>
+      </c>
+      <c r="L38">
+        <v>3.54</v>
+      </c>
+      <c r="M38">
+        <v>0.8532179999999999</v>
+      </c>
+      <c r="N38">
+        <v>2.686782</v>
+      </c>
+      <c r="O38">
+        <v>0.6716955</v>
+      </c>
+      <c r="P38">
+        <v>2.0150865</v>
+      </c>
+      <c r="Q38">
+        <v>5.5150865</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.136919814378257</v>
+      </c>
+      <c r="T38">
+        <v>1.328698825496791</v>
+      </c>
+      <c r="U38">
+        <v>0.0535</v>
+      </c>
+      <c r="V38">
+        <v>0.25</v>
+      </c>
+      <c r="W38">
+        <v>0.040125</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>4.14899826304649</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1019144128471337</v>
+      </c>
+      <c r="C39">
+        <v>26.10697844676427</v>
+      </c>
+      <c r="D39">
+        <v>-21.10202155323574</v>
+      </c>
+      <c r="E39">
+        <v>16.391</v>
+      </c>
+      <c r="F39">
+        <v>16.391</v>
+      </c>
+      <c r="G39">
+        <v>63.6</v>
+      </c>
+      <c r="H39">
+        <v>44.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>7.04</v>
+      </c>
+      <c r="K39">
+        <v>3.5</v>
+      </c>
+      <c r="L39">
+        <v>3.54</v>
+      </c>
+      <c r="M39">
+        <v>0.8769184999999999</v>
+      </c>
+      <c r="N39">
+        <v>2.6630815</v>
+      </c>
+      <c r="O39">
+        <v>0.665770375</v>
+      </c>
+      <c r="P39">
+        <v>1.997311125</v>
+      </c>
+      <c r="Q39">
+        <v>5.497311125</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1382034330906883</v>
+      </c>
+      <c r="T39">
+        <v>1.346081070728303</v>
+      </c>
+      <c r="U39">
+        <v>0.0535</v>
+      </c>
+      <c r="V39">
+        <v>0.25</v>
+      </c>
+      <c r="W39">
+        <v>0.040125</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>4.036863174856045</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1025246444921829</v>
+      </c>
+      <c r="C40">
+        <v>25.86605287854669</v>
+      </c>
+      <c r="D40">
+        <v>-20.89994712145331</v>
+      </c>
+      <c r="E40">
+        <v>16.834</v>
+      </c>
+      <c r="F40">
+        <v>16.834</v>
+      </c>
+      <c r="G40">
+        <v>63.6</v>
+      </c>
+      <c r="H40">
+        <v>44.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>7.04</v>
+      </c>
+      <c r="K40">
+        <v>3.5</v>
+      </c>
+      <c r="L40">
+        <v>3.54</v>
+      </c>
+      <c r="M40">
+        <v>0.9460708</v>
+      </c>
+      <c r="N40">
+        <v>2.5939292</v>
+      </c>
+      <c r="O40">
+        <v>0.6484823</v>
+      </c>
+      <c r="P40">
+        <v>1.9454469</v>
+      </c>
+      <c r="Q40">
+        <v>5.4454469</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1395284588583595</v>
+      </c>
+      <c r="T40">
+        <v>1.364024033547929</v>
+      </c>
+      <c r="U40">
+        <v>0.0562</v>
+      </c>
+      <c r="V40">
+        <v>0.25</v>
+      </c>
+      <c r="W40">
+        <v>0.04215</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>3.7417918405261</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1023856261372321</v>
+      </c>
+      <c r="C41">
+        <v>25.37735896242307</v>
+      </c>
+      <c r="D41">
+        <v>-20.94564103757693</v>
+      </c>
+      <c r="E41">
+        <v>17.277</v>
+      </c>
+      <c r="F41">
+        <v>17.277</v>
+      </c>
+      <c r="G41">
+        <v>63.6</v>
+      </c>
+      <c r="H41">
+        <v>44.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>7.04</v>
+      </c>
+      <c r="K41">
+        <v>3.5</v>
+      </c>
+      <c r="L41">
+        <v>3.54</v>
+      </c>
+      <c r="M41">
+        <v>0.9709674</v>
+      </c>
+      <c r="N41">
+        <v>2.5690326</v>
+      </c>
+      <c r="O41">
+        <v>0.64225815</v>
+      </c>
+      <c r="P41">
+        <v>1.92677445</v>
+      </c>
+      <c r="Q41">
+        <v>5.42677445</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1408969280938231</v>
+      </c>
+      <c r="T41">
+        <v>1.382555290230493</v>
+      </c>
+      <c r="U41">
+        <v>0.0562</v>
+      </c>
+      <c r="V41">
+        <v>0.25</v>
+      </c>
+      <c r="W41">
+        <v>0.04215</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.64584845999979</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1022466077822813</v>
+      </c>
+      <c r="C42">
+        <v>24.88846480571062</v>
+      </c>
+      <c r="D42">
+        <v>-20.99153519428938</v>
+      </c>
+      <c r="E42">
+        <v>17.72</v>
+      </c>
+      <c r="F42">
+        <v>17.72</v>
+      </c>
+      <c r="G42">
+        <v>63.6</v>
+      </c>
+      <c r="H42">
+        <v>44.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>7.04</v>
+      </c>
+      <c r="K42">
+        <v>3.5</v>
+      </c>
+      <c r="L42">
+        <v>3.54</v>
+      </c>
+      <c r="M42">
+        <v>0.995864</v>
+      </c>
+      <c r="N42">
+        <v>2.544136</v>
+      </c>
+      <c r="O42">
+        <v>0.636034</v>
+      </c>
+      <c r="P42">
+        <v>1.908102</v>
+      </c>
+      <c r="Q42">
+        <v>5.408102</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1423110129704689</v>
+      </c>
+      <c r="T42">
+        <v>1.401704255469142</v>
+      </c>
+      <c r="U42">
+        <v>0.0562</v>
+      </c>
+      <c r="V42">
+        <v>0.25</v>
+      </c>
+      <c r="W42">
+        <v>0.04215</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>3.554702248499795</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1035528394273306</v>
+      </c>
+      <c r="C43">
+        <v>24.86891816762408</v>
+      </c>
+      <c r="D43">
+        <v>-20.56808183237592</v>
+      </c>
+      <c r="E43">
+        <v>18.163</v>
+      </c>
+      <c r="F43">
+        <v>18.163</v>
+      </c>
+      <c r="G43">
+        <v>63.6</v>
+      </c>
+      <c r="H43">
+        <v>44.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>7.04</v>
+      </c>
+      <c r="K43">
+        <v>3.5</v>
+      </c>
+      <c r="L43">
+        <v>3.54</v>
+      </c>
+      <c r="M43">
+        <v>1.1061267</v>
+      </c>
+      <c r="N43">
+        <v>2.4338733</v>
+      </c>
+      <c r="O43">
+        <v>0.608468325</v>
+      </c>
+      <c r="P43">
+        <v>1.825404975</v>
+      </c>
+      <c r="Q43">
+        <v>5.325404975</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1437730329276789</v>
+      </c>
+      <c r="T43">
+        <v>1.421502338173509</v>
+      </c>
+      <c r="U43">
+        <v>0.0609</v>
+      </c>
+      <c r="V43">
+        <v>0.25</v>
+      </c>
+      <c r="W43">
+        <v>0.045675</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>3.200356704164179</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1034490710723798</v>
+      </c>
+      <c r="C44">
+        <v>24.39290429780607</v>
+      </c>
+      <c r="D44">
+        <v>-20.60109570219393</v>
+      </c>
+      <c r="E44">
+        <v>18.606</v>
+      </c>
+      <c r="F44">
+        <v>18.606</v>
+      </c>
+      <c r="G44">
+        <v>63.6</v>
+      </c>
+      <c r="H44">
+        <v>44.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>7.04</v>
+      </c>
+      <c r="K44">
+        <v>3.5</v>
+      </c>
+      <c r="L44">
+        <v>3.54</v>
+      </c>
+      <c r="M44">
+        <v>1.1331054</v>
+      </c>
+      <c r="N44">
+        <v>2.4068946</v>
+      </c>
+      <c r="O44">
+        <v>0.6017236500000001</v>
+      </c>
+      <c r="P44">
+        <v>1.80517095</v>
+      </c>
+      <c r="Q44">
+        <v>5.30517095</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.145285467366172</v>
+      </c>
+      <c r="T44">
+        <v>1.441983113384922</v>
+      </c>
+      <c r="U44">
+        <v>0.0609</v>
+      </c>
+      <c r="V44">
+        <v>0.25</v>
+      </c>
+      <c r="W44">
+        <v>0.045675</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>3.124157735017413</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.103345302717429</v>
+      </c>
+      <c r="C45">
+        <v>23.91678427634519</v>
+      </c>
+      <c r="D45">
+        <v>-20.63421572365482</v>
+      </c>
+      <c r="E45">
+        <v>19.049</v>
+      </c>
+      <c r="F45">
+        <v>19.049</v>
+      </c>
+      <c r="G45">
+        <v>63.6</v>
+      </c>
+      <c r="H45">
+        <v>44.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>7.04</v>
+      </c>
+      <c r="K45">
+        <v>3.5</v>
+      </c>
+      <c r="L45">
+        <v>3.54</v>
+      </c>
+      <c r="M45">
+        <v>1.1600841</v>
+      </c>
+      <c r="N45">
+        <v>2.3799159</v>
+      </c>
+      <c r="O45">
+        <v>0.5949789750000001</v>
+      </c>
+      <c r="P45">
+        <v>1.784936925</v>
+      </c>
+      <c r="Q45">
+        <v>5.284936925</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1468509696797</v>
+      </c>
+      <c r="T45">
+        <v>1.463182512287964</v>
+      </c>
+      <c r="U45">
+        <v>0.0609</v>
+      </c>
+      <c r="V45">
+        <v>0.25</v>
+      </c>
+      <c r="W45">
+        <v>0.045675</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>3.051502903970497</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1063105343624782</v>
+      </c>
+      <c r="C46">
+        <v>24.38009067744753</v>
+      </c>
+      <c r="D46">
+        <v>-19.72790932255247</v>
+      </c>
+      <c r="E46">
+        <v>19.492</v>
+      </c>
+      <c r="F46">
+        <v>19.492</v>
+      </c>
+      <c r="G46">
+        <v>63.6</v>
+      </c>
+      <c r="H46">
+        <v>44.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>7.04</v>
+      </c>
+      <c r="K46">
+        <v>3.5</v>
+      </c>
+      <c r="L46">
+        <v>3.54</v>
+      </c>
+      <c r="M46">
+        <v>1.3683384</v>
+      </c>
+      <c r="N46">
+        <v>2.1716616</v>
+      </c>
+      <c r="O46">
+        <v>0.5429154</v>
+      </c>
+      <c r="P46">
+        <v>1.6287462</v>
+      </c>
+      <c r="Q46">
+        <v>5.1287462</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1484723827901396</v>
+      </c>
+      <c r="T46">
+        <v>1.485139032580401</v>
+      </c>
+      <c r="U46">
+        <v>0.0702</v>
+      </c>
+      <c r="V46">
+        <v>0.25</v>
+      </c>
+      <c r="W46">
+        <v>0.05265</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.587079336515003</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1062765160075274</v>
+      </c>
+      <c r="C47">
+        <v>23.92714483167066</v>
+      </c>
+      <c r="D47">
+        <v>-19.73785516832935</v>
+      </c>
+      <c r="E47">
+        <v>19.935</v>
+      </c>
+      <c r="F47">
+        <v>19.935</v>
+      </c>
+      <c r="G47">
+        <v>63.6</v>
+      </c>
+      <c r="H47">
+        <v>44.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>7.04</v>
+      </c>
+      <c r="K47">
+        <v>3.5</v>
+      </c>
+      <c r="L47">
+        <v>3.54</v>
+      </c>
+      <c r="M47">
+        <v>1.399437</v>
+      </c>
+      <c r="N47">
+        <v>2.140563</v>
+      </c>
+      <c r="O47">
+        <v>0.5351407500000001</v>
+      </c>
+      <c r="P47">
+        <v>1.60542225</v>
+      </c>
+      <c r="Q47">
+        <v>5.10542225</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1501527563773226</v>
+      </c>
+      <c r="T47">
+        <v>1.507893971792562</v>
+      </c>
+      <c r="U47">
+        <v>0.0702</v>
+      </c>
+      <c r="V47">
+        <v>0.25</v>
+      </c>
+      <c r="W47">
+        <v>0.05265</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.529588684592447</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1078639976525766</v>
+      </c>
+      <c r="C48">
+        <v>23.93783248163822</v>
+      </c>
+      <c r="D48">
+        <v>-19.28416751836178</v>
+      </c>
+      <c r="E48">
+        <v>20.378</v>
+      </c>
+      <c r="F48">
+        <v>20.378</v>
+      </c>
+      <c r="G48">
+        <v>63.6</v>
+      </c>
+      <c r="H48">
+        <v>44.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>7.04</v>
+      </c>
+      <c r="K48">
+        <v>3.5</v>
+      </c>
+      <c r="L48">
+        <v>3.54</v>
+      </c>
+      <c r="M48">
+        <v>1.5263122</v>
+      </c>
+      <c r="N48">
+        <v>2.0136878</v>
+      </c>
+      <c r="O48">
+        <v>0.5034219500000001</v>
+      </c>
+      <c r="P48">
+        <v>1.51026585</v>
+      </c>
+      <c r="Q48">
+        <v>5.010265850000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1518953660232901</v>
+      </c>
+      <c r="T48">
+        <v>1.5314916865311</v>
+      </c>
+      <c r="U48">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V48">
+        <v>0.25</v>
+      </c>
+      <c r="W48">
+        <v>0.056175</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.319315799218535</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1078652292976258</v>
+      </c>
+      <c r="C49">
+        <v>23.49517637754203</v>
+      </c>
+      <c r="D49">
+        <v>-19.28382362245796</v>
+      </c>
+      <c r="E49">
+        <v>20.821</v>
+      </c>
+      <c r="F49">
+        <v>20.821</v>
+      </c>
+      <c r="G49">
+        <v>63.6</v>
+      </c>
+      <c r="H49">
+        <v>44.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>7.04</v>
+      </c>
+      <c r="K49">
+        <v>3.5</v>
+      </c>
+      <c r="L49">
+        <v>3.54</v>
+      </c>
+      <c r="M49">
+        <v>1.5594929</v>
+      </c>
+      <c r="N49">
+        <v>1.9805071</v>
+      </c>
+      <c r="O49">
+        <v>0.495126775</v>
+      </c>
+      <c r="P49">
+        <v>1.485380325</v>
+      </c>
+      <c r="Q49">
+        <v>4.985380325</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1537037345238224</v>
+      </c>
+      <c r="T49">
+        <v>1.555979881071092</v>
+      </c>
+      <c r="U49">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V49">
+        <v>0.25</v>
+      </c>
+      <c r="W49">
+        <v>0.056175</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.269968654554311</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1078664609426751</v>
+      </c>
+      <c r="C50">
+        <v>23.05252026118064</v>
+      </c>
+      <c r="D50">
+        <v>-19.28347973881936</v>
+      </c>
+      <c r="E50">
+        <v>21.264</v>
+      </c>
+      <c r="F50">
+        <v>21.264</v>
+      </c>
+      <c r="G50">
+        <v>63.6</v>
+      </c>
+      <c r="H50">
+        <v>44.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>7.04</v>
+      </c>
+      <c r="K50">
+        <v>3.5</v>
+      </c>
+      <c r="L50">
+        <v>3.54</v>
+      </c>
+      <c r="M50">
+        <v>1.5926736</v>
+      </c>
+      <c r="N50">
+        <v>1.9473264</v>
+      </c>
+      <c r="O50">
+        <v>0.4868316</v>
+      </c>
+      <c r="P50">
+        <v>1.4604948</v>
+      </c>
+      <c r="Q50">
+        <v>4.9604948</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1555816556589905</v>
+      </c>
+      <c r="T50">
+        <v>1.581409929247237</v>
+      </c>
+      <c r="U50">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V50">
+        <v>0.25</v>
+      </c>
+      <c r="W50">
+        <v>0.056175</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>2.222677640917762</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1078676925877243</v>
+      </c>
+      <c r="C51">
+        <v>22.60986413255469</v>
+      </c>
+      <c r="D51">
+        <v>-19.28313586744532</v>
+      </c>
+      <c r="E51">
+        <v>21.707</v>
+      </c>
+      <c r="F51">
+        <v>21.707</v>
+      </c>
+      <c r="G51">
+        <v>63.6</v>
+      </c>
+      <c r="H51">
+        <v>44.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>7.04</v>
+      </c>
+      <c r="K51">
+        <v>3.5</v>
+      </c>
+      <c r="L51">
+        <v>3.54</v>
+      </c>
+      <c r="M51">
+        <v>1.6258543</v>
+      </c>
+      <c r="N51">
+        <v>1.9141457</v>
+      </c>
+      <c r="O51">
+        <v>0.4785364250000001</v>
+      </c>
+      <c r="P51">
+        <v>1.435609275</v>
+      </c>
+      <c r="Q51">
+        <v>4.935609275</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1575332207602437</v>
+      </c>
+      <c r="T51">
+        <v>1.607837234214604</v>
+      </c>
+      <c r="U51">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V51">
+        <v>0.25</v>
+      </c>
+      <c r="W51">
+        <v>0.056175</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>2.177316872735767</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1078689242327735</v>
+      </c>
+      <c r="C52">
+        <v>22.16720799166482</v>
+      </c>
+      <c r="D52">
+        <v>-19.28279200833518</v>
+      </c>
+      <c r="E52">
+        <v>22.15</v>
+      </c>
+      <c r="F52">
+        <v>22.15</v>
+      </c>
+      <c r="G52">
+        <v>63.6</v>
+      </c>
+      <c r="H52">
+        <v>44.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>7.04</v>
+      </c>
+      <c r="K52">
+        <v>3.5</v>
+      </c>
+      <c r="L52">
+        <v>3.54</v>
+      </c>
+      <c r="M52">
+        <v>1.659035</v>
+      </c>
+      <c r="N52">
+        <v>1.880965</v>
+      </c>
+      <c r="O52">
+        <v>0.4702412500000001</v>
+      </c>
+      <c r="P52">
+        <v>1.41072375</v>
+      </c>
+      <c r="Q52">
+        <v>4.910723750000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.159562848465547</v>
+      </c>
+      <c r="T52">
+        <v>1.635321631380666</v>
+      </c>
+      <c r="U52">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V52">
+        <v>0.25</v>
+      </c>
+      <c r="W52">
+        <v>0.056175</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>2.133770535281052</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1078701558778227</v>
+      </c>
+      <c r="C53">
+        <v>21.7245518385117</v>
+      </c>
+      <c r="D53">
+        <v>-19.2824481614883</v>
+      </c>
+      <c r="E53">
+        <v>22.593</v>
+      </c>
+      <c r="F53">
+        <v>22.593</v>
+      </c>
+      <c r="G53">
+        <v>63.6</v>
+      </c>
+      <c r="H53">
+        <v>44.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>7.04</v>
+      </c>
+      <c r="K53">
+        <v>3.5</v>
+      </c>
+      <c r="L53">
+        <v>3.54</v>
+      </c>
+      <c r="M53">
+        <v>1.6922157</v>
+      </c>
+      <c r="N53">
+        <v>1.8477843</v>
+      </c>
+      <c r="O53">
+        <v>0.4619460750000001</v>
+      </c>
+      <c r="P53">
+        <v>1.385838225</v>
+      </c>
+      <c r="Q53">
+        <v>4.885838225000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1616753181180056</v>
+      </c>
+      <c r="T53">
+        <v>1.663927840675955</v>
+      </c>
+      <c r="U53">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V53">
+        <v>0.25</v>
+      </c>
+      <c r="W53">
+        <v>0.056175</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>2.091931897334365</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.107871387522872</v>
+      </c>
+      <c r="C54">
+        <v>21.28189567309599</v>
+      </c>
+      <c r="D54">
+        <v>-19.28210432690401</v>
+      </c>
+      <c r="E54">
+        <v>23.036</v>
+      </c>
+      <c r="F54">
+        <v>23.036</v>
+      </c>
+      <c r="G54">
+        <v>63.6</v>
+      </c>
+      <c r="H54">
+        <v>44.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>7.04</v>
+      </c>
+      <c r="K54">
+        <v>3.5</v>
+      </c>
+      <c r="L54">
+        <v>3.54</v>
+      </c>
+      <c r="M54">
+        <v>1.7253964</v>
+      </c>
+      <c r="N54">
+        <v>1.8146036</v>
+      </c>
+      <c r="O54">
+        <v>0.4536509000000001</v>
+      </c>
+      <c r="P54">
+        <v>1.3609527</v>
+      </c>
+      <c r="Q54">
+        <v>4.8609527</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1638758073393166</v>
+      </c>
+      <c r="T54">
+        <v>1.693725975358547</v>
+      </c>
+      <c r="U54">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V54">
+        <v>0.25</v>
+      </c>
+      <c r="W54">
+        <v>0.056175</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>2.051702437770243</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1078726191679212</v>
+      </c>
+      <c r="C55">
+        <v>20.83923949541833</v>
+      </c>
+      <c r="D55">
+        <v>-19.28176050458167</v>
+      </c>
+      <c r="E55">
+        <v>23.479</v>
+      </c>
+      <c r="F55">
+        <v>23.479</v>
+      </c>
+      <c r="G55">
+        <v>63.6</v>
+      </c>
+      <c r="H55">
+        <v>44.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>7.04</v>
+      </c>
+      <c r="K55">
+        <v>3.5</v>
+      </c>
+      <c r="L55">
+        <v>3.54</v>
+      </c>
+      <c r="M55">
+        <v>1.7585771</v>
+      </c>
+      <c r="N55">
+        <v>1.7814229</v>
+      </c>
+      <c r="O55">
+        <v>0.445355725</v>
+      </c>
+      <c r="P55">
+        <v>1.336067175</v>
+      </c>
+      <c r="Q55">
+        <v>4.836067175</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1661699343998323</v>
+      </c>
+      <c r="T55">
+        <v>1.724792115772313</v>
+      </c>
+      <c r="U55">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V55">
+        <v>0.25</v>
+      </c>
+      <c r="W55">
+        <v>0.056175</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>2.012991071019861</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1144753508129704</v>
+      </c>
+      <c r="C56">
+        <v>22.07858769583184</v>
+      </c>
+      <c r="D56">
+        <v>-17.59941230416816</v>
+      </c>
+      <c r="E56">
+        <v>23.922</v>
+      </c>
+      <c r="F56">
+        <v>23.922</v>
+      </c>
+      <c r="G56">
+        <v>63.6</v>
+      </c>
+      <c r="H56">
+        <v>44.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>7.04</v>
+      </c>
+      <c r="K56">
+        <v>3.5</v>
+      </c>
+      <c r="L56">
+        <v>3.54</v>
+      </c>
+      <c r="M56">
+        <v>2.1816864</v>
+      </c>
+      <c r="N56">
+        <v>1.3583136</v>
+      </c>
+      <c r="O56">
+        <v>0.3395783999999999</v>
+      </c>
+      <c r="P56">
+        <v>1.0187352</v>
+      </c>
+      <c r="Q56">
+        <v>4.5187352</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.168563806115153</v>
+      </c>
+      <c r="T56">
+        <v>1.7572089579432</v>
+      </c>
+      <c r="U56">
+        <v>0.0912</v>
+      </c>
+      <c r="V56">
+        <v>0.25</v>
+      </c>
+      <c r="W56">
+        <v>0.0684</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>1.622598004919497</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1145988324580196</v>
+      </c>
+      <c r="C57">
+        <v>21.664258379967</v>
+      </c>
+      <c r="D57">
+        <v>-17.570741620033</v>
+      </c>
+      <c r="E57">
+        <v>24.365</v>
+      </c>
+      <c r="F57">
+        <v>24.365</v>
+      </c>
+      <c r="G57">
+        <v>63.6</v>
+      </c>
+      <c r="H57">
+        <v>44.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>7.04</v>
+      </c>
+      <c r="K57">
+        <v>3.5</v>
+      </c>
+      <c r="L57">
+        <v>3.54</v>
+      </c>
+      <c r="M57">
+        <v>2.222088</v>
+      </c>
+      <c r="N57">
+        <v>1.317912</v>
+      </c>
+      <c r="O57">
+        <v>0.3294779999999999</v>
+      </c>
+      <c r="P57">
+        <v>0.9884339999999998</v>
+      </c>
+      <c r="Q57">
+        <v>4.488434</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1710640721289325</v>
+      </c>
+      <c r="T57">
+        <v>1.791066548655015</v>
+      </c>
+      <c r="U57">
+        <v>0.0912</v>
+      </c>
+      <c r="V57">
+        <v>0.25</v>
+      </c>
+      <c r="W57">
+        <v>0.0684</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>1.59309622301187</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1147223141030688</v>
+      </c>
+      <c r="C58">
+        <v>21.24983580289738</v>
+      </c>
+      <c r="D58">
+        <v>-17.54216419710262</v>
+      </c>
+      <c r="E58">
+        <v>24.808</v>
+      </c>
+      <c r="F58">
+        <v>24.808</v>
+      </c>
+      <c r="G58">
+        <v>63.6</v>
+      </c>
+      <c r="H58">
+        <v>44.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>7.04</v>
+      </c>
+      <c r="K58">
+        <v>3.5</v>
+      </c>
+      <c r="L58">
+        <v>3.54</v>
+      </c>
+      <c r="M58">
+        <v>2.2624896</v>
+      </c>
+      <c r="N58">
+        <v>1.2775104</v>
+      </c>
+      <c r="O58">
+        <v>0.3193776</v>
+      </c>
+      <c r="P58">
+        <v>0.9581328000000001</v>
+      </c>
+      <c r="Q58">
+        <v>4.4581328</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1736779865978837</v>
+      </c>
+      <c r="T58">
+        <v>1.826463120762821</v>
+      </c>
+      <c r="U58">
+        <v>0.0912</v>
+      </c>
+      <c r="V58">
+        <v>0.25</v>
+      </c>
+      <c r="W58">
+        <v>0.0684</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>1.564648076172372</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.114845795748118</v>
+      </c>
+      <c r="C59">
+        <v>20.83532041893002</v>
+      </c>
+      <c r="D59">
+        <v>-17.51367958106998</v>
+      </c>
+      <c r="E59">
+        <v>25.251</v>
+      </c>
+      <c r="F59">
+        <v>25.251</v>
+      </c>
+      <c r="G59">
+        <v>63.6</v>
+      </c>
+      <c r="H59">
+        <v>44.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>7.04</v>
+      </c>
+      <c r="K59">
+        <v>3.5</v>
+      </c>
+      <c r="L59">
+        <v>3.54</v>
+      </c>
+      <c r="M59">
+        <v>2.3028912</v>
+      </c>
+      <c r="N59">
+        <v>1.2371088</v>
+      </c>
+      <c r="O59">
+        <v>0.3092771999999999</v>
+      </c>
+      <c r="P59">
+        <v>0.9278315999999998</v>
+      </c>
+      <c r="Q59">
+        <v>4.427831599999999</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1764134784839954</v>
+      </c>
+      <c r="T59">
+        <v>1.863506045061689</v>
+      </c>
+      <c r="U59">
+        <v>0.0912</v>
+      </c>
+      <c r="V59">
+        <v>0.25</v>
+      </c>
+      <c r="W59">
+        <v>0.0684</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>1.537198109923734</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1149692773931673</v>
+      </c>
+      <c r="C60">
+        <v>20.42071267942598</v>
+      </c>
+      <c r="D60">
+        <v>-17.48528732057402</v>
+      </c>
+      <c r="E60">
+        <v>25.694</v>
+      </c>
+      <c r="F60">
+        <v>25.694</v>
+      </c>
+      <c r="G60">
+        <v>63.6</v>
+      </c>
+      <c r="H60">
+        <v>44.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>7.04</v>
+      </c>
+      <c r="K60">
+        <v>3.5</v>
+      </c>
+      <c r="L60">
+        <v>3.54</v>
+      </c>
+      <c r="M60">
+        <v>2.3432928</v>
+      </c>
+      <c r="N60">
+        <v>1.196707200000001</v>
+      </c>
+      <c r="O60">
+        <v>0.2991768000000001</v>
+      </c>
+      <c r="P60">
+        <v>0.8975304000000004</v>
+      </c>
+      <c r="Q60">
+        <v>4.397530400000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1792792318884935</v>
+      </c>
+      <c r="T60">
+        <v>1.902312918136693</v>
+      </c>
+      <c r="U60">
+        <v>0.0912</v>
+      </c>
+      <c r="V60">
+        <v>0.25</v>
+      </c>
+      <c r="W60">
+        <v>0.0684</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>1.510694694235394</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1485286643105617</v>
+      </c>
+      <c r="C61">
+        <v>25.32540852754243</v>
+      </c>
+      <c r="D61">
+        <v>-12.13759147245757</v>
+      </c>
+      <c r="E61">
+        <v>26.137</v>
+      </c>
+      <c r="F61">
+        <v>26.137</v>
+      </c>
+      <c r="G61">
+        <v>63.6</v>
+      </c>
+      <c r="H61">
+        <v>44.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>7.04</v>
+      </c>
+      <c r="K61">
+        <v>3.5</v>
+      </c>
+      <c r="L61">
+        <v>3.54</v>
+      </c>
+      <c r="M61">
+        <v>4.0930542</v>
+      </c>
+      <c r="N61">
+        <v>-0.5530542000000001</v>
+      </c>
+      <c r="O61">
+        <v>-0.13826355</v>
+      </c>
+      <c r="P61">
+        <v>-0.41479065</v>
+      </c>
+      <c r="Q61">
+        <v>3.08520935</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1856392462125134</v>
+      </c>
+      <c r="T61">
+        <v>1.98843765875117</v>
+      </c>
+      <c r="U61">
+        <v>0.1566</v>
+      </c>
+      <c r="V61">
+        <v>0.2162199562370808</v>
+      </c>
+      <c r="W61">
+        <v>0.1227399548532732</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.8648798249483234</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1497066643105617</v>
+      </c>
+      <c r="C62">
+        <v>25.01132848779403</v>
+      </c>
+      <c r="D62">
+        <v>-12.00867151220598</v>
+      </c>
+      <c r="E62">
+        <v>26.58</v>
+      </c>
+      <c r="F62">
+        <v>26.58</v>
+      </c>
+      <c r="G62">
+        <v>63.6</v>
+      </c>
+      <c r="H62">
+        <v>44.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>7.04</v>
+      </c>
+      <c r="K62">
+        <v>3.5</v>
+      </c>
+      <c r="L62">
+        <v>3.54</v>
+      </c>
+      <c r="M62">
+        <v>4.162428</v>
+      </c>
+      <c r="N62">
+        <v>-0.6224280000000002</v>
+      </c>
+      <c r="O62">
+        <v>-0.1556070000000001</v>
+      </c>
+      <c r="P62">
+        <v>-0.4668210000000002</v>
+      </c>
+      <c r="Q62">
+        <v>3.033179</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1893102273678263</v>
+      </c>
+      <c r="T62">
+        <v>2.03814860021995</v>
+      </c>
+      <c r="U62">
+        <v>0.1566</v>
+      </c>
+      <c r="V62">
+        <v>0.2126162902997962</v>
+      </c>
+      <c r="W62">
+        <v>0.1233042889390519</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.8504651611991847</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1508846643105617</v>
+      </c>
+      <c r="C63">
+        <v>24.69453857307548</v>
+      </c>
+      <c r="D63">
+        <v>-11.88246142692453</v>
+      </c>
+      <c r="E63">
+        <v>27.023</v>
+      </c>
+      <c r="F63">
+        <v>27.023</v>
+      </c>
+      <c r="G63">
+        <v>63.6</v>
+      </c>
+      <c r="H63">
+        <v>44.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>7.04</v>
+      </c>
+      <c r="K63">
+        <v>3.5</v>
+      </c>
+      <c r="L63">
+        <v>3.54</v>
+      </c>
+      <c r="M63">
+        <v>4.2318018</v>
+      </c>
+      <c r="N63">
+        <v>-0.6918017999999995</v>
+      </c>
+      <c r="O63">
+        <v>-0.1729504499999999</v>
+      </c>
+      <c r="P63">
+        <v>-0.5188513499999996</v>
+      </c>
+      <c r="Q63">
+        <v>2.981148650000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1931694639670013</v>
+      </c>
+      <c r="T63">
+        <v>2.09040882073841</v>
+      </c>
+      <c r="U63">
+        <v>0.1566</v>
+      </c>
+      <c r="V63">
+        <v>0.2091307773440619</v>
+      </c>
+      <c r="W63">
+        <v>0.1238501202679199</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.8365231093762473</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1520626643105616</v>
+      </c>
+      <c r="C64">
+        <v>24.37512333638756</v>
+      </c>
+      <c r="D64">
+        <v>-11.75887666361244</v>
+      </c>
+      <c r="E64">
+        <v>27.466</v>
+      </c>
+      <c r="F64">
+        <v>27.466</v>
+      </c>
+      <c r="G64">
+        <v>63.6</v>
+      </c>
+      <c r="H64">
+        <v>44.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>7.04</v>
+      </c>
+      <c r="K64">
+        <v>3.5</v>
+      </c>
+      <c r="L64">
+        <v>3.54</v>
+      </c>
+      <c r="M64">
+        <v>4.3011756</v>
+      </c>
+      <c r="N64">
+        <v>-0.7611755999999996</v>
+      </c>
+      <c r="O64">
+        <v>-0.1902938999999999</v>
+      </c>
+      <c r="P64">
+        <v>-0.5708816999999997</v>
+      </c>
+      <c r="Q64">
+        <v>2.9291183</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1972318182819224</v>
+      </c>
+      <c r="T64">
+        <v>2.145419579178895</v>
+      </c>
+      <c r="U64">
+        <v>0.1566</v>
+      </c>
+      <c r="V64">
+        <v>0.2057577002901254</v>
+      </c>
+      <c r="W64">
+        <v>0.1243783441345664</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.8230308011605014</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1532406643105617</v>
+      </c>
+      <c r="C65">
+        <v>24.05316384933098</v>
+      </c>
+      <c r="D65">
+        <v>-11.63783615066903</v>
+      </c>
+      <c r="E65">
+        <v>27.909</v>
+      </c>
+      <c r="F65">
+        <v>27.909</v>
+      </c>
+      <c r="G65">
+        <v>63.6</v>
+      </c>
+      <c r="H65">
+        <v>44.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>7.04</v>
+      </c>
+      <c r="K65">
+        <v>3.5</v>
+      </c>
+      <c r="L65">
+        <v>3.54</v>
+      </c>
+      <c r="M65">
+        <v>4.370549400000001</v>
+      </c>
+      <c r="N65">
+        <v>-0.8305494000000007</v>
+      </c>
+      <c r="O65">
+        <v>-0.2076373500000002</v>
+      </c>
+      <c r="P65">
+        <v>-0.6229120500000005</v>
+      </c>
+      <c r="Q65">
+        <v>2.87708795</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2015137593165689</v>
+      </c>
+      <c r="T65">
+        <v>2.203403892129676</v>
+      </c>
+      <c r="U65">
+        <v>0.1566</v>
+      </c>
+      <c r="V65">
+        <v>0.2024917050474249</v>
+      </c>
+      <c r="W65">
+        <v>0.1248897989895733</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.8099668201896996</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1900274770688572</v>
+      </c>
+      <c r="C66">
+        <v>26.44112359080343</v>
+      </c>
+      <c r="D66">
+        <v>-8.806876409196567</v>
+      </c>
+      <c r="E66">
+        <v>28.352</v>
+      </c>
+      <c r="F66">
+        <v>28.352</v>
+      </c>
+      <c r="G66">
+        <v>63.6</v>
+      </c>
+      <c r="H66">
+        <v>44.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>7.04</v>
+      </c>
+      <c r="K66">
+        <v>3.5</v>
+      </c>
+      <c r="L66">
+        <v>3.54</v>
+      </c>
+      <c r="M66">
+        <v>5.919897600000001</v>
+      </c>
+      <c r="N66">
+        <v>-2.379897600000001</v>
+      </c>
+      <c r="O66">
+        <v>-0.5949744000000001</v>
+      </c>
+      <c r="P66">
+        <v>-1.7849232</v>
+      </c>
+      <c r="Q66">
+        <v>1.7150768</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2121469547372945</v>
+      </c>
+      <c r="T66">
+        <v>2.347394322159746</v>
+      </c>
+      <c r="U66">
+        <v>0.2088</v>
+      </c>
+      <c r="V66">
+        <v>0.1494958291170442</v>
+      </c>
+      <c r="W66">
+        <v>0.1775852708803612</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.5979833164681767</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1917274770688572</v>
+      </c>
+      <c r="C67">
+        <v>26.09602417860227</v>
+      </c>
+      <c r="D67">
+        <v>-8.708975821397729</v>
+      </c>
+      <c r="E67">
+        <v>28.795</v>
+      </c>
+      <c r="F67">
+        <v>28.795</v>
+      </c>
+      <c r="G67">
+        <v>63.6</v>
+      </c>
+      <c r="H67">
+        <v>44.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>7.04</v>
+      </c>
+      <c r="K67">
+        <v>3.5</v>
+      </c>
+      <c r="L67">
+        <v>3.54</v>
+      </c>
+      <c r="M67">
+        <v>6.012396</v>
+      </c>
+      <c r="N67">
+        <v>-2.472396</v>
+      </c>
+      <c r="O67">
+        <v>-0.618099</v>
+      </c>
+      <c r="P67">
+        <v>-1.854297</v>
+      </c>
+      <c r="Q67">
+        <v>1.645703</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2170997248726458</v>
+      </c>
+      <c r="T67">
+        <v>2.414462731364311</v>
+      </c>
+      <c r="U67">
+        <v>0.2088</v>
+      </c>
+      <c r="V67">
+        <v>0.1471958932844743</v>
+      </c>
+      <c r="W67">
+        <v>0.1780654974822018</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.5887835731378972</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1934274770688572</v>
+      </c>
+      <c r="C68">
+        <v>25.74877209596487</v>
+      </c>
+      <c r="D68">
+        <v>-8.613227904035131</v>
+      </c>
+      <c r="E68">
+        <v>29.238</v>
+      </c>
+      <c r="F68">
+        <v>29.238</v>
+      </c>
+      <c r="G68">
+        <v>63.6</v>
+      </c>
+      <c r="H68">
+        <v>44.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>7.04</v>
+      </c>
+      <c r="K68">
+        <v>3.5</v>
+      </c>
+      <c r="L68">
+        <v>3.54</v>
+      </c>
+      <c r="M68">
+        <v>6.1048944</v>
+      </c>
+      <c r="N68">
+        <v>-2.5648944</v>
+      </c>
+      <c r="O68">
+        <v>-0.6412236</v>
+      </c>
+      <c r="P68">
+        <v>-1.9236708</v>
+      </c>
+      <c r="Q68">
+        <v>1.5763292</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2223438344277237</v>
+      </c>
+      <c r="T68">
+        <v>2.48547634111032</v>
+      </c>
+      <c r="U68">
+        <v>0.2088</v>
+      </c>
+      <c r="V68">
+        <v>0.1449656524771337</v>
+      </c>
+      <c r="W68">
+        <v>0.1785311717627745</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.5798626099085351</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1951274770688572</v>
+      </c>
+      <c r="C69">
+        <v>25.39943757123132</v>
+      </c>
+      <c r="D69">
+        <v>-8.51956242876868</v>
+      </c>
+      <c r="E69">
+        <v>29.681</v>
+      </c>
+      <c r="F69">
+        <v>29.681</v>
+      </c>
+      <c r="G69">
+        <v>63.6</v>
+      </c>
+      <c r="H69">
+        <v>44.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>7.04</v>
+      </c>
+      <c r="K69">
+        <v>3.5</v>
+      </c>
+      <c r="L69">
+        <v>3.54</v>
+      </c>
+      <c r="M69">
+        <v>6.1973928</v>
+      </c>
+      <c r="N69">
+        <v>-2.6573928</v>
+      </c>
+      <c r="O69">
+        <v>-0.6643482000000001</v>
+      </c>
+      <c r="P69">
+        <v>-1.9930446</v>
+      </c>
+      <c r="Q69">
+        <v>1.5069554</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2279057688043213</v>
+      </c>
+      <c r="T69">
+        <v>2.560793805992451</v>
+      </c>
+      <c r="U69">
+        <v>0.2088</v>
+      </c>
+      <c r="V69">
+        <v>0.1428019860222512</v>
+      </c>
+      <c r="W69">
+        <v>0.178982945318554</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5712079440890047</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1968274770688572</v>
+      </c>
+      <c r="C70">
+        <v>25.04808781078173</v>
+      </c>
+      <c r="D70">
+        <v>-8.427912189218276</v>
+      </c>
+      <c r="E70">
+        <v>30.124</v>
+      </c>
+      <c r="F70">
+        <v>30.124</v>
+      </c>
+      <c r="G70">
+        <v>63.6</v>
+      </c>
+      <c r="H70">
+        <v>44.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>7.04</v>
+      </c>
+      <c r="K70">
+        <v>3.5</v>
+      </c>
+      <c r="L70">
+        <v>3.54</v>
+      </c>
+      <c r="M70">
+        <v>6.2898912</v>
+      </c>
+      <c r="N70">
+        <v>-2.7498912</v>
+      </c>
+      <c r="O70">
+        <v>-0.6874728000000001</v>
+      </c>
+      <c r="P70">
+        <v>-2.0624184</v>
+      </c>
+      <c r="Q70">
+        <v>1.4375816</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2338153240794564</v>
+      </c>
+      <c r="T70">
+        <v>2.640818612429715</v>
+      </c>
+      <c r="U70">
+        <v>0.2088</v>
+      </c>
+      <c r="V70">
+        <v>0.1407019568160416</v>
+      </c>
+      <c r="W70">
+        <v>0.1794214314168105</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5628078272641663</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1985274770688572</v>
+      </c>
+      <c r="C71">
+        <v>24.69478715985174</v>
+      </c>
+      <c r="D71">
+        <v>-8.338212840148266</v>
+      </c>
+      <c r="E71">
+        <v>30.567</v>
+      </c>
+      <c r="F71">
+        <v>30.567</v>
+      </c>
+      <c r="G71">
+        <v>63.6</v>
+      </c>
+      <c r="H71">
+        <v>44.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>7.04</v>
+      </c>
+      <c r="K71">
+        <v>3.5</v>
+      </c>
+      <c r="L71">
+        <v>3.54</v>
+      </c>
+      <c r="M71">
+        <v>6.382389600000001</v>
+      </c>
+      <c r="N71">
+        <v>-2.842389600000001</v>
+      </c>
+      <c r="O71">
+        <v>-0.7105974000000002</v>
+      </c>
+      <c r="P71">
+        <v>-2.1317922</v>
+      </c>
+      <c r="Q71">
+        <v>1.3682078</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2401061409852453</v>
+      </c>
+      <c r="T71">
+        <v>2.726006309604867</v>
+      </c>
+      <c r="U71">
+        <v>0.2088</v>
+      </c>
+      <c r="V71">
+        <v>0.1386627980216062</v>
+      </c>
+      <c r="W71">
+        <v>0.1798472077730886</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5546511920864248</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2002274770688572</v>
+      </c>
+      <c r="C72">
+        <v>24.33959725318674</v>
+      </c>
+      <c r="D72">
+        <v>-8.250402746813256</v>
+      </c>
+      <c r="E72">
+        <v>31.01</v>
+      </c>
+      <c r="F72">
+        <v>31.01</v>
+      </c>
+      <c r="G72">
+        <v>63.6</v>
+      </c>
+      <c r="H72">
+        <v>44.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>7.04</v>
+      </c>
+      <c r="K72">
+        <v>3.5</v>
+      </c>
+      <c r="L72">
+        <v>3.54</v>
+      </c>
+      <c r="M72">
+        <v>6.474888000000001</v>
+      </c>
+      <c r="N72">
+        <v>-2.934888000000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.7337220000000002</v>
+      </c>
+      <c r="P72">
+        <v>-2.201166000000001</v>
+      </c>
+      <c r="Q72">
+        <v>1.298833999999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2468163456847534</v>
+      </c>
+      <c r="T72">
+        <v>2.816873186591696</v>
+      </c>
+      <c r="U72">
+        <v>0.2088</v>
+      </c>
+      <c r="V72">
+        <v>0.1366819009070118</v>
+      </c>
+      <c r="W72">
+        <v>0.1802608190906159</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.5467276036280473</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2019274770688572</v>
+      </c>
+      <c r="C73">
+        <v>23.98257715627605</v>
+      </c>
+      <c r="D73">
+        <v>-8.164422843723953</v>
+      </c>
+      <c r="E73">
+        <v>31.453</v>
+      </c>
+      <c r="F73">
+        <v>31.453</v>
+      </c>
+      <c r="G73">
+        <v>63.6</v>
+      </c>
+      <c r="H73">
+        <v>44.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>7.04</v>
+      </c>
+      <c r="K73">
+        <v>3.5</v>
+      </c>
+      <c r="L73">
+        <v>3.54</v>
+      </c>
+      <c r="M73">
+        <v>6.567386399999999</v>
+      </c>
+      <c r="N73">
+        <v>-3.027386399999999</v>
+      </c>
+      <c r="O73">
+        <v>-0.7568465999999998</v>
+      </c>
+      <c r="P73">
+        <v>-2.270539799999999</v>
+      </c>
+      <c r="Q73">
+        <v>1.229460200000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2539893231221587</v>
+      </c>
+      <c r="T73">
+        <v>2.91400674475003</v>
+      </c>
+      <c r="U73">
+        <v>0.2088</v>
+      </c>
+      <c r="V73">
+        <v>0.1347568037111384</v>
+      </c>
+      <c r="W73">
+        <v>0.1806627793851143</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.5390272148445537</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2036274770688572</v>
+      </c>
+      <c r="C74">
+        <v>23.62378349784695</v>
+      </c>
+      <c r="D74">
+        <v>-8.08021650215305</v>
+      </c>
+      <c r="E74">
+        <v>31.896</v>
+      </c>
+      <c r="F74">
+        <v>31.896</v>
+      </c>
+      <c r="G74">
+        <v>63.6</v>
+      </c>
+      <c r="H74">
+        <v>44.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>7.04</v>
+      </c>
+      <c r="K74">
+        <v>3.5</v>
+      </c>
+      <c r="L74">
+        <v>3.54</v>
+      </c>
+      <c r="M74">
+        <v>6.659884799999999</v>
+      </c>
+      <c r="N74">
+        <v>-3.119884799999999</v>
+      </c>
+      <c r="O74">
+        <v>-0.7799711999999999</v>
+      </c>
+      <c r="P74">
+        <v>-2.3399136</v>
+      </c>
+      <c r="Q74">
+        <v>1.1600864</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2616746560908072</v>
+      </c>
+      <c r="T74">
+        <v>3.018078414205388</v>
+      </c>
+      <c r="U74">
+        <v>0.2088</v>
+      </c>
+      <c r="V74">
+        <v>0.1328851814373726</v>
+      </c>
+      <c r="W74">
+        <v>0.1810535741158766</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5315407257494904</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2053274770688572</v>
+      </c>
+      <c r="C75">
+        <v>23.26327059424354</v>
+      </c>
+      <c r="D75">
+        <v>-7.997729405756457</v>
+      </c>
+      <c r="E75">
+        <v>32.339</v>
+      </c>
+      <c r="F75">
+        <v>32.339</v>
+      </c>
+      <c r="G75">
+        <v>63.6</v>
+      </c>
+      <c r="H75">
+        <v>44.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>7.04</v>
+      </c>
+      <c r="K75">
+        <v>3.5</v>
+      </c>
+      <c r="L75">
+        <v>3.54</v>
+      </c>
+      <c r="M75">
+        <v>6.752383200000001</v>
+      </c>
+      <c r="N75">
+        <v>-3.212383200000001</v>
+      </c>
+      <c r="O75">
+        <v>-0.8030958000000001</v>
+      </c>
+      <c r="P75">
+        <v>-2.4092874</v>
+      </c>
+      <c r="Q75">
+        <v>1.0907126</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2699292729830594</v>
+      </c>
+      <c r="T75">
+        <v>3.129859096212995</v>
+      </c>
+      <c r="U75">
+        <v>0.2088</v>
+      </c>
+      <c r="V75">
+        <v>0.1310648364861757</v>
+      </c>
+      <c r="W75">
+        <v>0.1814336621416865</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5242593459447029</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2070274770688572</v>
+      </c>
+      <c r="C76">
+        <v>22.90109056626406</v>
+      </c>
+      <c r="D76">
+        <v>-7.916909433735949</v>
+      </c>
+      <c r="E76">
+        <v>32.782</v>
+      </c>
+      <c r="F76">
+        <v>32.782</v>
+      </c>
+      <c r="G76">
+        <v>63.6</v>
+      </c>
+      <c r="H76">
+        <v>44.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>7.04</v>
+      </c>
+      <c r="K76">
+        <v>3.5</v>
+      </c>
+      <c r="L76">
+        <v>3.54</v>
+      </c>
+      <c r="M76">
+        <v>6.8448816</v>
+      </c>
+      <c r="N76">
+        <v>-3.3048816</v>
+      </c>
+      <c r="O76">
+        <v>-0.8262204</v>
+      </c>
+      <c r="P76">
+        <v>-2.4786612</v>
+      </c>
+      <c r="Q76">
+        <v>1.0213388</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2788188604054846</v>
+      </c>
+      <c r="T76">
+        <v>3.250238292221187</v>
+      </c>
+      <c r="U76">
+        <v>0.2088</v>
+      </c>
+      <c r="V76">
+        <v>0.1292936900471734</v>
+      </c>
+      <c r="W76">
+        <v>0.1818034775181502</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5171747601886933</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2087274770688572</v>
+      </c>
+      <c r="C77">
+        <v>22.53729344898501</v>
+      </c>
+      <c r="D77">
+        <v>-7.837706551015</v>
+      </c>
+      <c r="E77">
+        <v>33.22499999999999</v>
+      </c>
+      <c r="F77">
+        <v>33.22499999999999</v>
+      </c>
+      <c r="G77">
+        <v>63.6</v>
+      </c>
+      <c r="H77">
+        <v>44.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>7.04</v>
+      </c>
+      <c r="K77">
+        <v>3.5</v>
+      </c>
+      <c r="L77">
+        <v>3.54</v>
+      </c>
+      <c r="M77">
+        <v>6.937379999999999</v>
+      </c>
+      <c r="N77">
+        <v>-3.397379999999999</v>
+      </c>
+      <c r="O77">
+        <v>-0.8493449999999998</v>
+      </c>
+      <c r="P77">
+        <v>-2.548035</v>
+      </c>
+      <c r="Q77">
+        <v>0.9519650000000004</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2884196148217041</v>
+      </c>
+      <c r="T77">
+        <v>3.380247823910035</v>
+      </c>
+      <c r="U77">
+        <v>0.2088</v>
+      </c>
+      <c r="V77">
+        <v>0.1275697741798777</v>
+      </c>
+      <c r="W77">
+        <v>0.1821634311512416</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5102790967195109</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2104274770688572</v>
+      </c>
+      <c r="C78">
+        <v>22.17192729505838</v>
+      </c>
+      <c r="D78">
+        <v>-7.760072704941623</v>
+      </c>
+      <c r="E78">
+        <v>33.668</v>
+      </c>
+      <c r="F78">
+        <v>33.668</v>
+      </c>
+      <c r="G78">
+        <v>63.6</v>
+      </c>
+      <c r="H78">
+        <v>44.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>7.04</v>
+      </c>
+      <c r="K78">
+        <v>3.5</v>
+      </c>
+      <c r="L78">
+        <v>3.54</v>
+      </c>
+      <c r="M78">
+        <v>7.0298784</v>
+      </c>
+      <c r="N78">
+        <v>-3.4898784</v>
+      </c>
+      <c r="O78">
+        <v>-0.8724696000000001</v>
+      </c>
+      <c r="P78">
+        <v>-2.6174088</v>
+      </c>
+      <c r="Q78">
+        <v>0.8825911999999998</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2988204321059417</v>
+      </c>
+      <c r="T78">
+        <v>3.521091483239619</v>
+      </c>
+      <c r="U78">
+        <v>0.2088</v>
+      </c>
+      <c r="V78">
+        <v>0.1258912245196162</v>
+      </c>
+      <c r="W78">
+        <v>0.1825139123203041</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5035648980784646</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2360569291134409</v>
+      </c>
+      <c r="C79">
+        <v>22.73718800431543</v>
+      </c>
+      <c r="D79">
+        <v>-6.751811995684578</v>
+      </c>
+      <c r="E79">
+        <v>34.111</v>
+      </c>
+      <c r="F79">
+        <v>34.111</v>
+      </c>
+      <c r="G79">
+        <v>63.6</v>
+      </c>
+      <c r="H79">
+        <v>44.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>7.04</v>
+      </c>
+      <c r="K79">
+        <v>3.5</v>
+      </c>
+      <c r="L79">
+        <v>3.54</v>
+      </c>
+      <c r="M79">
+        <v>8.145706799999999</v>
+      </c>
+      <c r="N79">
+        <v>-4.605706799999999</v>
+      </c>
+      <c r="O79">
+        <v>-1.1514267</v>
+      </c>
+      <c r="P79">
+        <v>-3.454280099999999</v>
+      </c>
+      <c r="Q79">
+        <v>0.04571990000000081</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3137319815217816</v>
+      </c>
+      <c r="T79">
+        <v>3.723017651982497</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.108646188934765</v>
+      </c>
+      <c r="W79">
+        <v>0.2128552900823781</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.4345847557390601</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.238056929113441</v>
+      </c>
+      <c r="C80">
+        <v>22.36195791350478</v>
+      </c>
+      <c r="D80">
+        <v>-6.684042086495215</v>
+      </c>
+      <c r="E80">
+        <v>34.554</v>
+      </c>
+      <c r="F80">
+        <v>34.554</v>
+      </c>
+      <c r="G80">
+        <v>63.6</v>
+      </c>
+      <c r="H80">
+        <v>44.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>7.04</v>
+      </c>
+      <c r="K80">
+        <v>3.5</v>
+      </c>
+      <c r="L80">
+        <v>3.54</v>
+      </c>
+      <c r="M80">
+        <v>8.251495200000001</v>
+      </c>
+      <c r="N80">
+        <v>-4.711495200000001</v>
+      </c>
+      <c r="O80">
+        <v>-1.1778738</v>
+      </c>
+      <c r="P80">
+        <v>-3.5336214</v>
+      </c>
+      <c r="Q80">
+        <v>-0.03362140000000036</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3262288897727717</v>
+      </c>
+      <c r="T80">
+        <v>3.892245727072611</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.107253289076627</v>
+      </c>
+      <c r="W80">
+        <v>0.2131879145685015</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.4290131563065079</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2400569291134409</v>
+      </c>
+      <c r="C81">
+        <v>21.98538088950804</v>
+      </c>
+      <c r="D81">
+        <v>-6.617619110491964</v>
+      </c>
+      <c r="E81">
+        <v>34.997</v>
+      </c>
+      <c r="F81">
+        <v>34.997</v>
+      </c>
+      <c r="G81">
+        <v>63.6</v>
+      </c>
+      <c r="H81">
+        <v>44.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>7.04</v>
+      </c>
+      <c r="K81">
+        <v>3.5</v>
+      </c>
+      <c r="L81">
+        <v>3.54</v>
+      </c>
+      <c r="M81">
+        <v>8.357283600000001</v>
+      </c>
+      <c r="N81">
+        <v>-4.817283600000001</v>
+      </c>
+      <c r="O81">
+        <v>-1.2043209</v>
+      </c>
+      <c r="P81">
+        <v>-3.612962700000001</v>
+      </c>
+      <c r="Q81">
+        <v>-0.1129627000000006</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3399159797619513</v>
+      </c>
+      <c r="T81">
+        <v>4.077590761695117</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.1058956525060368</v>
+      </c>
+      <c r="W81">
+        <v>0.2135121181815584</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.4235826100241471</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2420569291134409</v>
+      </c>
+      <c r="C82">
+        <v>21.60749669283496</v>
+      </c>
+      <c r="D82">
+        <v>-6.552503307165046</v>
+      </c>
+      <c r="E82">
+        <v>35.44</v>
+      </c>
+      <c r="F82">
+        <v>35.44</v>
+      </c>
+      <c r="G82">
+        <v>63.6</v>
+      </c>
+      <c r="H82">
+        <v>44.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>7.04</v>
+      </c>
+      <c r="K82">
+        <v>3.5</v>
+      </c>
+      <c r="L82">
+        <v>3.54</v>
+      </c>
+      <c r="M82">
+        <v>8.463072</v>
+      </c>
+      <c r="N82">
+        <v>-4.923072</v>
+      </c>
+      <c r="O82">
+        <v>-1.230768</v>
+      </c>
+      <c r="P82">
+        <v>-3.692304</v>
+      </c>
+      <c r="Q82">
+        <v>-0.192304</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3549717787500489</v>
+      </c>
+      <c r="T82">
+        <v>4.281470299779873</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.1045719568497113</v>
+      </c>
+      <c r="W82">
+        <v>0.2138282167042889</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.4182878273988452</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2440569291134409</v>
+      </c>
+      <c r="C83">
+        <v>21.2283435343079</v>
+      </c>
+      <c r="D83">
+        <v>-6.488656465692098</v>
+      </c>
+      <c r="E83">
+        <v>35.883</v>
+      </c>
+      <c r="F83">
+        <v>35.883</v>
+      </c>
+      <c r="G83">
+        <v>63.6</v>
+      </c>
+      <c r="H83">
+        <v>44.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>7.04</v>
+      </c>
+      <c r="K83">
+        <v>3.5</v>
+      </c>
+      <c r="L83">
+        <v>3.54</v>
+      </c>
+      <c r="M83">
+        <v>8.568860400000002</v>
+      </c>
+      <c r="N83">
+        <v>-5.028860400000002</v>
+      </c>
+      <c r="O83">
+        <v>-1.2572151</v>
+      </c>
+      <c r="P83">
+        <v>-3.771645300000001</v>
+      </c>
+      <c r="Q83">
+        <v>-0.2716453000000012</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.371612398684262</v>
+      </c>
+      <c r="T83">
+        <v>4.50681084187355</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.1032809450367519</v>
+      </c>
+      <c r="W83">
+        <v>0.2141365103252237</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.4131237801470076</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2460569291134409</v>
+      </c>
+      <c r="C84">
+        <v>20.84795814983316</v>
+      </c>
+      <c r="D84">
+        <v>-6.426041850166837</v>
+      </c>
+      <c r="E84">
+        <v>36.326</v>
+      </c>
+      <c r="F84">
+        <v>36.326</v>
+      </c>
+      <c r="G84">
+        <v>63.6</v>
+      </c>
+      <c r="H84">
+        <v>44.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>7.04</v>
+      </c>
+      <c r="K84">
+        <v>3.5</v>
+      </c>
+      <c r="L84">
+        <v>3.54</v>
+      </c>
+      <c r="M84">
+        <v>8.6746488</v>
+      </c>
+      <c r="N84">
+        <v>-5.1346488</v>
+      </c>
+      <c r="O84">
+        <v>-1.2836622</v>
+      </c>
+      <c r="P84">
+        <v>-3.8509866</v>
+      </c>
+      <c r="Q84">
+        <v>-0.3509865999999997</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3901019763889432</v>
+      </c>
+      <c r="T84">
+        <v>4.757189221977637</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.1020214213167915</v>
+      </c>
+      <c r="W84">
+        <v>0.2144372845895502</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.408085685267166</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2480569291134409</v>
+      </c>
+      <c r="C85">
+        <v>20.46637587088443</v>
+      </c>
+      <c r="D85">
+        <v>-6.364624129115573</v>
+      </c>
+      <c r="E85">
+        <v>36.769</v>
+      </c>
+      <c r="F85">
+        <v>36.769</v>
+      </c>
+      <c r="G85">
+        <v>63.6</v>
+      </c>
+      <c r="H85">
+        <v>44.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>7.04</v>
+      </c>
+      <c r="K85">
+        <v>3.5</v>
+      </c>
+      <c r="L85">
+        <v>3.54</v>
+      </c>
+      <c r="M85">
+        <v>8.7804372</v>
+      </c>
+      <c r="N85">
+        <v>-5.2404372</v>
+      </c>
+      <c r="O85">
+        <v>-1.3101093</v>
+      </c>
+      <c r="P85">
+        <v>-3.9303279</v>
+      </c>
+      <c r="Q85">
+        <v>-0.4303279</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4107667985294693</v>
+      </c>
+      <c r="T85">
+        <v>5.037023882093968</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.1007922475659868</v>
+      </c>
+      <c r="W85">
+        <v>0.2147308112812424</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.4031689902639473</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.250056929113441</v>
+      </c>
+      <c r="C86">
+        <v>20.08363069098264</v>
+      </c>
+      <c r="D86">
+        <v>-6.30436930901736</v>
+      </c>
+      <c r="E86">
+        <v>37.212</v>
+      </c>
+      <c r="F86">
+        <v>37.212</v>
+      </c>
+      <c r="G86">
+        <v>63.6</v>
+      </c>
+      <c r="H86">
+        <v>44.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>7.04</v>
+      </c>
+      <c r="K86">
+        <v>3.5</v>
+      </c>
+      <c r="L86">
+        <v>3.54</v>
+      </c>
+      <c r="M86">
+        <v>8.8862256</v>
+      </c>
+      <c r="N86">
+        <v>-5.346225599999999</v>
+      </c>
+      <c r="O86">
+        <v>-1.3365564</v>
+      </c>
+      <c r="P86">
+        <v>-4.009669199999999</v>
+      </c>
+      <c r="Q86">
+        <v>-0.5096691999999994</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.434014723437561</v>
+      </c>
+      <c r="T86">
+        <v>5.351837874724839</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.09959233985686793</v>
+      </c>
+      <c r="W86">
+        <v>0.21501734924218</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3983693594274716</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2520569291134409</v>
+      </c>
+      <c r="C87">
+        <v>19.699755328435</v>
+      </c>
+      <c r="D87">
+        <v>-6.245244671565006</v>
+      </c>
+      <c r="E87">
+        <v>37.65499999999999</v>
+      </c>
+      <c r="F87">
+        <v>37.65499999999999</v>
+      </c>
+      <c r="G87">
+        <v>63.6</v>
+      </c>
+      <c r="H87">
+        <v>44.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>7.04</v>
+      </c>
+      <c r="K87">
+        <v>3.5</v>
+      </c>
+      <c r="L87">
+        <v>3.54</v>
+      </c>
+      <c r="M87">
+        <v>8.992013999999999</v>
+      </c>
+      <c r="N87">
+        <v>-5.452013999999999</v>
+      </c>
+      <c r="O87">
+        <v>-1.3630035</v>
+      </c>
+      <c r="P87">
+        <v>-4.0890105</v>
+      </c>
+      <c r="Q87">
+        <v>-0.5890104999999997</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4603623716667317</v>
+      </c>
+      <c r="T87">
+        <v>5.708627066373161</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.09842066527031654</v>
+      </c>
+      <c r="W87">
+        <v>0.2152971451334484</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3936826610812661</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2540569291134409</v>
+      </c>
+      <c r="C88">
+        <v>19.31478128557642</v>
+      </c>
+      <c r="D88">
+        <v>-6.187218714423588</v>
+      </c>
+      <c r="E88">
+        <v>38.098</v>
+      </c>
+      <c r="F88">
+        <v>38.098</v>
+      </c>
+      <c r="G88">
+        <v>63.6</v>
+      </c>
+      <c r="H88">
+        <v>44.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>7.04</v>
+      </c>
+      <c r="K88">
+        <v>3.5</v>
+      </c>
+      <c r="L88">
+        <v>3.54</v>
+      </c>
+      <c r="M88">
+        <v>9.097802400000001</v>
+      </c>
+      <c r="N88">
+        <v>-5.557802400000001</v>
+      </c>
+      <c r="O88">
+        <v>-1.3894506</v>
+      </c>
+      <c r="P88">
+        <v>-4.168351800000001</v>
+      </c>
+      <c r="Q88">
+        <v>-0.6683518000000008</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4904739696429268</v>
+      </c>
+      <c r="T88">
+        <v>6.116386142542673</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.097276238929964</v>
+      </c>
+      <c r="W88">
+        <v>0.2155704341435246</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.389104955719856</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2560569291134409</v>
+      </c>
+      <c r="C89">
+        <v>18.92873890473887</v>
+      </c>
+      <c r="D89">
+        <v>-6.130261095261136</v>
+      </c>
+      <c r="E89">
+        <v>38.541</v>
+      </c>
+      <c r="F89">
+        <v>38.541</v>
+      </c>
+      <c r="G89">
+        <v>63.6</v>
+      </c>
+      <c r="H89">
+        <v>44.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>7.04</v>
+      </c>
+      <c r="K89">
+        <v>3.5</v>
+      </c>
+      <c r="L89">
+        <v>3.54</v>
+      </c>
+      <c r="M89">
+        <v>9.203590799999999</v>
+      </c>
+      <c r="N89">
+        <v>-5.663590799999999</v>
+      </c>
+      <c r="O89">
+        <v>-1.4158977</v>
+      </c>
+      <c r="P89">
+        <v>-4.247693099999999</v>
+      </c>
+      <c r="Q89">
+        <v>-0.7476930999999993</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5252181211539212</v>
+      </c>
+      <c r="T89">
+        <v>6.586877384276725</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.09615812124111386</v>
+      </c>
+      <c r="W89">
+        <v>0.215837440647622</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.3846324849644555</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2580569291134409</v>
+      </c>
+      <c r="C90">
+        <v>18.54165742115747</v>
+      </c>
+      <c r="D90">
+        <v>-6.074342578842532</v>
+      </c>
+      <c r="E90">
+        <v>38.98399999999999</v>
+      </c>
+      <c r="F90">
+        <v>38.98399999999999</v>
+      </c>
+      <c r="G90">
+        <v>63.6</v>
+      </c>
+      <c r="H90">
+        <v>44.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>7.04</v>
+      </c>
+      <c r="K90">
+        <v>3.5</v>
+      </c>
+      <c r="L90">
+        <v>3.54</v>
+      </c>
+      <c r="M90">
+        <v>9.309379199999999</v>
+      </c>
+      <c r="N90">
+        <v>-5.769379199999999</v>
+      </c>
+      <c r="O90">
+        <v>-1.4423448</v>
+      </c>
+      <c r="P90">
+        <v>-4.327034399999999</v>
+      </c>
+      <c r="Q90">
+        <v>-0.8270343999999987</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5657529645834147</v>
+      </c>
+      <c r="T90">
+        <v>7.135783832966452</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.09506541531791939</v>
+      </c>
+      <c r="W90">
+        <v>0.2160983788220809</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3802616612716776</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2600569291134409</v>
+      </c>
+      <c r="C91">
+        <v>18.1535650130072</v>
+      </c>
+      <c r="D91">
+        <v>-6.019434986992804</v>
+      </c>
+      <c r="E91">
+        <v>39.427</v>
+      </c>
+      <c r="F91">
+        <v>39.427</v>
+      </c>
+      <c r="G91">
+        <v>63.6</v>
+      </c>
+      <c r="H91">
+        <v>44.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>7.04</v>
+      </c>
+      <c r="K91">
+        <v>3.5</v>
+      </c>
+      <c r="L91">
+        <v>3.54</v>
+      </c>
+      <c r="M91">
+        <v>9.4151676</v>
+      </c>
+      <c r="N91">
+        <v>-5.8751676</v>
+      </c>
+      <c r="O91">
+        <v>-1.4687919</v>
+      </c>
+      <c r="P91">
+        <v>-4.4063757</v>
+      </c>
+      <c r="Q91">
+        <v>-0.9063756999999999</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6136577795455433</v>
+      </c>
+      <c r="T91">
+        <v>7.784491454145222</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.09399726458401017</v>
+      </c>
+      <c r="W91">
+        <v>0.2163534532173384</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3759890583360407</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2620569291134409</v>
+      </c>
+      <c r="C92">
+        <v>17.76448884875013</v>
+      </c>
+      <c r="D92">
+        <v>-5.965511151249868</v>
+      </c>
+      <c r="E92">
+        <v>39.87</v>
+      </c>
+      <c r="F92">
+        <v>39.87</v>
+      </c>
+      <c r="G92">
+        <v>63.6</v>
+      </c>
+      <c r="H92">
+        <v>44.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>7.04</v>
+      </c>
+      <c r="K92">
+        <v>3.5</v>
+      </c>
+      <c r="L92">
+        <v>3.54</v>
+      </c>
+      <c r="M92">
+        <v>9.520956</v>
+      </c>
+      <c r="N92">
+        <v>-5.980956</v>
+      </c>
+      <c r="O92">
+        <v>-1.495239</v>
+      </c>
+      <c r="P92">
+        <v>-4.485717</v>
+      </c>
+      <c r="Q92">
+        <v>-0.9857170000000002</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6711435575000977</v>
+      </c>
+      <c r="T92">
+        <v>8.562940599559743</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.09295285053307673</v>
+      </c>
+      <c r="W92">
+        <v>0.2166028592927013</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3718114021323069</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2640569291134409</v>
+      </c>
+      <c r="C93">
+        <v>17.37445513196042</v>
+      </c>
+      <c r="D93">
+        <v>-5.912544868039592</v>
+      </c>
+      <c r="E93">
+        <v>40.313</v>
+      </c>
+      <c r="F93">
+        <v>40.313</v>
+      </c>
+      <c r="G93">
+        <v>63.6</v>
+      </c>
+      <c r="H93">
+        <v>44.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>7.04</v>
+      </c>
+      <c r="K93">
+        <v>3.5</v>
+      </c>
+      <c r="L93">
+        <v>3.54</v>
+      </c>
+      <c r="M93">
+        <v>9.6267444</v>
+      </c>
+      <c r="N93">
+        <v>-6.0867444</v>
+      </c>
+      <c r="O93">
+        <v>-1.5216861</v>
+      </c>
+      <c r="P93">
+        <v>-4.5650583</v>
+      </c>
+      <c r="Q93">
+        <v>-1.0650583</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7414039527778864</v>
+      </c>
+      <c r="T93">
+        <v>9.514378443955273</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.09193139063710885</v>
+      </c>
+      <c r="W93">
+        <v>0.2168467839158584</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3677255625484354</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2660569291134409</v>
+      </c>
+      <c r="C94">
+        <v>16.98348914378223</v>
+      </c>
+      <c r="D94">
+        <v>-5.860510856217771</v>
+      </c>
+      <c r="E94">
+        <v>40.756</v>
+      </c>
+      <c r="F94">
+        <v>40.756</v>
+      </c>
+      <c r="G94">
+        <v>63.6</v>
+      </c>
+      <c r="H94">
+        <v>44.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>7.04</v>
+      </c>
+      <c r="K94">
+        <v>3.5</v>
+      </c>
+      <c r="L94">
+        <v>3.54</v>
+      </c>
+      <c r="M94">
+        <v>9.732532800000001</v>
+      </c>
+      <c r="N94">
+        <v>-6.192532800000001</v>
+      </c>
+      <c r="O94">
+        <v>-1.5481332</v>
+      </c>
+      <c r="P94">
+        <v>-4.644399600000001</v>
+      </c>
+      <c r="Q94">
+        <v>-1.144399600000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8292294468751225</v>
+      </c>
+      <c r="T94">
+        <v>10.70367574944968</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.0909321363910533</v>
+      </c>
+      <c r="W94">
+        <v>0.2170854058298165</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3637285455642132</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2680569291134409</v>
+      </c>
+      <c r="C95">
+        <v>16.59161528316551</v>
+      </c>
+      <c r="D95">
+        <v>-5.809384716834496</v>
+      </c>
+      <c r="E95">
+        <v>41.199</v>
+      </c>
+      <c r="F95">
+        <v>41.199</v>
+      </c>
+      <c r="G95">
+        <v>63.6</v>
+      </c>
+      <c r="H95">
+        <v>44.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>7.04</v>
+      </c>
+      <c r="K95">
+        <v>3.5</v>
+      </c>
+      <c r="L95">
+        <v>3.54</v>
+      </c>
+      <c r="M95">
+        <v>9.838321199999999</v>
+      </c>
+      <c r="N95">
+        <v>-6.298321199999999</v>
+      </c>
+      <c r="O95">
+        <v>-1.5745803</v>
+      </c>
+      <c r="P95">
+        <v>-4.723740899999999</v>
+      </c>
+      <c r="Q95">
+        <v>-1.223740899999999</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9421479392858543</v>
+      </c>
+      <c r="T95">
+        <v>12.23277228508536</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.08995437148362263</v>
+      </c>
+      <c r="W95">
+        <v>0.2173188960897109</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3598174859344906</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2700569291134409</v>
+      </c>
+      <c r="C96">
+        <v>16.19885710501366</v>
+      </c>
+      <c r="D96">
+        <v>-5.759142894986341</v>
+      </c>
+      <c r="E96">
+        <v>41.642</v>
+      </c>
+      <c r="F96">
+        <v>41.642</v>
+      </c>
+      <c r="G96">
+        <v>63.6</v>
+      </c>
+      <c r="H96">
+        <v>44.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>7.04</v>
+      </c>
+      <c r="K96">
+        <v>3.5</v>
+      </c>
+      <c r="L96">
+        <v>3.54</v>
+      </c>
+      <c r="M96">
+        <v>9.944109600000001</v>
+      </c>
+      <c r="N96">
+        <v>-6.404109600000001</v>
+      </c>
+      <c r="O96">
+        <v>-1.6010274</v>
+      </c>
+      <c r="P96">
+        <v>-4.8030822</v>
+      </c>
+      <c r="Q96">
+        <v>-1.3030822</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.09270592916683</v>
+      </c>
+      <c r="T96">
+        <v>14.27156766593292</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.08899741008486069</v>
+      </c>
+      <c r="W96">
+        <v>0.2175474184717353</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3559896403394427</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.272056929113441</v>
+      </c>
+      <c r="C97">
+        <v>15.8052373563689</v>
+      </c>
+      <c r="D97">
+        <v>-5.7097626436311</v>
+      </c>
+      <c r="E97">
+        <v>42.085</v>
+      </c>
+      <c r="F97">
+        <v>42.085</v>
+      </c>
+      <c r="G97">
+        <v>63.6</v>
+      </c>
+      <c r="H97">
+        <v>44.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>7.04</v>
+      </c>
+      <c r="K97">
+        <v>3.5</v>
+      </c>
+      <c r="L97">
+        <v>3.54</v>
+      </c>
+      <c r="M97">
+        <v>10.049898</v>
+      </c>
+      <c r="N97">
+        <v>-6.509898000000001</v>
+      </c>
+      <c r="O97">
+        <v>-1.6274745</v>
+      </c>
+      <c r="P97">
+        <v>-4.882423500000001</v>
+      </c>
+      <c r="Q97">
+        <v>-1.382423500000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.303487115000197</v>
+      </c>
+      <c r="T97">
+        <v>17.12588119911951</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.08806059524186215</v>
+      </c>
+      <c r="W97">
+        <v>0.2177711298562433</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3522423809674486</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2740569291134409</v>
+      </c>
+      <c r="C98">
+        <v>15.41077801075173</v>
+      </c>
+      <c r="D98">
+        <v>-5.661221989248271</v>
+      </c>
+      <c r="E98">
+        <v>42.528</v>
+      </c>
+      <c r="F98">
+        <v>42.528</v>
+      </c>
+      <c r="G98">
+        <v>63.6</v>
+      </c>
+      <c r="H98">
+        <v>44.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>7.04</v>
+      </c>
+      <c r="K98">
+        <v>3.5</v>
+      </c>
+      <c r="L98">
+        <v>3.54</v>
+      </c>
+      <c r="M98">
+        <v>10.1556864</v>
+      </c>
+      <c r="N98">
+        <v>-6.6156864</v>
+      </c>
+      <c r="O98">
+        <v>-1.6539216</v>
+      </c>
+      <c r="P98">
+        <v>-4.9617648</v>
+      </c>
+      <c r="Q98">
+        <v>-1.4617648</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.619658893750243</v>
+      </c>
+      <c r="T98">
+        <v>21.40735149889934</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.08714329737475943</v>
+      </c>
+      <c r="W98">
+        <v>0.2179901805869074</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3485731894990377</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2760569291134409</v>
+      </c>
+      <c r="C99">
+        <v>15.01550030076368</v>
+      </c>
+      <c r="D99">
+        <v>-5.613499699236318</v>
+      </c>
+      <c r="E99">
+        <v>42.971</v>
+      </c>
+      <c r="F99">
+        <v>42.971</v>
+      </c>
+      <c r="G99">
+        <v>63.6</v>
+      </c>
+      <c r="H99">
+        <v>44.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>7.04</v>
+      </c>
+      <c r="K99">
+        <v>3.5</v>
+      </c>
+      <c r="L99">
+        <v>3.54</v>
+      </c>
+      <c r="M99">
+        <v>10.2614748</v>
+      </c>
+      <c r="N99">
+        <v>-6.7214748</v>
+      </c>
+      <c r="O99">
+        <v>-1.6803687</v>
+      </c>
+      <c r="P99">
+        <v>-5.0411061</v>
+      </c>
+      <c r="Q99">
+        <v>-1.5411061</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.146611858333657</v>
+      </c>
+      <c r="T99">
+        <v>28.54313533186579</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.08624491286574129</v>
+      </c>
+      <c r="W99">
+        <v>0.218204714807661</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3449796514629652</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2780569291134409</v>
+      </c>
+      <c r="C100">
+        <v>14.61942474905479</v>
+      </c>
+      <c r="D100">
+        <v>-5.566575250945212</v>
+      </c>
+      <c r="E100">
+        <v>43.41399999999999</v>
+      </c>
+      <c r="F100">
+        <v>43.41399999999999</v>
+      </c>
+      <c r="G100">
+        <v>63.6</v>
+      </c>
+      <c r="H100">
+        <v>44.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>7.04</v>
+      </c>
+      <c r="K100">
+        <v>3.5</v>
+      </c>
+      <c r="L100">
+        <v>3.54</v>
+      </c>
+      <c r="M100">
+        <v>10.3672632</v>
+      </c>
+      <c r="N100">
+        <v>-6.8272632</v>
+      </c>
+      <c r="O100">
+        <v>-1.7068158</v>
+      </c>
+      <c r="P100">
+        <v>-5.1204474</v>
+      </c>
+      <c r="Q100">
+        <v>-1.6204474</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.200517787500485</v>
+      </c>
+      <c r="T100">
+        <v>42.81470299779868</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.08536486273445822</v>
+      </c>
+      <c r="W100">
+        <v>0.2184148707790114</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3414594509378328</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2800569291134409</v>
+      </c>
+      <c r="C101">
+        <v>14.2225711977508</v>
+      </c>
+      <c r="D101">
+        <v>-5.5204288022492</v>
+      </c>
+      <c r="E101">
+        <v>43.857</v>
+      </c>
+      <c r="F101">
+        <v>43.857</v>
+      </c>
+      <c r="G101">
+        <v>63.6</v>
+      </c>
+      <c r="H101">
+        <v>44.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>7.04</v>
+      </c>
+      <c r="K101">
+        <v>3.5</v>
+      </c>
+      <c r="L101">
+        <v>3.54</v>
+      </c>
+      <c r="M101">
+        <v>10.4730516</v>
+      </c>
+      <c r="N101">
+        <v>-6.9330516</v>
+      </c>
+      <c r="O101">
+        <v>-1.7332629</v>
+      </c>
+      <c r="P101">
+        <v>-5.1997887</v>
+      </c>
+      <c r="Q101">
+        <v>-1.6997887</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.36223557500097</v>
+      </c>
+      <c r="T101">
+        <v>85.62940599559735</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.08450259139370611</v>
+      </c>
+      <c r="W101">
+        <v>0.218620781175183</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3380103655748244</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/philippines/philippines_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_furn_home_furnishings.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1100193302248852</v>
+        <v>0.109778031899323</v>
       </c>
       <c r="C2">
-        <v>40.16186110814241</v>
+        <v>39.65058425892909</v>
       </c>
       <c r="D2">
-        <v>-29.13813889185759</v>
+        <v>-29.2480357410709</v>
       </c>
       <c r="E2">
-        <v>-0.238</v>
+        <v>0.16338</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.40138</v>
       </c>
       <c r="G2">
         <v>69.3</v>
@@ -1451,28 +1451,28 @@
         <v>4.71</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.020189414</v>
       </c>
       <c r="N2">
-        <v>4.71</v>
+        <v>4.689810586</v>
       </c>
       <c r="O2">
-        <v>1.1775</v>
+        <v>1.1724526465</v>
       </c>
       <c r="P2">
-        <v>3.5325</v>
+        <v>3.5173579395</v>
       </c>
       <c r="Q2">
-        <v>6.8725</v>
+        <v>6.857357939500001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1100193302248852</v>
+        <v>0.1105058403023465</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460947</v>
+        <v>0.941548818067656</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>233.290574951804</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.109778031899323</v>
+        <v>0.1095367335737608</v>
       </c>
       <c r="C3">
-        <v>39.65058425892909</v>
+        <v>39.13847530162952</v>
       </c>
       <c r="D3">
-        <v>-29.2480357410709</v>
+        <v>-29.35876469837048</v>
       </c>
       <c r="E3">
-        <v>0.16338</v>
+        <v>0.56476</v>
       </c>
       <c r="F3">
-        <v>0.40138</v>
+        <v>0.80276</v>
       </c>
       <c r="G3">
         <v>69.3</v>
@@ -1533,28 +1533,28 @@
         <v>4.71</v>
       </c>
       <c r="M3">
-        <v>0.020189414</v>
+        <v>0.040378828</v>
       </c>
       <c r="N3">
-        <v>4.689810586</v>
+        <v>4.669621172</v>
       </c>
       <c r="O3">
-        <v>1.1724526465</v>
+        <v>1.167405293</v>
       </c>
       <c r="P3">
-        <v>3.5173579395</v>
+        <v>3.502215879</v>
       </c>
       <c r="Q3">
-        <v>6.857357939500001</v>
+        <v>6.842215879000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1105058403023465</v>
+        <v>0.1110022791568988</v>
       </c>
       <c r="T3">
-        <v>0.941548818067656</v>
+        <v>0.9487726082937391</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>233.290574951804</v>
+        <v>116.645287475902</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1095367335737608</v>
+        <v>0.1092954352481986</v>
       </c>
       <c r="C4">
-        <v>39.13847530162952</v>
+        <v>38.62552474959534</v>
       </c>
       <c r="D4">
-        <v>-29.35876469837048</v>
+        <v>-29.47033525040465</v>
       </c>
       <c r="E4">
-        <v>0.56476</v>
+        <v>0.96614</v>
       </c>
       <c r="F4">
-        <v>0.80276</v>
+        <v>1.20414</v>
       </c>
       <c r="G4">
         <v>69.3</v>
@@ -1615,28 +1615,28 @@
         <v>4.71</v>
       </c>
       <c r="M4">
-        <v>0.040378828</v>
+        <v>0.06056824199999999</v>
       </c>
       <c r="N4">
-        <v>4.669621172</v>
+        <v>4.649431758</v>
       </c>
       <c r="O4">
-        <v>1.167405293</v>
+        <v>1.1623579395</v>
       </c>
       <c r="P4">
-        <v>3.502215879</v>
+        <v>3.4870738185</v>
       </c>
       <c r="Q4">
-        <v>6.842215879000001</v>
+        <v>6.827073818500001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1110022791568988</v>
+        <v>0.1115089538641223</v>
       </c>
       <c r="T4">
-        <v>0.9487726082937391</v>
+        <v>0.9561453426481947</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>116.645287475902</v>
+        <v>77.76352498393466</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1092954352481986</v>
+        <v>0.1090541369226364</v>
       </c>
       <c r="C5">
-        <v>38.62552474959534</v>
+        <v>38.11172297142174</v>
       </c>
       <c r="D5">
-        <v>-29.47033525040465</v>
+        <v>-29.58275702857826</v>
       </c>
       <c r="E5">
-        <v>0.96614</v>
+        <v>1.36752</v>
       </c>
       <c r="F5">
-        <v>1.20414</v>
+        <v>1.60552</v>
       </c>
       <c r="G5">
         <v>69.3</v>
@@ -1697,28 +1697,28 @@
         <v>4.71</v>
       </c>
       <c r="M5">
-        <v>0.06056824199999999</v>
+        <v>0.080757656</v>
       </c>
       <c r="N5">
-        <v>4.649431758</v>
+        <v>4.629242344</v>
       </c>
       <c r="O5">
-        <v>1.1623579395</v>
+        <v>1.157310586</v>
       </c>
       <c r="P5">
-        <v>3.4870738185</v>
+        <v>3.471931758</v>
       </c>
       <c r="Q5">
-        <v>6.827073818500001</v>
+        <v>6.811931758</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1115089538641223</v>
+        <v>0.1120261842944129</v>
       </c>
       <c r="T5">
-        <v>0.9561453426481947</v>
+        <v>0.9636716756350352</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>77.76352498393466</v>
+        <v>58.32264373795098</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1090541369226364</v>
+        <v>0.1088128385970742</v>
       </c>
       <c r="C6">
-        <v>38.11172297142174</v>
+        <v>37.5970601881757</v>
       </c>
       <c r="D6">
-        <v>-29.58275702857826</v>
+        <v>-29.6960398118243</v>
       </c>
       <c r="E6">
-        <v>1.36752</v>
+        <v>1.7689</v>
       </c>
       <c r="F6">
-        <v>1.60552</v>
+        <v>2.0069</v>
       </c>
       <c r="G6">
         <v>69.3</v>
@@ -1779,28 +1779,28 @@
         <v>4.71</v>
       </c>
       <c r="M6">
-        <v>0.080757656</v>
+        <v>0.10094707</v>
       </c>
       <c r="N6">
-        <v>4.629242344</v>
+        <v>4.60905293</v>
       </c>
       <c r="O6">
-        <v>1.157310586</v>
+        <v>1.1522632325</v>
       </c>
       <c r="P6">
-        <v>3.471931758</v>
+        <v>3.4567896975</v>
       </c>
       <c r="Q6">
-        <v>6.811931758</v>
+        <v>6.7967896975</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1120261842944129</v>
+        <v>0.1125543037863939</v>
       </c>
       <c r="T6">
-        <v>0.9636716756350352</v>
+        <v>0.971356457737388</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>58.32264373795098</v>
+        <v>46.65811499036079</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1088128385970742</v>
+        <v>0.108571540271512</v>
       </c>
       <c r="C7">
-        <v>37.5970601881757</v>
+        <v>37.08152647056055</v>
       </c>
       <c r="D7">
-        <v>-29.6960398118243</v>
+        <v>-29.81019352943945</v>
       </c>
       <c r="E7">
-        <v>1.7689</v>
+        <v>2.17028</v>
       </c>
       <c r="F7">
-        <v>2.0069</v>
+        <v>2.40828</v>
       </c>
       <c r="G7">
         <v>69.3</v>
@@ -1861,28 +1861,28 @@
         <v>4.71</v>
       </c>
       <c r="M7">
-        <v>0.10094707</v>
+        <v>0.121136484</v>
       </c>
       <c r="N7">
-        <v>4.60905293</v>
+        <v>4.588863516</v>
       </c>
       <c r="O7">
-        <v>1.1522632325</v>
+        <v>1.147215879</v>
       </c>
       <c r="P7">
-        <v>3.4567896975</v>
+        <v>3.441647637</v>
       </c>
       <c r="Q7">
-        <v>6.7967896975</v>
+        <v>6.781647637000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1125543037863939</v>
+        <v>0.1130936598633106</v>
       </c>
       <c r="T7">
-        <v>0.971356457737388</v>
+        <v>0.9792047458419184</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.65811499036079</v>
+        <v>38.88176249196733</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.108571540271512</v>
+        <v>0.1083302419459497</v>
       </c>
       <c r="C8">
-        <v>37.08152647056055</v>
+        <v>36.56511173601471</v>
       </c>
       <c r="D8">
-        <v>-29.81019352943945</v>
+        <v>-29.92522826398529</v>
       </c>
       <c r="E8">
-        <v>2.17028</v>
+        <v>2.57166</v>
       </c>
       <c r="F8">
-        <v>2.40828</v>
+        <v>2.80966</v>
       </c>
       <c r="G8">
         <v>69.3</v>
@@ -1943,28 +1943,28 @@
         <v>4.71</v>
       </c>
       <c r="M8">
-        <v>0.121136484</v>
+        <v>0.141325898</v>
       </c>
       <c r="N8">
-        <v>4.588863516</v>
+        <v>4.568674102</v>
       </c>
       <c r="O8">
-        <v>1.147215879</v>
+        <v>1.1421685255</v>
       </c>
       <c r="P8">
-        <v>3.441647637</v>
+        <v>3.4265055765</v>
       </c>
       <c r="Q8">
-        <v>6.781647637000001</v>
+        <v>6.766505576500001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1130936598633106</v>
+        <v>0.1136446149956449</v>
       </c>
       <c r="T8">
-        <v>0.9792047458419184</v>
+        <v>0.9872218143357936</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.88176249196733</v>
+        <v>33.32722499311485</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1083302419459497</v>
+        <v>0.1080889436203875</v>
       </c>
       <c r="C9">
-        <v>36.56511173601471</v>
+        <v>36.0478057457431</v>
       </c>
       <c r="D9">
-        <v>-29.92522826398529</v>
+        <v>-30.0411542542569</v>
       </c>
       <c r="E9">
-        <v>2.57166</v>
+        <v>2.97304</v>
       </c>
       <c r="F9">
-        <v>2.80966</v>
+        <v>3.21104</v>
       </c>
       <c r="G9">
         <v>69.3</v>
@@ -2025,28 +2025,28 @@
         <v>4.71</v>
       </c>
       <c r="M9">
-        <v>0.141325898</v>
+        <v>0.161515312</v>
       </c>
       <c r="N9">
-        <v>4.568674102</v>
+        <v>4.548484688</v>
       </c>
       <c r="O9">
-        <v>1.1421685255</v>
+        <v>1.137121172</v>
       </c>
       <c r="P9">
-        <v>3.4265055765</v>
+        <v>3.411363516</v>
       </c>
       <c r="Q9">
-        <v>6.766505576500001</v>
+        <v>6.751363516000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1136446149956449</v>
+        <v>0.1142075474134647</v>
       </c>
       <c r="T9">
-        <v>0.9872218143357936</v>
+        <v>0.9954131669273618</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.32722499311485</v>
+        <v>29.1613218689755</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1080889436203875</v>
+        <v>0.1078476452948253</v>
       </c>
       <c r="C10">
-        <v>36.0478057457431</v>
+        <v>35.52959810167917</v>
       </c>
       <c r="D10">
-        <v>-30.0411542542569</v>
+        <v>-30.15798189832083</v>
       </c>
       <c r="E10">
-        <v>2.97304</v>
+        <v>3.37442</v>
       </c>
       <c r="F10">
-        <v>3.21104</v>
+        <v>3.61242</v>
       </c>
       <c r="G10">
         <v>69.3</v>
@@ -2107,28 +2107,28 @@
         <v>4.71</v>
       </c>
       <c r="M10">
-        <v>0.161515312</v>
+        <v>0.181704726</v>
       </c>
       <c r="N10">
-        <v>4.548484688</v>
+        <v>4.528295274</v>
       </c>
       <c r="O10">
-        <v>1.137121172</v>
+        <v>1.1320738185</v>
       </c>
       <c r="P10">
-        <v>3.411363516</v>
+        <v>3.3962214555</v>
       </c>
       <c r="Q10">
-        <v>6.751363516000001</v>
+        <v>6.736221455500001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1142075474134647</v>
+        <v>0.1147828519723355</v>
       </c>
       <c r="T10">
-        <v>0.9954131669273618</v>
+        <v>1.003784549246217</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.1613218689755</v>
+        <v>25.92117499464488</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1078476452948253</v>
+        <v>0.1076063469692631</v>
       </c>
       <c r="C11">
-        <v>35.52959810167917</v>
+        <v>35.01047824337596</v>
       </c>
       <c r="D11">
-        <v>-30.15798189832083</v>
+        <v>-30.27572175662404</v>
       </c>
       <c r="E11">
-        <v>3.37442</v>
+        <v>3.7758</v>
       </c>
       <c r="F11">
-        <v>3.61242</v>
+        <v>4.0138</v>
       </c>
       <c r="G11">
         <v>69.3</v>
@@ -2189,28 +2189,28 @@
         <v>4.71</v>
       </c>
       <c r="M11">
-        <v>0.181704726</v>
+        <v>0.20189414</v>
       </c>
       <c r="N11">
-        <v>4.528295274</v>
+        <v>4.50810586</v>
       </c>
       <c r="O11">
-        <v>1.1320738185</v>
+        <v>1.127026465</v>
       </c>
       <c r="P11">
-        <v>3.3962214555</v>
+        <v>3.381079395</v>
       </c>
       <c r="Q11">
-        <v>6.736221455500001</v>
+        <v>6.721079395</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1147828519723355</v>
+        <v>0.115370941076959</v>
       </c>
       <c r="T11">
-        <v>1.003784549246217</v>
+        <v>1.012341962283269</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.92117499464488</v>
+        <v>23.3290574951804</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1076063469692631</v>
+        <v>0.1073650486437009</v>
       </c>
       <c r="C12">
-        <v>35.01047824337596</v>
+        <v>34.49043544482381</v>
       </c>
       <c r="D12">
-        <v>-30.27572175662404</v>
+        <v>-30.39438455517619</v>
       </c>
       <c r="E12">
-        <v>3.7758</v>
+        <v>4.17718</v>
       </c>
       <c r="F12">
-        <v>4.0138</v>
+        <v>4.415179999999999</v>
       </c>
       <c r="G12">
         <v>69.3</v>
@@ -2271,28 +2271,28 @@
         <v>4.71</v>
       </c>
       <c r="M12">
-        <v>0.20189414</v>
+        <v>0.222083554</v>
       </c>
       <c r="N12">
-        <v>4.50810586</v>
+        <v>4.487916446</v>
       </c>
       <c r="O12">
-        <v>1.127026465</v>
+        <v>1.1219791115</v>
       </c>
       <c r="P12">
-        <v>3.381079395</v>
+        <v>3.3659373345</v>
       </c>
       <c r="Q12">
-        <v>6.721079395</v>
+        <v>6.705937334500001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.115370941076959</v>
+        <v>0.1159722456670797</v>
       </c>
       <c r="T12">
-        <v>1.012341962283269</v>
+        <v>1.021091676736885</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.3290574951804</v>
+        <v>21.20823408652764</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1073650486437009</v>
+        <v>0.1071237503181387</v>
       </c>
       <c r="C13">
-        <v>34.49043544482381</v>
+        <v>33.96945881119313</v>
       </c>
       <c r="D13">
-        <v>-30.39438455517619</v>
+        <v>-30.51398118880687</v>
       </c>
       <c r="E13">
-        <v>4.17718</v>
+        <v>4.57856</v>
       </c>
       <c r="F13">
-        <v>4.415179999999999</v>
+        <v>4.81656</v>
       </c>
       <c r="G13">
         <v>69.3</v>
@@ -2353,28 +2353,28 @@
         <v>4.71</v>
       </c>
       <c r="M13">
-        <v>0.222083554</v>
+        <v>0.242272968</v>
       </c>
       <c r="N13">
-        <v>4.487916446</v>
+        <v>4.467727032</v>
       </c>
       <c r="O13">
-        <v>1.1219791115</v>
+        <v>1.116931758</v>
       </c>
       <c r="P13">
-        <v>3.3659373345</v>
+        <v>3.350795274</v>
       </c>
       <c r="Q13">
-        <v>6.705937334500001</v>
+        <v>6.690795274000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1159722456670797</v>
+        <v>0.1165872162706121</v>
       </c>
       <c r="T13">
-        <v>1.021091676736885</v>
+        <v>1.030040248337173</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.20823408652764</v>
+        <v>19.44088124598366</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1071237503181387</v>
+        <v>0.1068824519925765</v>
       </c>
       <c r="C14">
-        <v>33.96945881119313</v>
+        <v>33.44753727549984</v>
       </c>
       <c r="D14">
-        <v>-30.51398118880687</v>
+        <v>-30.63452272450016</v>
       </c>
       <c r="E14">
-        <v>4.57856</v>
+        <v>4.979939999999999</v>
       </c>
       <c r="F14">
-        <v>4.81656</v>
+        <v>5.21794</v>
       </c>
       <c r="G14">
         <v>69.3</v>
@@ -2435,28 +2435,28 @@
         <v>4.71</v>
       </c>
       <c r="M14">
-        <v>0.242272968</v>
+        <v>0.2624623819999999</v>
       </c>
       <c r="N14">
-        <v>4.467727032</v>
+        <v>4.447537618</v>
       </c>
       <c r="O14">
-        <v>1.116931758</v>
+        <v>1.1118844045</v>
       </c>
       <c r="P14">
-        <v>3.350795274</v>
+        <v>3.3356532135</v>
       </c>
       <c r="Q14">
-        <v>6.690795274000001</v>
+        <v>6.6756532135</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1165872162706121</v>
+        <v>0.1172163241293982</v>
       </c>
       <c r="T14">
-        <v>1.030040248337173</v>
+        <v>1.039194534227122</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.44088124598366</v>
+        <v>17.94542884244646</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1068824519925765</v>
+        <v>0.1066411536670142</v>
       </c>
       <c r="C15">
-        <v>33.44753727549984</v>
+        <v>32.92465959519159</v>
       </c>
       <c r="D15">
-        <v>-30.63452272450016</v>
+        <v>-30.7560204048084</v>
       </c>
       <c r="E15">
-        <v>4.979939999999999</v>
+        <v>5.381320000000001</v>
       </c>
       <c r="F15">
-        <v>5.21794</v>
+        <v>5.61932</v>
       </c>
       <c r="G15">
         <v>69.3</v>
@@ -2517,28 +2517,28 @@
         <v>4.71</v>
       </c>
       <c r="M15">
-        <v>0.2624623819999999</v>
+        <v>0.282651796</v>
       </c>
       <c r="N15">
-        <v>4.447537618</v>
+        <v>4.427348204</v>
       </c>
       <c r="O15">
-        <v>1.1118844045</v>
+        <v>1.106837051</v>
       </c>
       <c r="P15">
-        <v>3.3356532135</v>
+        <v>3.320511153</v>
       </c>
       <c r="Q15">
-        <v>6.6756532135</v>
+        <v>6.660511153000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1172163241293982</v>
+        <v>0.1178600624035049</v>
       </c>
       <c r="T15">
-        <v>1.039194534227122</v>
+        <v>1.048561710486606</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.94542884244646</v>
+        <v>16.66361249655743</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1066411536670142</v>
+        <v>0.106399855341452</v>
       </c>
       <c r="C16">
-        <v>32.92465959519159</v>
+        <v>32.40081434865228</v>
       </c>
       <c r="D16">
-        <v>-30.7560204048084</v>
+        <v>-30.87848565134771</v>
       </c>
       <c r="E16">
-        <v>5.381320000000001</v>
+        <v>5.7827</v>
       </c>
       <c r="F16">
-        <v>5.61932</v>
+        <v>6.020700000000001</v>
       </c>
       <c r="G16">
         <v>69.3</v>
@@ -2599,28 +2599,28 @@
         <v>4.71</v>
       </c>
       <c r="M16">
-        <v>0.282651796</v>
+        <v>0.30284121</v>
       </c>
       <c r="N16">
-        <v>4.427348204</v>
+        <v>4.40715879</v>
       </c>
       <c r="O16">
-        <v>1.106837051</v>
+        <v>1.1017896975</v>
       </c>
       <c r="P16">
-        <v>3.320511153</v>
+        <v>3.305369092499999</v>
       </c>
       <c r="Q16">
-        <v>6.660511153000001</v>
+        <v>6.6453690925</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1178600624035049</v>
+        <v>0.1185189474605318</v>
       </c>
       <c r="T16">
-        <v>1.048561710486606</v>
+        <v>1.058149290893372</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.66361249655743</v>
+        <v>15.55270499678693</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.106399855341452</v>
+        <v>0.1061585570158898</v>
       </c>
       <c r="C17">
-        <v>32.40081434865228</v>
+        <v>31.8759899316228</v>
       </c>
       <c r="D17">
-        <v>-30.87848565134771</v>
+        <v>-31.00193006837719</v>
       </c>
       <c r="E17">
-        <v>5.7827</v>
+        <v>6.18408</v>
       </c>
       <c r="F17">
-        <v>6.0207</v>
+        <v>6.42208</v>
       </c>
       <c r="G17">
         <v>69.3</v>
@@ -2681,28 +2681,28 @@
         <v>4.71</v>
       </c>
       <c r="M17">
-        <v>0.30284121</v>
+        <v>0.323030624</v>
       </c>
       <c r="N17">
-        <v>4.40715879</v>
+        <v>4.386969376</v>
       </c>
       <c r="O17">
-        <v>1.1017896975</v>
+        <v>1.096742344</v>
       </c>
       <c r="P17">
-        <v>3.3053690925</v>
+        <v>3.290227032</v>
       </c>
       <c r="Q17">
-        <v>6.645369092500001</v>
+        <v>6.630227032000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1185189474605318</v>
+        <v>0.1191935202570117</v>
       </c>
       <c r="T17">
-        <v>1.058149290893372</v>
+        <v>1.067965147024108</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.55270499678693</v>
+        <v>14.58066093448775</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1061585570158898</v>
+        <v>0.1059172586903276</v>
       </c>
       <c r="C18">
-        <v>31.8759899316228</v>
+        <v>31.35017455353563</v>
       </c>
       <c r="D18">
-        <v>-31.00193006837719</v>
+        <v>-31.12636544646437</v>
       </c>
       <c r="E18">
-        <v>6.18408</v>
+        <v>6.585459999999999</v>
       </c>
       <c r="F18">
-        <v>6.42208</v>
+        <v>6.82346</v>
       </c>
       <c r="G18">
         <v>69.3</v>
@@ -2763,28 +2763,28 @@
         <v>4.71</v>
       </c>
       <c r="M18">
-        <v>0.323030624</v>
+        <v>0.3432200379999999</v>
       </c>
       <c r="N18">
-        <v>4.386969376</v>
+        <v>4.366779962</v>
       </c>
       <c r="O18">
-        <v>1.096742344</v>
+        <v>1.0916949905</v>
       </c>
       <c r="P18">
-        <v>3.290227032</v>
+        <v>3.2750849715</v>
       </c>
       <c r="Q18">
-        <v>6.630227032000001</v>
+        <v>6.615084971500001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1191935202570117</v>
+        <v>0.1198843478196718</v>
       </c>
       <c r="T18">
-        <v>1.067965147024108</v>
+        <v>1.078017529808597</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.58066093448775</v>
+        <v>13.72297499716494</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1059172586903276</v>
+        <v>0.1056759603647654</v>
       </c>
       <c r="C19">
-        <v>31.35017455353563</v>
+        <v>30.82335623376065</v>
       </c>
       <c r="D19">
-        <v>-31.12636544646437</v>
+        <v>-31.25180376623935</v>
       </c>
       <c r="E19">
-        <v>6.585459999999999</v>
+        <v>6.986840000000001</v>
       </c>
       <c r="F19">
-        <v>6.82346</v>
+        <v>7.22484</v>
       </c>
       <c r="G19">
         <v>69.3</v>
@@ -2845,28 +2845,28 @@
         <v>4.71</v>
       </c>
       <c r="M19">
-        <v>0.3432200379999999</v>
+        <v>0.363409452</v>
       </c>
       <c r="N19">
-        <v>4.366779962</v>
+        <v>4.346590548</v>
       </c>
       <c r="O19">
-        <v>1.0916949905</v>
+        <v>1.086647637</v>
       </c>
       <c r="P19">
-        <v>3.2750849715</v>
+        <v>3.259942911</v>
       </c>
       <c r="Q19">
-        <v>6.615084971500001</v>
+        <v>6.599942911000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1198843478196718</v>
+        <v>0.1205920248350797</v>
       </c>
       <c r="T19">
-        <v>1.078017529808597</v>
+        <v>1.088315092661001</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.72297499716494</v>
+        <v>12.96058749732244</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1056759603647654</v>
+        <v>0.1056484120392032</v>
       </c>
       <c r="C20">
-        <v>30.82335623376065</v>
+        <v>30.40759097548521</v>
       </c>
       <c r="D20">
-        <v>-31.25180376623934</v>
+        <v>-31.26618902451479</v>
       </c>
       <c r="E20">
-        <v>6.986839999999999</v>
+        <v>7.38822</v>
       </c>
       <c r="F20">
-        <v>7.224839999999999</v>
+        <v>7.62622</v>
       </c>
       <c r="G20">
         <v>69.3</v>
@@ -2927,45 +2927,45 @@
         <v>4.71</v>
       </c>
       <c r="M20">
-        <v>0.363409452</v>
+        <v>0.395038196</v>
       </c>
       <c r="N20">
-        <v>4.346590548</v>
+        <v>4.314961804</v>
       </c>
       <c r="O20">
-        <v>1.086647637</v>
+        <v>1.078740451</v>
       </c>
       <c r="P20">
-        <v>3.259942911</v>
+        <v>3.236221353</v>
       </c>
       <c r="Q20">
-        <v>6.599942911000001</v>
+        <v>6.576221353000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1205920248350797</v>
+        <v>0.121317175357041</v>
       </c>
       <c r="T20">
-        <v>1.088315092661001</v>
+        <v>1.098866916324574</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>12.96058749732244</v>
+        <v>11.92289770379571</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1056484120392032</v>
+        <v>0.105418363713641</v>
       </c>
       <c r="C21">
-        <v>30.40759097548521</v>
+        <v>29.88556468491694</v>
       </c>
       <c r="D21">
-        <v>-31.26618902451479</v>
+        <v>-31.38683531508306</v>
       </c>
       <c r="E21">
-        <v>7.38822</v>
+        <v>7.7896</v>
       </c>
       <c r="F21">
-        <v>7.62622</v>
+        <v>8.0276</v>
       </c>
       <c r="G21">
         <v>69.3</v>
@@ -3009,28 +3009,28 @@
         <v>4.71</v>
       </c>
       <c r="M21">
-        <v>0.395038196</v>
+        <v>0.41582968</v>
       </c>
       <c r="N21">
-        <v>4.314961804</v>
+        <v>4.29417032</v>
       </c>
       <c r="O21">
-        <v>1.078740451</v>
+        <v>1.07354258</v>
       </c>
       <c r="P21">
-        <v>3.236221353</v>
+        <v>3.22062774</v>
       </c>
       <c r="Q21">
-        <v>6.576221353000001</v>
+        <v>6.560627740000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.121317175357041</v>
+        <v>0.1220604546420512</v>
       </c>
       <c r="T21">
-        <v>1.098866916324574</v>
+        <v>1.109682535579738</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.92289770379571</v>
+        <v>11.32675281860593</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.105418363713641</v>
+        <v>0.1051883153880788</v>
       </c>
       <c r="C22">
-        <v>29.88556468491694</v>
+        <v>29.36260371630807</v>
       </c>
       <c r="D22">
-        <v>-31.38683531508306</v>
+        <v>-31.50841628369193</v>
       </c>
       <c r="E22">
-        <v>7.7896</v>
+        <v>8.190980000000001</v>
       </c>
       <c r="F22">
-        <v>8.0276</v>
+        <v>8.428980000000001</v>
       </c>
       <c r="G22">
         <v>69.3</v>
@@ -3091,28 +3091,28 @@
         <v>4.71</v>
       </c>
       <c r="M22">
-        <v>0.41582968</v>
+        <v>0.4366211640000001</v>
       </c>
       <c r="N22">
-        <v>4.29417032</v>
+        <v>4.273378836</v>
       </c>
       <c r="O22">
-        <v>1.07354258</v>
+        <v>1.068344709</v>
       </c>
       <c r="P22">
-        <v>3.22062774</v>
+        <v>3.205034127</v>
       </c>
       <c r="Q22">
-        <v>6.560627740000001</v>
+        <v>6.545034127000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1220604546420512</v>
+        <v>0.1228225511241503</v>
       </c>
       <c r="T22">
-        <v>1.109682535579738</v>
+        <v>1.120771967980601</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.32675281860593</v>
+        <v>10.78738363676755</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1051883153880788</v>
+        <v>0.1049582670625166</v>
       </c>
       <c r="C23">
-        <v>29.36260371630807</v>
+        <v>28.83869716563137</v>
       </c>
       <c r="D23">
-        <v>-31.50841628369193</v>
+        <v>-31.63094283436862</v>
       </c>
       <c r="E23">
-        <v>8.19098</v>
+        <v>8.592359999999999</v>
       </c>
       <c r="F23">
-        <v>8.428979999999999</v>
+        <v>8.830359999999999</v>
       </c>
       <c r="G23">
         <v>69.3</v>
@@ -3173,28 +3173,28 @@
         <v>4.71</v>
       </c>
       <c r="M23">
-        <v>0.436621164</v>
+        <v>0.4574126479999999</v>
       </c>
       <c r="N23">
-        <v>4.273378836</v>
+        <v>4.252587352</v>
       </c>
       <c r="O23">
-        <v>1.068344709</v>
+        <v>1.063146838</v>
       </c>
       <c r="P23">
-        <v>3.205034127</v>
+        <v>3.189440514</v>
       </c>
       <c r="Q23">
-        <v>6.545034127000001</v>
+        <v>6.529440514000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1228225511241503</v>
+        <v>0.1236041885416879</v>
       </c>
       <c r="T23">
-        <v>1.120771967980601</v>
+        <v>1.132145744801999</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.78738363676755</v>
+        <v>10.29704801691448</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1049582670625166</v>
+        <v>0.1047282187369543</v>
       </c>
       <c r="C24">
-        <v>28.83869716563137</v>
+        <v>28.31383395858786</v>
       </c>
       <c r="D24">
-        <v>-31.63094283436862</v>
+        <v>-31.75442604141214</v>
       </c>
       <c r="E24">
-        <v>8.592359999999999</v>
+        <v>8.993740000000001</v>
       </c>
       <c r="F24">
-        <v>8.830359999999999</v>
+        <v>9.23174</v>
       </c>
       <c r="G24">
         <v>69.3</v>
@@ -3255,28 +3255,28 @@
         <v>4.71</v>
       </c>
       <c r="M24">
-        <v>0.4574126479999999</v>
+        <v>0.478204132</v>
       </c>
       <c r="N24">
-        <v>4.252587352</v>
+        <v>4.231795868</v>
       </c>
       <c r="O24">
-        <v>1.063146838</v>
+        <v>1.057948967</v>
       </c>
       <c r="P24">
-        <v>3.189440514</v>
+        <v>3.173846901</v>
       </c>
       <c r="Q24">
-        <v>6.529440514000001</v>
+        <v>6.513846901000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1236041885416879</v>
+        <v>0.1244061282298108</v>
       </c>
       <c r="T24">
-        <v>1.132145744801999</v>
+        <v>1.143814944397979</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.29704801691448</v>
+        <v>9.849350277048631</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1047282187369543</v>
+        <v>0.1048041704113921</v>
       </c>
       <c r="C25">
-        <v>28.31383395858786</v>
+        <v>27.95332906642924</v>
       </c>
       <c r="D25">
-        <v>-31.75442604141214</v>
+        <v>-31.71355093357076</v>
       </c>
       <c r="E25">
-        <v>8.993740000000001</v>
+        <v>9.39512</v>
       </c>
       <c r="F25">
-        <v>9.23174</v>
+        <v>9.63312</v>
       </c>
       <c r="G25">
         <v>69.3</v>
@@ -3337,45 +3337,45 @@
         <v>4.71</v>
       </c>
       <c r="M25">
-        <v>0.478204132</v>
+        <v>0.51537192</v>
       </c>
       <c r="N25">
-        <v>4.231795868</v>
+        <v>4.19462808</v>
       </c>
       <c r="O25">
-        <v>1.057948967</v>
+        <v>1.04865702</v>
       </c>
       <c r="P25">
-        <v>3.173846901</v>
+        <v>3.14597106</v>
       </c>
       <c r="Q25">
-        <v>6.513846901000001</v>
+        <v>6.485971060000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1244061282298108</v>
+        <v>0.125229171593937</v>
       </c>
       <c r="T25">
-        <v>1.143814944397979</v>
+        <v>1.155791228193854</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.849350277048631</v>
+        <v>9.139031090401666</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1048041704113921</v>
+        <v>0.1045868720858299</v>
       </c>
       <c r="C26">
-        <v>27.95332906642924</v>
+        <v>27.43472388891961</v>
       </c>
       <c r="D26">
-        <v>-31.71355093357076</v>
+        <v>-31.83077611108038</v>
       </c>
       <c r="E26">
-        <v>9.39512</v>
+        <v>9.7965</v>
       </c>
       <c r="F26">
-        <v>9.63312</v>
+        <v>10.0345</v>
       </c>
       <c r="G26">
         <v>69.3</v>
@@ -3419,28 +3419,28 @@
         <v>4.71</v>
       </c>
       <c r="M26">
-        <v>0.51537192</v>
+        <v>0.53684575</v>
       </c>
       <c r="N26">
-        <v>4.19462808</v>
+        <v>4.17315425</v>
       </c>
       <c r="O26">
-        <v>1.04865702</v>
+        <v>1.0432885625</v>
       </c>
       <c r="P26">
-        <v>3.14597106</v>
+        <v>3.1298656875</v>
       </c>
       <c r="Q26">
-        <v>6.485971060000001</v>
+        <v>6.4698656875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.125229171593937</v>
+        <v>0.1260741627811066</v>
       </c>
       <c r="T26">
-        <v>1.155791228193854</v>
+        <v>1.168086879557618</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.139031090401666</v>
+        <v>8.773469846785598</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1045868720858299</v>
+        <v>0.1043695737602677</v>
       </c>
       <c r="C27">
-        <v>27.43472388891961</v>
+        <v>26.91524887974992</v>
       </c>
       <c r="D27">
-        <v>-31.83077611108038</v>
+        <v>-31.94887112025008</v>
       </c>
       <c r="E27">
-        <v>9.7965</v>
+        <v>10.19788</v>
       </c>
       <c r="F27">
-        <v>10.0345</v>
+        <v>10.43588</v>
       </c>
       <c r="G27">
         <v>69.3</v>
@@ -3501,28 +3501,28 @@
         <v>4.71</v>
       </c>
       <c r="M27">
-        <v>0.53684575</v>
+        <v>0.5583195799999999</v>
       </c>
       <c r="N27">
-        <v>4.17315425</v>
+        <v>4.15168042</v>
       </c>
       <c r="O27">
-        <v>1.0432885625</v>
+        <v>1.037920105</v>
       </c>
       <c r="P27">
-        <v>3.1298656875</v>
+        <v>3.113760315</v>
       </c>
       <c r="Q27">
-        <v>6.4698656875</v>
+        <v>6.453760315</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1260741627811066</v>
+        <v>0.1269419915679293</v>
       </c>
       <c r="T27">
-        <v>1.168086879557618</v>
+        <v>1.180714845823106</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.773469846785598</v>
+        <v>8.436028698832308</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1043695737602677</v>
+        <v>0.1041522754347055</v>
       </c>
       <c r="C28">
-        <v>26.91524887974992</v>
+        <v>26.39489432140898</v>
       </c>
       <c r="D28">
-        <v>-31.94887112025008</v>
+        <v>-32.06784567859102</v>
       </c>
       <c r="E28">
-        <v>10.19788</v>
+        <v>10.59926</v>
       </c>
       <c r="F28">
-        <v>10.43588</v>
+        <v>10.83726</v>
       </c>
       <c r="G28">
         <v>69.3</v>
@@ -3583,28 +3583,28 @@
         <v>4.71</v>
       </c>
       <c r="M28">
-        <v>0.5583195799999999</v>
+        <v>0.5797934100000001</v>
       </c>
       <c r="N28">
-        <v>4.15168042</v>
+        <v>4.13020659</v>
       </c>
       <c r="O28">
-        <v>1.037920105</v>
+        <v>1.0325516475</v>
       </c>
       <c r="P28">
-        <v>3.113760315</v>
+        <v>3.0976549425</v>
       </c>
       <c r="Q28">
-        <v>6.453760315</v>
+        <v>6.437654942500001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1269419915679293</v>
+        <v>0.1278335964858979</v>
       </c>
       <c r="T28">
-        <v>1.180714845823106</v>
+        <v>1.193688783767101</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.436028698832308</v>
+        <v>8.123583191468146</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1041522754347055</v>
+        <v>0.1039349771091433</v>
       </c>
       <c r="C29">
-        <v>26.39489432140898</v>
+        <v>25.87365035109618</v>
       </c>
       <c r="D29">
-        <v>-32.06784567859102</v>
+        <v>-32.18770964890382</v>
       </c>
       <c r="E29">
-        <v>10.59926</v>
+        <v>11.00064</v>
       </c>
       <c r="F29">
-        <v>10.83726</v>
+        <v>11.23864</v>
       </c>
       <c r="G29">
         <v>69.3</v>
@@ -3665,28 +3665,28 @@
         <v>4.71</v>
       </c>
       <c r="M29">
-        <v>0.5797934100000001</v>
+        <v>0.60126724</v>
       </c>
       <c r="N29">
-        <v>4.13020659</v>
+        <v>4.10873276</v>
       </c>
       <c r="O29">
-        <v>1.0325516475</v>
+        <v>1.02718319</v>
       </c>
       <c r="P29">
-        <v>3.0976549425</v>
+        <v>3.08154957</v>
       </c>
       <c r="Q29">
-        <v>6.437654942500001</v>
+        <v>6.421549570000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1278335964858979</v>
+        <v>0.1287499682071434</v>
       </c>
       <c r="T29">
-        <v>1.193688783767101</v>
+        <v>1.207023108876206</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.123583191468146</v>
+        <v>7.833455220344285</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1039349771091433</v>
+        <v>0.103891678783581</v>
       </c>
       <c r="C30">
-        <v>25.87365035109618</v>
+        <v>25.44827941193478</v>
       </c>
       <c r="D30">
-        <v>-32.18770964890382</v>
+        <v>-32.21170058806522</v>
       </c>
       <c r="E30">
-        <v>11.00064</v>
+        <v>11.40202</v>
       </c>
       <c r="F30">
-        <v>11.23864</v>
+        <v>11.64002</v>
       </c>
       <c r="G30">
         <v>69.3</v>
@@ -3747,45 +3747,45 @@
         <v>4.71</v>
       </c>
       <c r="M30">
-        <v>0.60126724</v>
+        <v>0.6320530860000001</v>
       </c>
       <c r="N30">
-        <v>4.10873276</v>
+        <v>4.077946914</v>
       </c>
       <c r="O30">
-        <v>1.02718319</v>
+        <v>1.0194867285</v>
       </c>
       <c r="P30">
-        <v>3.08154957</v>
+        <v>3.0584601855</v>
       </c>
       <c r="Q30">
-        <v>6.421549570000001</v>
+        <v>6.398460185500001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1287499682071434</v>
+        <v>0.1296921532163113</v>
       </c>
       <c r="T30">
-        <v>1.207023108876206</v>
+        <v>1.220733048777117</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.833455220344285</v>
+        <v>7.451905709072038</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.103891678783581</v>
+        <v>0.1036803804580188</v>
       </c>
       <c r="C31">
-        <v>25.44827941193477</v>
+        <v>24.92930726164291</v>
       </c>
       <c r="D31">
-        <v>-32.21170058806523</v>
+        <v>-32.32929273835708</v>
       </c>
       <c r="E31">
-        <v>11.40202</v>
+        <v>11.8034</v>
       </c>
       <c r="F31">
-        <v>11.64002</v>
+        <v>12.0414</v>
       </c>
       <c r="G31">
         <v>69.3</v>
@@ -3829,28 +3829,28 @@
         <v>4.71</v>
       </c>
       <c r="M31">
-        <v>0.6320530859999999</v>
+        <v>0.65384802</v>
       </c>
       <c r="N31">
-        <v>4.077946914</v>
+        <v>4.05615198</v>
       </c>
       <c r="O31">
-        <v>1.0194867285</v>
+        <v>1.014037995</v>
       </c>
       <c r="P31">
-        <v>3.0584601855</v>
+        <v>3.042113985</v>
       </c>
       <c r="Q31">
-        <v>6.398460185500001</v>
+        <v>6.382113985000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1296921532163113</v>
+        <v>0.1306612577971698</v>
       </c>
       <c r="T31">
-        <v>1.220733048777117</v>
+        <v>1.234834701246625</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.451905709072039</v>
+        <v>7.203508852102971</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1036803804580188</v>
+        <v>0.1034690821324566</v>
       </c>
       <c r="C32">
-        <v>24.92930726164291</v>
+        <v>24.40947340093233</v>
       </c>
       <c r="D32">
-        <v>-32.32929273835708</v>
+        <v>-32.44774659906767</v>
       </c>
       <c r="E32">
-        <v>11.8034</v>
+        <v>12.20478</v>
       </c>
       <c r="F32">
-        <v>12.0414</v>
+        <v>12.44278</v>
       </c>
       <c r="G32">
         <v>69.3</v>
@@ -3911,28 +3911,28 @@
         <v>4.71</v>
       </c>
       <c r="M32">
-        <v>0.65384802</v>
+        <v>0.675642954</v>
       </c>
       <c r="N32">
-        <v>4.05615198</v>
+        <v>4.034357046</v>
       </c>
       <c r="O32">
-        <v>1.014037995</v>
+        <v>1.0085892615</v>
       </c>
       <c r="P32">
-        <v>3.042113985</v>
+        <v>3.0257677845</v>
       </c>
       <c r="Q32">
-        <v>6.382113985000001</v>
+        <v>6.365767784500001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1306612577971698</v>
+        <v>0.1316584523658792</v>
       </c>
       <c r="T32">
-        <v>1.234834701246625</v>
+        <v>1.249345097265974</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.203508852102971</v>
+        <v>6.971137598809327</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1034690821324566</v>
+        <v>0.1032577838068944</v>
       </c>
       <c r="C33">
-        <v>24.40947340093233</v>
+        <v>23.88876832310314</v>
       </c>
       <c r="D33">
-        <v>-32.44774659906767</v>
+        <v>-32.56707167689685</v>
       </c>
       <c r="E33">
-        <v>12.20478</v>
+        <v>12.60616</v>
       </c>
       <c r="F33">
-        <v>12.44278</v>
+        <v>12.84416</v>
       </c>
       <c r="G33">
         <v>69.3</v>
@@ -3993,28 +3993,28 @@
         <v>4.71</v>
       </c>
       <c r="M33">
-        <v>0.675642954</v>
+        <v>0.6974378880000001</v>
       </c>
       <c r="N33">
-        <v>4.034357046</v>
+        <v>4.012562111999999</v>
       </c>
       <c r="O33">
-        <v>1.0085892615</v>
+        <v>1.003140528</v>
       </c>
       <c r="P33">
-        <v>3.0257677845</v>
+        <v>3.009421584</v>
       </c>
       <c r="Q33">
-        <v>6.365767784500001</v>
+        <v>6.349421584</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1316584523658792</v>
+        <v>0.1326849761866094</v>
       </c>
       <c r="T33">
-        <v>1.249345097265974</v>
+        <v>1.264282269638834</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.971137598809327</v>
+        <v>6.753289548846533</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1032577838068944</v>
+        <v>0.1030464854813322</v>
       </c>
       <c r="C34">
-        <v>23.88876832310314</v>
+        <v>23.36718238109756</v>
       </c>
       <c r="D34">
-        <v>-32.56707167689685</v>
+        <v>-32.68727761890243</v>
       </c>
       <c r="E34">
-        <v>12.60616</v>
+        <v>13.00754</v>
       </c>
       <c r="F34">
-        <v>12.84416</v>
+        <v>13.24554</v>
       </c>
       <c r="G34">
         <v>69.3</v>
@@ -4075,28 +4075,28 @@
         <v>4.71</v>
       </c>
       <c r="M34">
-        <v>0.6974378880000001</v>
+        <v>0.719232822</v>
       </c>
       <c r="N34">
-        <v>4.012562111999999</v>
+        <v>3.990767178</v>
       </c>
       <c r="O34">
-        <v>1.003140528</v>
+        <v>0.9976917945</v>
       </c>
       <c r="P34">
-        <v>3.009421584</v>
+        <v>2.9930753835</v>
       </c>
       <c r="Q34">
-        <v>6.349421584</v>
+        <v>6.333075383500001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1326849761866094</v>
+        <v>0.1337421425094511</v>
       </c>
       <c r="T34">
-        <v>1.264282269638834</v>
+        <v>1.279665327754167</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.753289548846533</v>
+        <v>6.5486444110027</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1030464854813322</v>
+        <v>0.10283518715577</v>
       </c>
       <c r="C35">
-        <v>23.36718238109756</v>
+        <v>22.84470578489988</v>
       </c>
       <c r="D35">
-        <v>-32.68727761890243</v>
+        <v>-32.80837421510012</v>
       </c>
       <c r="E35">
-        <v>13.00754</v>
+        <v>13.40892</v>
       </c>
       <c r="F35">
-        <v>13.24554</v>
+        <v>13.64692</v>
       </c>
       <c r="G35">
         <v>69.3</v>
@@ -4157,28 +4157,28 @@
         <v>4.71</v>
       </c>
       <c r="M35">
-        <v>0.719232822</v>
+        <v>0.741027756</v>
       </c>
       <c r="N35">
-        <v>3.990767178</v>
+        <v>3.968972244</v>
       </c>
       <c r="O35">
-        <v>0.9976917945</v>
+        <v>0.9922430609999999</v>
       </c>
       <c r="P35">
-        <v>2.9930753835</v>
+        <v>2.976729183</v>
       </c>
       <c r="Q35">
-        <v>6.333075383500001</v>
+        <v>6.316729183000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1337421425094511</v>
+        <v>0.1348313441754091</v>
       </c>
       <c r="T35">
-        <v>1.279665327754167</v>
+        <v>1.295514539145722</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.5486444110027</v>
+        <v>6.356037222443796</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.10283518715577</v>
+        <v>0.1026238888302078</v>
       </c>
       <c r="C36">
-        <v>22.84470578489988</v>
+        <v>22.32132859887864</v>
       </c>
       <c r="D36">
-        <v>-32.80837421510012</v>
+        <v>-32.93037140112136</v>
       </c>
       <c r="E36">
-        <v>13.40892</v>
+        <v>13.8103</v>
       </c>
       <c r="F36">
-        <v>13.64692</v>
+        <v>14.0483</v>
       </c>
       <c r="G36">
         <v>69.3</v>
@@ -4239,28 +4239,28 @@
         <v>4.71</v>
       </c>
       <c r="M36">
-        <v>0.741027756</v>
+        <v>0.76282269</v>
       </c>
       <c r="N36">
-        <v>3.968972244</v>
+        <v>3.94717731</v>
       </c>
       <c r="O36">
-        <v>0.9922430609999999</v>
+        <v>0.9867943275</v>
       </c>
       <c r="P36">
-        <v>2.976729183</v>
+        <v>2.9603829825</v>
       </c>
       <c r="Q36">
-        <v>6.316729183000001</v>
+        <v>6.3003829825</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1348313441754091</v>
+        <v>0.1359540597387812</v>
       </c>
       <c r="T36">
-        <v>1.295514539145722</v>
+        <v>1.311851418580095</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.356037222443796</v>
+        <v>6.174436158945403</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1026238888302078</v>
+        <v>0.1026825905046455</v>
       </c>
       <c r="C37">
-        <v>22.32132859887864</v>
+        <v>21.95393207121971</v>
       </c>
       <c r="D37">
-        <v>-32.93037140112136</v>
+        <v>-32.89638792878029</v>
       </c>
       <c r="E37">
-        <v>13.8103</v>
+        <v>14.21168</v>
       </c>
       <c r="F37">
-        <v>14.0483</v>
+        <v>14.44968</v>
       </c>
       <c r="G37">
         <v>69.3</v>
@@ -4321,45 +4321,45 @@
         <v>4.71</v>
       </c>
       <c r="M37">
-        <v>0.76282269</v>
+        <v>0.799067304</v>
       </c>
       <c r="N37">
-        <v>3.94717731</v>
+        <v>3.910932696</v>
       </c>
       <c r="O37">
-        <v>0.9867943275</v>
+        <v>0.9777331739999999</v>
       </c>
       <c r="P37">
-        <v>2.9603829825</v>
+        <v>2.933199522</v>
       </c>
       <c r="Q37">
-        <v>6.3003829825</v>
+        <v>6.273199522000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1359540597387812</v>
+        <v>0.1371118601635087</v>
       </c>
       <c r="T37">
-        <v>1.311851418580095</v>
+        <v>1.328698825496791</v>
       </c>
       <c r="U37">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>6.174436158945403</v>
+        <v>5.894372071567077</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1026825905046456</v>
+        <v>0.1024787921790833</v>
       </c>
       <c r="C38">
-        <v>21.95393207121972</v>
+        <v>21.43426746212383</v>
       </c>
       <c r="D38">
-        <v>-32.89638792878028</v>
+        <v>-33.01467253787617</v>
       </c>
       <c r="E38">
-        <v>14.21168</v>
+        <v>14.61306</v>
       </c>
       <c r="F38">
-        <v>14.44968</v>
+        <v>14.85106</v>
       </c>
       <c r="G38">
         <v>69.3</v>
@@ -4403,28 +4403,28 @@
         <v>4.71</v>
       </c>
       <c r="M38">
-        <v>0.7990673039999999</v>
+        <v>0.8212636179999999</v>
       </c>
       <c r="N38">
-        <v>3.910932696</v>
+        <v>3.888736382</v>
       </c>
       <c r="O38">
-        <v>0.977733174</v>
+        <v>0.9721840955000001</v>
       </c>
       <c r="P38">
-        <v>2.933199522</v>
+        <v>2.9165522865</v>
       </c>
       <c r="Q38">
-        <v>6.273199522000001</v>
+        <v>6.256552286500001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1371118601635087</v>
+        <v>0.1383064161572752</v>
       </c>
       <c r="T38">
-        <v>1.328698825496791</v>
+        <v>1.346081070728303</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.894372071567078</v>
+        <v>5.735064718281482</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1024787921790833</v>
+        <v>0.1022749938535211</v>
       </c>
       <c r="C39">
-        <v>21.43426746212383</v>
+        <v>20.91374915819316</v>
       </c>
       <c r="D39">
-        <v>-33.01467253787617</v>
+        <v>-33.13381084180684</v>
       </c>
       <c r="E39">
-        <v>14.61306</v>
+        <v>15.01444</v>
       </c>
       <c r="F39">
-        <v>14.85106</v>
+        <v>15.25244</v>
       </c>
       <c r="G39">
         <v>69.3</v>
@@ -4485,28 +4485,28 @@
         <v>4.71</v>
       </c>
       <c r="M39">
-        <v>0.8212636179999999</v>
+        <v>0.843459932</v>
       </c>
       <c r="N39">
-        <v>3.888736382</v>
+        <v>3.866540068</v>
       </c>
       <c r="O39">
-        <v>0.9721840955000001</v>
+        <v>0.966635017</v>
       </c>
       <c r="P39">
-        <v>2.9165522865</v>
+        <v>2.899905051</v>
       </c>
       <c r="Q39">
-        <v>6.256552286500001</v>
+        <v>6.239905051000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1383064161572752</v>
+        <v>0.1395395062153567</v>
       </c>
       <c r="T39">
-        <v>1.346081070728303</v>
+        <v>1.364024033547929</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.735064718281482</v>
+        <v>5.584141962537232</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1022749938535211</v>
+        <v>0.1020711955279589</v>
       </c>
       <c r="C40">
-        <v>20.91374915819316</v>
+        <v>20.39236788390532</v>
       </c>
       <c r="D40">
-        <v>-33.13381084180684</v>
+        <v>-33.25381211609468</v>
       </c>
       <c r="E40">
-        <v>15.01444</v>
+        <v>15.41582</v>
       </c>
       <c r="F40">
-        <v>15.25244</v>
+        <v>15.65382</v>
       </c>
       <c r="G40">
         <v>69.3</v>
@@ -4567,28 +4567,28 @@
         <v>4.71</v>
       </c>
       <c r="M40">
-        <v>0.843459932</v>
+        <v>0.865656246</v>
       </c>
       <c r="N40">
-        <v>3.866540068</v>
+        <v>3.844343754</v>
       </c>
       <c r="O40">
-        <v>0.966635017</v>
+        <v>0.9610859385</v>
       </c>
       <c r="P40">
-        <v>2.899905051</v>
+        <v>2.8832578155</v>
       </c>
       <c r="Q40">
-        <v>6.239905051000001</v>
+        <v>6.2232578155</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1395395062153567</v>
+        <v>0.1408130254556704</v>
       </c>
       <c r="T40">
-        <v>1.364024033547929</v>
+        <v>1.382555290230493</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.584141962537232</v>
+        <v>5.440958835292688</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1020711955279589</v>
+        <v>0.1018673972023967</v>
       </c>
       <c r="C41">
-        <v>20.39236788390532</v>
+        <v>19.87011422887624</v>
       </c>
       <c r="D41">
-        <v>-33.25381211609468</v>
+        <v>-33.37468577112376</v>
       </c>
       <c r="E41">
-        <v>15.41582</v>
+        <v>15.8172</v>
       </c>
       <c r="F41">
-        <v>15.65382</v>
+        <v>16.0552</v>
       </c>
       <c r="G41">
         <v>69.3</v>
@@ -4649,28 +4649,28 @@
         <v>4.71</v>
       </c>
       <c r="M41">
-        <v>0.865656246</v>
+        <v>0.88785256</v>
       </c>
       <c r="N41">
-        <v>3.844343754</v>
+        <v>3.82214744</v>
       </c>
       <c r="O41">
-        <v>0.9610859385</v>
+        <v>0.95553686</v>
       </c>
       <c r="P41">
-        <v>2.8832578155</v>
+        <v>2.86661058</v>
       </c>
       <c r="Q41">
-        <v>6.2232578155</v>
+        <v>6.206610580000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1408130254556704</v>
+        <v>0.1421289953373278</v>
       </c>
       <c r="T41">
-        <v>1.382555290230493</v>
+        <v>1.401704255469142</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.440958835292688</v>
+        <v>5.30493486441037</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1018673972023967</v>
+        <v>0.1016635988768345</v>
       </c>
       <c r="C42">
-        <v>19.87011422887624</v>
+        <v>19.34697864540021</v>
       </c>
       <c r="D42">
-        <v>-33.37468577112376</v>
+        <v>-33.49644135459979</v>
       </c>
       <c r="E42">
-        <v>15.8172</v>
+        <v>16.21858</v>
       </c>
       <c r="F42">
-        <v>16.0552</v>
+        <v>16.45658</v>
       </c>
       <c r="G42">
         <v>69.3</v>
@@ -4731,28 +4731,28 @@
         <v>4.71</v>
       </c>
       <c r="M42">
-        <v>0.88785256</v>
+        <v>0.910048874</v>
       </c>
       <c r="N42">
-        <v>3.82214744</v>
+        <v>3.799951126</v>
       </c>
       <c r="O42">
-        <v>0.95553686</v>
+        <v>0.9499877815</v>
       </c>
       <c r="P42">
-        <v>2.86661058</v>
+        <v>2.8499633445</v>
       </c>
       <c r="Q42">
-        <v>6.206610580000001</v>
+        <v>6.189963344500001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1421289953373278</v>
+        <v>0.1434895743675161</v>
       </c>
       <c r="T42">
-        <v>1.401704255469142</v>
+        <v>1.421502338173509</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.30493486441037</v>
+        <v>5.175546209180848</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1016635988768345</v>
+        <v>0.1014598005512723</v>
       </c>
       <c r="C43">
-        <v>19.34697864540021</v>
+        <v>18.82295144593581</v>
       </c>
       <c r="D43">
-        <v>-33.49644135459979</v>
+        <v>-33.61908855406418</v>
       </c>
       <c r="E43">
-        <v>16.21858</v>
+        <v>16.61996</v>
       </c>
       <c r="F43">
-        <v>16.45658</v>
+        <v>16.85796</v>
       </c>
       <c r="G43">
         <v>69.3</v>
@@ -4813,28 +4813,28 @@
         <v>4.71</v>
       </c>
       <c r="M43">
-        <v>0.910048874</v>
+        <v>0.9322451880000001</v>
       </c>
       <c r="N43">
-        <v>3.799951126</v>
+        <v>3.777754812</v>
       </c>
       <c r="O43">
-        <v>0.9499877815</v>
+        <v>0.944438703</v>
       </c>
       <c r="P43">
-        <v>2.8499633445</v>
+        <v>2.833316109</v>
       </c>
       <c r="Q43">
-        <v>6.189963344500001</v>
+        <v>6.173316109000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1434895743675161</v>
+        <v>0.1448970699159867</v>
       </c>
       <c r="T43">
-        <v>1.421502338173509</v>
+        <v>1.441983113384922</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.175546209180848</v>
+        <v>5.052318918486066</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1014598005512723</v>
+        <v>0.1012560022257101</v>
       </c>
       <c r="C44">
-        <v>18.82295144593582</v>
+        <v>18.29802280053654</v>
       </c>
       <c r="D44">
-        <v>-33.61908855406418</v>
+        <v>-33.74263719946346</v>
       </c>
       <c r="E44">
-        <v>16.61996</v>
+        <v>17.02134</v>
       </c>
       <c r="F44">
-        <v>16.85796</v>
+        <v>17.25934</v>
       </c>
       <c r="G44">
         <v>69.3</v>
@@ -4895,28 +4895,28 @@
         <v>4.71</v>
       </c>
       <c r="M44">
-        <v>0.932245188</v>
+        <v>0.9544415019999999</v>
       </c>
       <c r="N44">
-        <v>3.777754812</v>
+        <v>3.755558498</v>
       </c>
       <c r="O44">
-        <v>0.944438703</v>
+        <v>0.9388896245</v>
       </c>
       <c r="P44">
-        <v>2.833316109</v>
+        <v>2.8166688735</v>
       </c>
       <c r="Q44">
-        <v>6.173316109000001</v>
+        <v>6.156668873500001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1448970699159867</v>
+        <v>0.1463539512731755</v>
       </c>
       <c r="T44">
-        <v>1.441983113384922</v>
+        <v>1.463182512287964</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.052318918486066</v>
+        <v>4.934823129684066</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1012560022257101</v>
+        <v>0.1010522039001479</v>
       </c>
       <c r="C45">
-        <v>18.29802280053654</v>
+        <v>17.7721827342244</v>
       </c>
       <c r="D45">
-        <v>-33.74263719946346</v>
+        <v>-33.8670972657756</v>
       </c>
       <c r="E45">
-        <v>17.02134</v>
+        <v>17.42272</v>
       </c>
       <c r="F45">
-        <v>17.25934</v>
+        <v>17.66072</v>
       </c>
       <c r="G45">
         <v>69.3</v>
@@ -4977,28 +4977,28 @@
         <v>4.71</v>
       </c>
       <c r="M45">
-        <v>0.9544415019999999</v>
+        <v>0.9766378159999999</v>
       </c>
       <c r="N45">
-        <v>3.755558498</v>
+        <v>3.733362184</v>
       </c>
       <c r="O45">
-        <v>0.9388896245</v>
+        <v>0.933340546</v>
       </c>
       <c r="P45">
-        <v>2.8166688735</v>
+        <v>2.800021638</v>
       </c>
       <c r="Q45">
-        <v>6.156668873500001</v>
+        <v>6.140021638</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1463539512731755</v>
+        <v>0.1478628641074069</v>
       </c>
       <c r="T45">
-        <v>1.463182512287964</v>
+        <v>1.485139032580401</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.934823129684066</v>
+        <v>4.822668058554882</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1010522039001479</v>
+        <v>0.1008484055745856</v>
       </c>
       <c r="C46">
-        <v>17.7721827342244</v>
+        <v>17.24542112430535</v>
       </c>
       <c r="D46">
-        <v>-33.8670972657756</v>
+        <v>-33.99247887569464</v>
       </c>
       <c r="E46">
-        <v>17.42272</v>
+        <v>17.8241</v>
       </c>
       <c r="F46">
-        <v>17.66072</v>
+        <v>18.0621</v>
       </c>
       <c r="G46">
         <v>69.3</v>
@@ -5059,28 +5059,28 @@
         <v>4.71</v>
       </c>
       <c r="M46">
-        <v>0.9766378159999999</v>
+        <v>0.9988341300000001</v>
       </c>
       <c r="N46">
-        <v>3.733362184</v>
+        <v>3.71116587</v>
       </c>
       <c r="O46">
-        <v>0.933340546</v>
+        <v>0.9277914675</v>
       </c>
       <c r="P46">
-        <v>2.800021638</v>
+        <v>2.7833744025</v>
       </c>
       <c r="Q46">
-        <v>6.140021638</v>
+        <v>6.123374402500001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1478628641074069</v>
+        <v>0.1494266464992466</v>
       </c>
       <c r="T46">
-        <v>1.485139032580401</v>
+        <v>1.507893971792562</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.822668058554882</v>
+        <v>4.715497657253662</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1008484055745856</v>
+        <v>0.1006446072490234</v>
       </c>
       <c r="C47">
-        <v>17.24542112430535</v>
+        <v>16.71772769762477</v>
       </c>
       <c r="D47">
-        <v>-33.99247887569464</v>
+        <v>-34.11879230237523</v>
       </c>
       <c r="E47">
-        <v>17.8241</v>
+        <v>18.22548</v>
       </c>
       <c r="F47">
-        <v>18.0621</v>
+        <v>18.46348</v>
       </c>
       <c r="G47">
         <v>69.3</v>
@@ -5141,28 +5141,28 @@
         <v>4.71</v>
       </c>
       <c r="M47">
-        <v>0.9988341300000001</v>
+        <v>1.021030444</v>
       </c>
       <c r="N47">
-        <v>3.71116587</v>
+        <v>3.688969556</v>
       </c>
       <c r="O47">
-        <v>0.9277914675</v>
+        <v>0.922242389</v>
       </c>
       <c r="P47">
-        <v>2.7833744025</v>
+        <v>2.766727167</v>
       </c>
       <c r="Q47">
-        <v>6.123374402500001</v>
+        <v>6.106727167000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1494266464992466</v>
+        <v>0.1510483467574508</v>
       </c>
       <c r="T47">
-        <v>1.507893971792562</v>
+        <v>1.5314916865311</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.715497657253662</v>
+        <v>4.612986838617713</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1006446072490234</v>
+        <v>0.1004408089234612</v>
       </c>
       <c r="C48">
-        <v>16.71772769762477</v>
+        <v>16.18909202776145</v>
       </c>
       <c r="D48">
-        <v>-34.11879230237523</v>
+        <v>-34.24604797223855</v>
       </c>
       <c r="E48">
-        <v>18.22548</v>
+        <v>18.62686</v>
       </c>
       <c r="F48">
-        <v>18.46348</v>
+        <v>18.86486</v>
       </c>
       <c r="G48">
         <v>69.3</v>
@@ -5223,28 +5223,28 @@
         <v>4.71</v>
       </c>
       <c r="M48">
-        <v>1.021030444</v>
+        <v>1.043226758</v>
       </c>
       <c r="N48">
-        <v>3.688969556</v>
+        <v>3.666773242</v>
       </c>
       <c r="O48">
-        <v>0.922242389</v>
+        <v>0.9166933104999999</v>
       </c>
       <c r="P48">
-        <v>2.766727167</v>
+        <v>2.7500799315</v>
       </c>
       <c r="Q48">
-        <v>6.106727167000001</v>
+        <v>6.0900799315</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1510483467574508</v>
+        <v>0.1527312432518136</v>
       </c>
       <c r="T48">
-        <v>1.5314916865311</v>
+        <v>1.555979881071092</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.612986838617713</v>
+        <v>4.51483818247691</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1004408089234612</v>
+        <v>0.101137010597899</v>
       </c>
       <c r="C49">
-        <v>16.18909202776145</v>
+        <v>16.21856573098</v>
       </c>
       <c r="D49">
-        <v>-34.24604797223855</v>
+        <v>-33.81519426902</v>
       </c>
       <c r="E49">
-        <v>18.62686</v>
+        <v>19.02824</v>
       </c>
       <c r="F49">
-        <v>18.86486</v>
+        <v>19.26624</v>
       </c>
       <c r="G49">
         <v>69.3</v>
@@ -5305,45 +5305,45 @@
         <v>4.71</v>
       </c>
       <c r="M49">
-        <v>1.043226758</v>
+        <v>1.113588672</v>
       </c>
       <c r="N49">
-        <v>3.666773242</v>
+        <v>3.596411328</v>
       </c>
       <c r="O49">
-        <v>0.9166933104999999</v>
+        <v>0.899102832</v>
       </c>
       <c r="P49">
-        <v>2.7500799315</v>
+        <v>2.697308496</v>
       </c>
       <c r="Q49">
-        <v>6.0900799315</v>
+        <v>6.037308496000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1527312432518136</v>
+        <v>0.1544788665344212</v>
       </c>
       <c r="T49">
-        <v>1.555979881071092</v>
+        <v>1.581409929247237</v>
       </c>
       <c r="U49">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.51483818247691</v>
+        <v>4.229568886993849</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.101137010597899</v>
+        <v>0.1009519622723368</v>
       </c>
       <c r="C50">
-        <v>16.21856573098</v>
+        <v>15.70372748180395</v>
       </c>
       <c r="D50">
-        <v>-33.81519426902</v>
+        <v>-33.92865251819605</v>
       </c>
       <c r="E50">
-        <v>19.02824</v>
+        <v>19.42962</v>
       </c>
       <c r="F50">
-        <v>19.26624</v>
+        <v>19.66762</v>
       </c>
       <c r="G50">
         <v>69.3</v>
@@ -5387,28 +5387,28 @@
         <v>4.71</v>
       </c>
       <c r="M50">
-        <v>1.113588672</v>
+        <v>1.136788436</v>
       </c>
       <c r="N50">
-        <v>3.596411328</v>
+        <v>3.573211564</v>
       </c>
       <c r="O50">
-        <v>0.899102832</v>
+        <v>0.893302891</v>
       </c>
       <c r="P50">
-        <v>2.697308496</v>
+        <v>2.679908673</v>
       </c>
       <c r="Q50">
-        <v>6.037308496000001</v>
+        <v>6.019908673000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1544788665344212</v>
+        <v>0.1562950240634055</v>
       </c>
       <c r="T50">
-        <v>1.581409929247237</v>
+        <v>1.607837234214604</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.229568886993849</v>
+        <v>4.143251154606221</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1009519622723368</v>
+        <v>0.1007669139467746</v>
       </c>
       <c r="C51">
-        <v>15.70372748180395</v>
+        <v>15.18812530911377</v>
       </c>
       <c r="D51">
-        <v>-33.92865251819605</v>
+        <v>-34.04287469088623</v>
       </c>
       <c r="E51">
-        <v>19.42962</v>
+        <v>19.831</v>
       </c>
       <c r="F51">
-        <v>19.66762</v>
+        <v>20.069</v>
       </c>
       <c r="G51">
         <v>69.3</v>
@@ -5469,28 +5469,28 @@
         <v>4.71</v>
       </c>
       <c r="M51">
-        <v>1.136788436</v>
+        <v>1.1599882</v>
       </c>
       <c r="N51">
-        <v>3.573211564</v>
+        <v>3.5500118</v>
       </c>
       <c r="O51">
-        <v>0.893302891</v>
+        <v>0.88750295</v>
       </c>
       <c r="P51">
-        <v>2.679908673</v>
+        <v>2.66250885</v>
       </c>
       <c r="Q51">
-        <v>6.019908673000001</v>
+        <v>6.002508850000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1562950240634055</v>
+        <v>0.1581838278935492</v>
       </c>
       <c r="T51">
-        <v>1.607837234214604</v>
+        <v>1.635321631380666</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.143251154606221</v>
+        <v>4.060386131514097</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1007669139467746</v>
+        <v>0.1019206156212124</v>
       </c>
       <c r="C52">
-        <v>15.18812530911377</v>
+        <v>15.48658299084274</v>
       </c>
       <c r="D52">
-        <v>-34.04287469088623</v>
+        <v>-33.34303700915726</v>
       </c>
       <c r="E52">
-        <v>19.831</v>
+        <v>20.23238</v>
       </c>
       <c r="F52">
-        <v>20.069</v>
+        <v>20.47038</v>
       </c>
       <c r="G52">
         <v>69.3</v>
@@ -5551,45 +5551,45 @@
         <v>4.71</v>
       </c>
       <c r="M52">
-        <v>1.1599882</v>
+        <v>1.254834294</v>
       </c>
       <c r="N52">
-        <v>3.5500118</v>
+        <v>3.455165706</v>
       </c>
       <c r="O52">
-        <v>0.88750295</v>
+        <v>0.8637914265</v>
       </c>
       <c r="P52">
-        <v>2.66250885</v>
+        <v>2.5913742795</v>
       </c>
       <c r="Q52">
-        <v>6.002508850000001</v>
+        <v>5.931374279500001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1581838278935492</v>
+        <v>0.1601497257575763</v>
       </c>
       <c r="T52">
-        <v>1.635321631380666</v>
+        <v>1.663927840675955</v>
       </c>
       <c r="U52">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.060386131514097</v>
+        <v>3.753483645227822</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1019206156212124</v>
+        <v>0.1017618172956501</v>
       </c>
       <c r="C53">
-        <v>15.48658299084274</v>
+        <v>14.99058814982996</v>
       </c>
       <c r="D53">
-        <v>-33.34303700915726</v>
+        <v>-33.43765185017003</v>
       </c>
       <c r="E53">
-        <v>20.23238</v>
+        <v>20.63376</v>
       </c>
       <c r="F53">
-        <v>20.47038</v>
+        <v>20.87176</v>
       </c>
       <c r="G53">
         <v>69.3</v>
@@ -5633,28 +5633,28 @@
         <v>4.71</v>
       </c>
       <c r="M53">
-        <v>1.254834294</v>
+        <v>1.279438888</v>
       </c>
       <c r="N53">
-        <v>3.455165706</v>
+        <v>3.430561112</v>
       </c>
       <c r="O53">
-        <v>0.8637914265</v>
+        <v>0.8576402780000001</v>
       </c>
       <c r="P53">
-        <v>2.5913742795</v>
+        <v>2.572920834</v>
       </c>
       <c r="Q53">
-        <v>5.931374279500001</v>
+        <v>5.912920834000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1601497257575763</v>
+        <v>0.1621975360326045</v>
       </c>
       <c r="T53">
-        <v>1.663927840675955</v>
+        <v>1.693725975358547</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.753483645227822</v>
+        <v>3.681301267434979</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1017618172956501</v>
+        <v>0.1016030189700879</v>
       </c>
       <c r="C54">
-        <v>14.99058814982996</v>
+        <v>14.49405481901492</v>
       </c>
       <c r="D54">
-        <v>-33.43765185017003</v>
+        <v>-33.53280518098507</v>
       </c>
       <c r="E54">
-        <v>20.63376</v>
+        <v>21.03514</v>
       </c>
       <c r="F54">
-        <v>20.87176</v>
+        <v>21.27314</v>
       </c>
       <c r="G54">
         <v>69.3</v>
@@ -5715,28 +5715,28 @@
         <v>4.71</v>
       </c>
       <c r="M54">
-        <v>1.279438888</v>
+        <v>1.304043482</v>
       </c>
       <c r="N54">
-        <v>3.430561112</v>
+        <v>3.405956518</v>
       </c>
       <c r="O54">
-        <v>0.8576402780000001</v>
+        <v>0.8514891295</v>
       </c>
       <c r="P54">
-        <v>2.572920834</v>
+        <v>2.5544673885</v>
       </c>
       <c r="Q54">
-        <v>5.912920834000001</v>
+        <v>5.894467388500001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1621975360326045</v>
+        <v>0.1643324871703999</v>
       </c>
       <c r="T54">
-        <v>1.693725975358547</v>
+        <v>1.724792115772313</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.681301267434979</v>
+        <v>3.611842752955073</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1016030189700879</v>
+        <v>0.1014442206445257</v>
       </c>
       <c r="C55">
-        <v>14.49405481901492</v>
+        <v>13.99697838814635</v>
       </c>
       <c r="D55">
-        <v>-33.53280518098507</v>
+        <v>-33.62850161185365</v>
       </c>
       <c r="E55">
-        <v>21.03514</v>
+        <v>21.43652</v>
       </c>
       <c r="F55">
-        <v>21.27314</v>
+        <v>21.67452</v>
       </c>
       <c r="G55">
         <v>69.3</v>
@@ -5797,28 +5797,28 @@
         <v>4.71</v>
       </c>
       <c r="M55">
-        <v>1.304043482</v>
+        <v>1.328648076</v>
       </c>
       <c r="N55">
-        <v>3.405956518</v>
+        <v>3.381351924</v>
       </c>
       <c r="O55">
-        <v>0.8514891295</v>
+        <v>0.8453379809999999</v>
       </c>
       <c r="P55">
-        <v>2.5544673885</v>
+        <v>2.536013942999999</v>
       </c>
       <c r="Q55">
-        <v>5.894467388500001</v>
+        <v>5.876013943</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1643324871703999</v>
+        <v>0.1665602622707081</v>
       </c>
       <c r="T55">
-        <v>1.724792115772313</v>
+        <v>1.7572089579432</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.611842752955073</v>
+        <v>3.544956776048497</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1014442206445257</v>
+        <v>0.1024404223189635</v>
       </c>
       <c r="C56">
-        <v>13.99697838814635</v>
+        <v>14.18706236816238</v>
       </c>
       <c r="D56">
-        <v>-33.62850161185365</v>
+        <v>-33.03703763183762</v>
       </c>
       <c r="E56">
-        <v>21.43652</v>
+        <v>21.8379</v>
       </c>
       <c r="F56">
-        <v>21.67452</v>
+        <v>22.0759</v>
       </c>
       <c r="G56">
         <v>69.3</v>
@@ -5879,45 +5879,45 @@
         <v>4.71</v>
       </c>
       <c r="M56">
-        <v>1.328648076</v>
+        <v>1.41506519</v>
       </c>
       <c r="N56">
-        <v>3.381351924</v>
+        <v>3.29493481</v>
       </c>
       <c r="O56">
-        <v>0.8453379809999999</v>
+        <v>0.8237337025</v>
       </c>
       <c r="P56">
-        <v>2.536013942999999</v>
+        <v>2.4712011075</v>
       </c>
       <c r="Q56">
-        <v>5.876013943</v>
+        <v>5.811201107500001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1665602622707081</v>
+        <v>0.1688870495976967</v>
       </c>
       <c r="T56">
-        <v>1.7572089579432</v>
+        <v>1.791066548655015</v>
       </c>
       <c r="U56">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.544956776048497</v>
+        <v>3.328468563345834</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1024404223189635</v>
+        <v>0.1023026239934013</v>
       </c>
       <c r="C57">
-        <v>14.18706236816238</v>
+        <v>13.7051118008957</v>
       </c>
       <c r="D57">
-        <v>-33.03703763183762</v>
+        <v>-33.1176081991043</v>
       </c>
       <c r="E57">
-        <v>21.8379</v>
+        <v>22.23928</v>
       </c>
       <c r="F57">
-        <v>22.0759</v>
+        <v>22.47728</v>
       </c>
       <c r="G57">
         <v>69.3</v>
@@ -5961,28 +5961,28 @@
         <v>4.71</v>
       </c>
       <c r="M57">
-        <v>1.41506519</v>
+        <v>1.440793648</v>
       </c>
       <c r="N57">
-        <v>3.29493481</v>
+        <v>3.269206352</v>
       </c>
       <c r="O57">
-        <v>0.8237337025</v>
+        <v>0.817301588</v>
       </c>
       <c r="P57">
-        <v>2.4712011075</v>
+        <v>2.451904764</v>
       </c>
       <c r="Q57">
-        <v>5.811201107500001</v>
+        <v>5.791904764000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1688870495976967</v>
+        <v>0.171319599985003</v>
       </c>
       <c r="T57">
-        <v>1.791066548655015</v>
+        <v>1.826463120762821</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.328468563345834</v>
+        <v>3.269031624714658</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1023026239934013</v>
+        <v>0.1021648256678391</v>
       </c>
       <c r="C58">
-        <v>13.7051118008957</v>
+        <v>13.22276728264536</v>
       </c>
       <c r="D58">
-        <v>-33.1176081991043</v>
+        <v>-33.19857271735464</v>
       </c>
       <c r="E58">
-        <v>22.23928</v>
+        <v>22.64066</v>
       </c>
       <c r="F58">
-        <v>22.47728</v>
+        <v>22.87866</v>
       </c>
       <c r="G58">
         <v>69.3</v>
@@ -6043,28 +6043,28 @@
         <v>4.71</v>
       </c>
       <c r="M58">
-        <v>1.440793648</v>
+        <v>1.466522106</v>
       </c>
       <c r="N58">
-        <v>3.269206352</v>
+        <v>3.243477894</v>
       </c>
       <c r="O58">
-        <v>0.817301588</v>
+        <v>0.8108694734999999</v>
       </c>
       <c r="P58">
-        <v>2.451904764</v>
+        <v>2.4326084205</v>
       </c>
       <c r="Q58">
-        <v>5.791904764000001</v>
+        <v>5.772608420500001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.171319599985003</v>
+        <v>0.1738652922507886</v>
       </c>
       <c r="T58">
-        <v>1.826463120762821</v>
+        <v>1.863506045061689</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.269031624714658</v>
+        <v>3.211680192702121</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1021648256678391</v>
+        <v>0.1020270273422769</v>
       </c>
       <c r="C59">
-        <v>13.22276728264536</v>
+        <v>12.74002591698647</v>
       </c>
       <c r="D59">
-        <v>-33.19857271735464</v>
+        <v>-33.27993408301352</v>
       </c>
       <c r="E59">
-        <v>22.64066</v>
+        <v>23.04204</v>
       </c>
       <c r="F59">
-        <v>22.87866</v>
+        <v>23.28004</v>
       </c>
       <c r="G59">
         <v>69.3</v>
@@ -6125,28 +6125,28 @@
         <v>4.71</v>
       </c>
       <c r="M59">
-        <v>1.466522106</v>
+        <v>1.492250564</v>
       </c>
       <c r="N59">
-        <v>3.243477894</v>
+        <v>3.217749436</v>
       </c>
       <c r="O59">
-        <v>0.8108694734999999</v>
+        <v>0.8044373589999999</v>
       </c>
       <c r="P59">
-        <v>2.4326084205</v>
+        <v>2.413312077</v>
       </c>
       <c r="Q59">
-        <v>5.772608420500001</v>
+        <v>5.753312077</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1738652922507886</v>
+        <v>0.1765322079578021</v>
       </c>
       <c r="T59">
-        <v>1.863506045061689</v>
+        <v>1.902312918136693</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.211680192702121</v>
+        <v>3.156306396276221</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1020270273422769</v>
+        <v>0.1018892290167147</v>
       </c>
       <c r="C60">
-        <v>12.74002591698649</v>
+        <v>12.25688477903087</v>
       </c>
       <c r="D60">
-        <v>-33.27993408301351</v>
+        <v>-33.36169522096913</v>
       </c>
       <c r="E60">
-        <v>23.04204</v>
+        <v>23.44342</v>
       </c>
       <c r="F60">
-        <v>23.28004</v>
+        <v>23.68142</v>
       </c>
       <c r="G60">
         <v>69.3</v>
@@ -6207,28 +6207,28 @@
         <v>4.71</v>
       </c>
       <c r="M60">
-        <v>1.492250564</v>
+        <v>1.517979022</v>
       </c>
       <c r="N60">
-        <v>3.217749436</v>
+        <v>3.192020978</v>
       </c>
       <c r="O60">
-        <v>0.804437359</v>
+        <v>0.7980052445</v>
       </c>
       <c r="P60">
-        <v>2.413312077</v>
+        <v>2.3940157335</v>
       </c>
       <c r="Q60">
-        <v>5.753312077</v>
+        <v>5.734015733500001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1765322079578021</v>
+        <v>0.1793292171139382</v>
       </c>
       <c r="T60">
-        <v>1.902312918136693</v>
+        <v>1.943012809410477</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.156306396276222</v>
+        <v>3.102809677695269</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1018892290167147</v>
+        <v>0.1017514306911525</v>
       </c>
       <c r="C61">
-        <v>12.25688477903087</v>
+        <v>11.77334091507639</v>
       </c>
       <c r="D61">
-        <v>-33.36169522096913</v>
+        <v>-33.44385908492361</v>
       </c>
       <c r="E61">
-        <v>23.44342</v>
+        <v>23.8448</v>
       </c>
       <c r="F61">
-        <v>23.68142</v>
+        <v>24.0828</v>
       </c>
       <c r="G61">
         <v>69.3</v>
@@ -6289,28 +6289,28 @@
         <v>4.71</v>
       </c>
       <c r="M61">
-        <v>1.517979022</v>
+        <v>1.54370748</v>
       </c>
       <c r="N61">
-        <v>3.192020978</v>
+        <v>3.16629252</v>
       </c>
       <c r="O61">
-        <v>0.7980052445</v>
+        <v>0.79157313</v>
       </c>
       <c r="P61">
-        <v>2.3940157335</v>
+        <v>2.37471939</v>
       </c>
       <c r="Q61">
-        <v>5.734015733500001</v>
+        <v>5.714719390000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1793292171139382</v>
+        <v>0.1822660767278811</v>
       </c>
       <c r="T61">
-        <v>1.943012809410477</v>
+        <v>1.985747695247951</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.102809677695269</v>
+        <v>3.051096183067014</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1017514306911525</v>
+        <v>0.1016136323655903</v>
       </c>
       <c r="C62">
-        <v>11.77334091507639</v>
+        <v>11.28939134225134</v>
       </c>
       <c r="D62">
-        <v>-33.44385908492361</v>
+        <v>-33.52642865774866</v>
       </c>
       <c r="E62">
-        <v>23.8448</v>
+        <v>24.24618</v>
       </c>
       <c r="F62">
-        <v>24.0828</v>
+        <v>24.48418</v>
       </c>
       <c r="G62">
         <v>69.3</v>
@@ -6371,28 +6371,28 @@
         <v>4.71</v>
       </c>
       <c r="M62">
-        <v>1.54370748</v>
+        <v>1.569435938</v>
       </c>
       <c r="N62">
-        <v>3.16629252</v>
+        <v>3.140564062</v>
       </c>
       <c r="O62">
-        <v>0.79157313</v>
+        <v>0.7851410155</v>
       </c>
       <c r="P62">
-        <v>2.37471939</v>
+        <v>2.3554230465</v>
       </c>
       <c r="Q62">
-        <v>5.714719390000001</v>
+        <v>5.695423046500001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1822660767278811</v>
+        <v>0.1853535445271545</v>
       </c>
       <c r="T62">
-        <v>1.985747695247951</v>
+        <v>2.030674113692475</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.051096183067014</v>
+        <v>3.001078212852801</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1016136323655903</v>
+        <v>0.105102834040028</v>
       </c>
       <c r="C63">
-        <v>11.28939134225134</v>
+        <v>12.86060629330504</v>
       </c>
       <c r="D63">
-        <v>-33.52642865774866</v>
+        <v>-31.55383370669496</v>
       </c>
       <c r="E63">
-        <v>24.24618</v>
+        <v>24.64756</v>
       </c>
       <c r="F63">
-        <v>24.48418</v>
+        <v>24.88556</v>
       </c>
       <c r="G63">
         <v>69.3</v>
@@ -6453,45 +6453,45 @@
         <v>4.71</v>
       </c>
       <c r="M63">
-        <v>1.569435938</v>
+        <v>1.789271764</v>
       </c>
       <c r="N63">
-        <v>3.140564062</v>
+        <v>2.920728236</v>
       </c>
       <c r="O63">
-        <v>0.7851410155</v>
+        <v>0.730182059</v>
       </c>
       <c r="P63">
-        <v>2.3554230465</v>
+        <v>2.190546177</v>
       </c>
       <c r="Q63">
-        <v>5.695423046500001</v>
+        <v>5.530546177000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1853535445271545</v>
+        <v>0.1886035106316527</v>
       </c>
       <c r="T63">
-        <v>2.030674113692475</v>
+        <v>2.077965080476184</v>
       </c>
       <c r="U63">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>3.001078212852801</v>
+        <v>2.632355852679739</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.105102834040028</v>
+        <v>0.1050235357144658</v>
       </c>
       <c r="C64">
-        <v>12.86060629330504</v>
+        <v>12.41697676956717</v>
       </c>
       <c r="D64">
-        <v>-31.55383370669496</v>
+        <v>-31.59608323043283</v>
       </c>
       <c r="E64">
-        <v>24.64756</v>
+        <v>25.04894</v>
       </c>
       <c r="F64">
-        <v>24.88556</v>
+        <v>25.28694</v>
       </c>
       <c r="G64">
         <v>69.3</v>
@@ -6535,28 +6535,28 @@
         <v>4.71</v>
       </c>
       <c r="M64">
-        <v>1.789271764</v>
+        <v>1.818130986</v>
       </c>
       <c r="N64">
-        <v>2.920728236</v>
+        <v>2.891869014</v>
       </c>
       <c r="O64">
-        <v>0.730182059</v>
+        <v>0.7229672535</v>
       </c>
       <c r="P64">
-        <v>2.190546177</v>
+        <v>2.1689017605</v>
       </c>
       <c r="Q64">
-        <v>5.530546177000001</v>
+        <v>5.508901760500001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1886035106316527</v>
+        <v>0.1920291505796373</v>
       </c>
       <c r="T64">
-        <v>2.077965080476184</v>
+        <v>2.127812315734689</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.632355852679739</v>
+        <v>2.590572426446727</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1050235357144658</v>
+        <v>0.1049442373889036</v>
       </c>
       <c r="C65">
-        <v>12.41697676956717</v>
+        <v>11.97323395274661</v>
       </c>
       <c r="D65">
-        <v>-31.59608323043283</v>
+        <v>-31.63844604725339</v>
       </c>
       <c r="E65">
-        <v>25.04894</v>
+        <v>25.45032</v>
       </c>
       <c r="F65">
-        <v>25.28694</v>
+        <v>25.68832</v>
       </c>
       <c r="G65">
         <v>69.3</v>
@@ -6617,28 +6617,28 @@
         <v>4.71</v>
       </c>
       <c r="M65">
-        <v>1.818130986</v>
+        <v>1.846990208</v>
       </c>
       <c r="N65">
-        <v>2.891869014</v>
+        <v>2.863009792</v>
       </c>
       <c r="O65">
-        <v>0.7229672535</v>
+        <v>0.7157524479999999</v>
       </c>
       <c r="P65">
-        <v>2.1689017605</v>
+        <v>2.147257344</v>
       </c>
       <c r="Q65">
-        <v>5.508901760500001</v>
+        <v>5.487257344000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1920291505796373</v>
+        <v>0.1956451038580655</v>
       </c>
       <c r="T65">
-        <v>2.127812315734689</v>
+        <v>2.180428841840888</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.590572426446727</v>
+        <v>2.550094732283497</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1049442373889036</v>
+        <v>0.1048649390633414</v>
       </c>
       <c r="C66">
-        <v>11.97323395274661</v>
+        <v>11.5293773865345</v>
       </c>
       <c r="D66">
-        <v>-31.63844604725339</v>
+        <v>-31.68092261346549</v>
       </c>
       <c r="E66">
-        <v>25.45032</v>
+        <v>25.8517</v>
       </c>
       <c r="F66">
-        <v>25.68832</v>
+        <v>26.0897</v>
       </c>
       <c r="G66">
         <v>69.3</v>
@@ -6699,28 +6699,28 @@
         <v>4.71</v>
       </c>
       <c r="M66">
-        <v>1.846990208</v>
+        <v>1.87584943</v>
       </c>
       <c r="N66">
-        <v>2.863009792</v>
+        <v>2.83415057</v>
       </c>
       <c r="O66">
-        <v>0.7157524479999999</v>
+        <v>0.7085376425</v>
       </c>
       <c r="P66">
-        <v>2.147257344</v>
+        <v>2.1256129275</v>
       </c>
       <c r="Q66">
-        <v>5.487257344000001</v>
+        <v>5.4656129275</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1956451038580655</v>
+        <v>0.1994676830381183</v>
       </c>
       <c r="T66">
-        <v>2.180428841840888</v>
+        <v>2.236052026581727</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.550094732283497</v>
+        <v>2.510862505632981</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1048649390633414</v>
+        <v>0.1067161407377792</v>
       </c>
       <c r="C67">
-        <v>11.5293773865345</v>
+        <v>12.0907599036519</v>
       </c>
       <c r="D67">
-        <v>-31.68092261346549</v>
+        <v>-30.7181600963481</v>
       </c>
       <c r="E67">
-        <v>25.8517</v>
+        <v>26.25308</v>
       </c>
       <c r="F67">
-        <v>26.0897</v>
+        <v>26.49108</v>
       </c>
       <c r="G67">
         <v>69.3</v>
@@ -6781,45 +6781,45 @@
         <v>4.71</v>
       </c>
       <c r="M67">
-        <v>1.87584943</v>
+        <v>2.008023864</v>
       </c>
       <c r="N67">
-        <v>2.83415057</v>
+        <v>2.701976136</v>
       </c>
       <c r="O67">
-        <v>0.7085376425</v>
+        <v>0.675494034</v>
       </c>
       <c r="P67">
-        <v>2.1256129275</v>
+        <v>2.026482102</v>
       </c>
       <c r="Q67">
-        <v>5.4656129275</v>
+        <v>5.366482102000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1994676830381183</v>
+        <v>0.2035151198169976</v>
       </c>
       <c r="T67">
-        <v>2.236052026581727</v>
+        <v>2.294947163366145</v>
       </c>
       <c r="U67">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.510862505632981</v>
+        <v>2.345589653809014</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1067161407377792</v>
+        <v>0.1066660924122169</v>
       </c>
       <c r="C68">
-        <v>12.0907599036519</v>
+        <v>11.66412130044204</v>
       </c>
       <c r="D68">
-        <v>-30.7181600963481</v>
+        <v>-30.74341869955796</v>
       </c>
       <c r="E68">
-        <v>26.25308</v>
+        <v>26.65446</v>
       </c>
       <c r="F68">
-        <v>26.49108</v>
+        <v>26.89246</v>
       </c>
       <c r="G68">
         <v>69.3</v>
@@ -6863,28 +6863,28 @@
         <v>4.71</v>
       </c>
       <c r="M68">
-        <v>2.008023864</v>
+        <v>2.038448468</v>
       </c>
       <c r="N68">
-        <v>2.701976136</v>
+        <v>2.671551532</v>
       </c>
       <c r="O68">
-        <v>0.675494034</v>
+        <v>0.6678878829999999</v>
       </c>
       <c r="P68">
-        <v>2.026482102</v>
+        <v>2.003663649</v>
       </c>
       <c r="Q68">
-        <v>5.366482102000001</v>
+        <v>5.343663649000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2035151198169976</v>
+        <v>0.2078078557945968</v>
       </c>
       <c r="T68">
-        <v>2.294947163366145</v>
+        <v>2.357411702379921</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.345589653809014</v>
+        <v>2.310580853005895</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1066660924122169</v>
+        <v>0.1066160440866548</v>
       </c>
       <c r="C69">
-        <v>11.66412130044204</v>
+        <v>11.23744112429481</v>
       </c>
       <c r="D69">
-        <v>-30.74341869955796</v>
+        <v>-30.76871887570519</v>
       </c>
       <c r="E69">
-        <v>26.65446</v>
+        <v>27.05584</v>
       </c>
       <c r="F69">
-        <v>26.89246</v>
+        <v>27.29384</v>
       </c>
       <c r="G69">
         <v>69.3</v>
@@ -6945,28 +6945,28 @@
         <v>4.71</v>
       </c>
       <c r="M69">
-        <v>2.038448468</v>
+        <v>2.068873072</v>
       </c>
       <c r="N69">
-        <v>2.671551532</v>
+        <v>2.641126928</v>
       </c>
       <c r="O69">
-        <v>0.6678878829999999</v>
+        <v>0.660281732</v>
       </c>
       <c r="P69">
-        <v>2.003663649</v>
+        <v>1.980845196</v>
       </c>
       <c r="Q69">
-        <v>5.343663649000001</v>
+        <v>5.320845196</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2078078557945968</v>
+        <v>0.2123688877707961</v>
       </c>
       <c r="T69">
-        <v>2.357411702379921</v>
+        <v>2.423780275082059</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.310580853005895</v>
+        <v>2.276601722814632</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1066160440866548</v>
+        <v>0.1065659957610925</v>
       </c>
       <c r="C70">
-        <v>11.23744112429481</v>
+        <v>10.81071927248877</v>
       </c>
       <c r="D70">
-        <v>-30.76871887570519</v>
+        <v>-30.79406072751122</v>
       </c>
       <c r="E70">
-        <v>27.05584</v>
+        <v>27.45722</v>
       </c>
       <c r="F70">
-        <v>27.29384</v>
+        <v>27.69522</v>
       </c>
       <c r="G70">
         <v>69.3</v>
@@ -7027,28 +7027,28 @@
         <v>4.71</v>
       </c>
       <c r="M70">
-        <v>2.068873072</v>
+        <v>2.099297676</v>
       </c>
       <c r="N70">
-        <v>2.641126928</v>
+        <v>2.610702324</v>
       </c>
       <c r="O70">
-        <v>0.660281732</v>
+        <v>0.6526755809999999</v>
       </c>
       <c r="P70">
-        <v>1.980845196</v>
+        <v>1.958026743</v>
       </c>
       <c r="Q70">
-        <v>5.320845196</v>
+        <v>5.298026743</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2123688877707961</v>
+        <v>0.2172241798744921</v>
       </c>
       <c r="T70">
-        <v>2.423780275082059</v>
+        <v>2.494430691184334</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.276601722814632</v>
+        <v>2.243607494947753</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1065659957610925</v>
+        <v>0.1065159474355303</v>
       </c>
       <c r="C71">
-        <v>10.81071927248877</v>
+        <v>10.38395564196386</v>
       </c>
       <c r="D71">
-        <v>-30.79406072751122</v>
+        <v>-30.81944435803614</v>
       </c>
       <c r="E71">
-        <v>27.45722</v>
+        <v>27.8586</v>
       </c>
       <c r="F71">
-        <v>27.69522</v>
+        <v>28.0966</v>
       </c>
       <c r="G71">
         <v>69.3</v>
@@ -7109,28 +7109,28 @@
         <v>4.71</v>
       </c>
       <c r="M71">
-        <v>2.099297676</v>
+        <v>2.12972228</v>
       </c>
       <c r="N71">
-        <v>2.610702324</v>
+        <v>2.58027772</v>
       </c>
       <c r="O71">
-        <v>0.6526755809999999</v>
+        <v>0.6450694299999999</v>
       </c>
       <c r="P71">
-        <v>1.958026743</v>
+        <v>1.93520829</v>
       </c>
       <c r="Q71">
-        <v>5.298026743</v>
+        <v>5.27520829</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2172241798744921</v>
+        <v>0.2224031581184344</v>
       </c>
       <c r="T71">
-        <v>2.494430691184334</v>
+        <v>2.569791135026761</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.243607494947753</v>
+        <v>2.211555959305642</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1065159474355303</v>
+        <v>0.1064658991099681</v>
       </c>
       <c r="C72">
-        <v>10.38395564196386</v>
+        <v>9.95715012931991</v>
       </c>
       <c r="D72">
-        <v>-30.81944435803614</v>
+        <v>-30.84486987068008</v>
       </c>
       <c r="E72">
-        <v>27.8586</v>
+        <v>28.25998</v>
       </c>
       <c r="F72">
-        <v>28.0966</v>
+        <v>28.49798</v>
       </c>
       <c r="G72">
         <v>69.3</v>
@@ -7191,28 +7191,28 @@
         <v>4.71</v>
       </c>
       <c r="M72">
-        <v>2.12972228</v>
+        <v>2.160146884</v>
       </c>
       <c r="N72">
-        <v>2.58027772</v>
+        <v>2.549853116</v>
       </c>
       <c r="O72">
-        <v>0.6450694299999999</v>
+        <v>0.6374632789999999</v>
       </c>
       <c r="P72">
-        <v>1.93520829</v>
+        <v>1.912389837</v>
       </c>
       <c r="Q72">
-        <v>5.27520829</v>
+        <v>5.252389837000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2224031581184344</v>
+        <v>0.2279393072757522</v>
       </c>
       <c r="T72">
-        <v>2.569791135026761</v>
+        <v>2.650348850858321</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.211555959305642</v>
+        <v>2.180407283822464</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1064658991099681</v>
+        <v>0.1064158507844059</v>
       </c>
       <c r="C73">
-        <v>9.957150129319913</v>
+        <v>9.530302630815232</v>
       </c>
       <c r="D73">
-        <v>-30.84486987068008</v>
+        <v>-30.87033736918477</v>
       </c>
       <c r="E73">
-        <v>28.25998</v>
+        <v>28.66136</v>
       </c>
       <c r="F73">
-        <v>28.49798</v>
+        <v>28.89936</v>
       </c>
       <c r="G73">
         <v>69.3</v>
@@ -7273,28 +7273,28 @@
         <v>4.71</v>
       </c>
       <c r="M73">
-        <v>2.160146884</v>
+        <v>2.190571488</v>
       </c>
       <c r="N73">
-        <v>2.549853116</v>
+        <v>2.519428512</v>
       </c>
       <c r="O73">
-        <v>0.637463279</v>
+        <v>0.6298571279999999</v>
       </c>
       <c r="P73">
-        <v>1.912389837</v>
+        <v>1.889571384</v>
       </c>
       <c r="Q73">
-        <v>5.252389837000001</v>
+        <v>5.229571384000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2279393072757521</v>
+        <v>0.2338708956585925</v>
       </c>
       <c r="T73">
-        <v>2.65034885085832</v>
+        <v>2.736660689249277</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.180407283822464</v>
+        <v>2.15012384932493</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1064158507844059</v>
+        <v>0.1063658024588437</v>
       </c>
       <c r="C74">
-        <v>9.530302630815232</v>
+        <v>9.103413042365254</v>
       </c>
       <c r="D74">
-        <v>-30.87033736918477</v>
+        <v>-30.89584695763475</v>
       </c>
       <c r="E74">
-        <v>28.66136</v>
+        <v>29.06274</v>
       </c>
       <c r="F74">
-        <v>28.89936</v>
+        <v>29.30074</v>
       </c>
       <c r="G74">
         <v>69.3</v>
@@ -7355,28 +7355,28 @@
         <v>4.71</v>
       </c>
       <c r="M74">
-        <v>2.190571488</v>
+        <v>2.220996092</v>
       </c>
       <c r="N74">
-        <v>2.519428512</v>
+        <v>2.489003908</v>
       </c>
       <c r="O74">
-        <v>0.6298571279999999</v>
+        <v>0.622250977</v>
       </c>
       <c r="P74">
-        <v>1.889571384</v>
+        <v>1.866752931</v>
       </c>
       <c r="Q74">
-        <v>5.229571384000001</v>
+        <v>5.206752931</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2338708956585925</v>
+        <v>0.2402418609586803</v>
       </c>
       <c r="T74">
-        <v>2.736660689249277</v>
+        <v>2.829365997150675</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.15012384932493</v>
+        <v>2.120670097964314</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1063658024588437</v>
+        <v>0.1063157541332815</v>
       </c>
       <c r="C75">
-        <v>9.103413042365254</v>
+        <v>8.676481259541031</v>
       </c>
       <c r="D75">
-        <v>-30.89584695763475</v>
+        <v>-30.92139874045897</v>
       </c>
       <c r="E75">
-        <v>29.06274</v>
+        <v>29.46412</v>
       </c>
       <c r="F75">
-        <v>29.30074</v>
+        <v>29.70212</v>
       </c>
       <c r="G75">
         <v>69.3</v>
@@ -7437,28 +7437,28 @@
         <v>4.71</v>
       </c>
       <c r="M75">
-        <v>2.220996092</v>
+        <v>2.251420696</v>
       </c>
       <c r="N75">
-        <v>2.489003908</v>
+        <v>2.458579304</v>
       </c>
       <c r="O75">
-        <v>0.622250977</v>
+        <v>0.614644826</v>
       </c>
       <c r="P75">
-        <v>1.866752931</v>
+        <v>1.843934478</v>
       </c>
       <c r="Q75">
-        <v>5.206752931</v>
+        <v>5.183934478000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2402418609586803</v>
+        <v>0.247102900512621</v>
       </c>
       <c r="T75">
-        <v>2.829365997150675</v>
+        <v>2.92920248258295</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.120670097964314</v>
+        <v>2.09201239393777</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1063157541332815</v>
+        <v>0.1062657058077192</v>
       </c>
       <c r="C76">
-        <v>8.676481259541031</v>
+        <v>8.249507177567978</v>
       </c>
       <c r="D76">
-        <v>-30.92139874045897</v>
+        <v>-30.94699282243202</v>
       </c>
       <c r="E76">
-        <v>29.46412</v>
+        <v>29.8655</v>
       </c>
       <c r="F76">
-        <v>29.70212</v>
+        <v>30.1035</v>
       </c>
       <c r="G76">
         <v>69.3</v>
@@ -7519,28 +7519,28 @@
         <v>4.71</v>
       </c>
       <c r="M76">
-        <v>2.251420696</v>
+        <v>2.2818453</v>
       </c>
       <c r="N76">
-        <v>2.458579304</v>
+        <v>2.4281547</v>
       </c>
       <c r="O76">
-        <v>0.614644826</v>
+        <v>0.607038675</v>
       </c>
       <c r="P76">
-        <v>1.843934478</v>
+        <v>1.821116025</v>
       </c>
       <c r="Q76">
-        <v>5.183934478000001</v>
+        <v>5.161116025</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.247102900512621</v>
+        <v>0.254512823230877</v>
       </c>
       <c r="T76">
-        <v>2.92920248258295</v>
+        <v>3.037025886849808</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.09201239393777</v>
+        <v>2.064118895351933</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1062657058077192</v>
+        <v>0.106215657482157</v>
       </c>
       <c r="C77">
-        <v>8.249507177567978</v>
+        <v>7.822490691324234</v>
       </c>
       <c r="D77">
-        <v>-30.94699282243202</v>
+        <v>-30.97262930867577</v>
       </c>
       <c r="E77">
-        <v>29.8655</v>
+        <v>30.26688</v>
       </c>
       <c r="F77">
-        <v>30.1035</v>
+        <v>30.50488</v>
       </c>
       <c r="G77">
         <v>69.3</v>
@@ -7601,28 +7601,28 @@
         <v>4.71</v>
       </c>
       <c r="M77">
-        <v>2.2818453</v>
+        <v>2.312269904</v>
       </c>
       <c r="N77">
-        <v>2.4281547</v>
+        <v>2.397730096</v>
       </c>
       <c r="O77">
-        <v>0.607038675</v>
+        <v>0.5994325239999999</v>
       </c>
       <c r="P77">
-        <v>1.821116025</v>
+        <v>1.798297572</v>
       </c>
       <c r="Q77">
-        <v>5.161116025</v>
+        <v>5.138297572000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.254512823230877</v>
+        <v>0.2625402395089876</v>
       </c>
       <c r="T77">
-        <v>3.037025886849808</v>
+        <v>3.15383457480557</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.064118895351933</v>
+        <v>2.036959436202565</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.106215657482157</v>
+        <v>0.1061656091565948</v>
       </c>
       <c r="C78">
-        <v>7.822490691324234</v>
+        <v>7.39543169533933</v>
       </c>
       <c r="D78">
-        <v>-30.97262930867577</v>
+        <v>-30.99830830466067</v>
       </c>
       <c r="E78">
-        <v>30.26688</v>
+        <v>30.66826</v>
       </c>
       <c r="F78">
-        <v>30.50488</v>
+        <v>30.90626</v>
       </c>
       <c r="G78">
         <v>69.3</v>
@@ -7683,28 +7683,28 @@
         <v>4.71</v>
       </c>
       <c r="M78">
-        <v>2.312269904</v>
+        <v>2.342694508</v>
       </c>
       <c r="N78">
-        <v>2.397730096</v>
+        <v>2.367305492</v>
       </c>
       <c r="O78">
-        <v>0.5994325239999999</v>
+        <v>0.591826373</v>
       </c>
       <c r="P78">
-        <v>1.798297572</v>
+        <v>1.775479119</v>
       </c>
       <c r="Q78">
-        <v>5.138297572000001</v>
+        <v>5.115479119000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2625402395089876</v>
+        <v>0.2712656919851949</v>
       </c>
       <c r="T78">
-        <v>3.15383457480557</v>
+        <v>3.280800539974876</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.036959436202565</v>
+        <v>2.010505417550584</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1061656091565948</v>
+        <v>0.1144225608310326</v>
       </c>
       <c r="C79">
-        <v>7.39543169533933</v>
+        <v>10.72389696140466</v>
       </c>
       <c r="D79">
-        <v>-30.99830830466067</v>
+        <v>-27.26846303859535</v>
       </c>
       <c r="E79">
-        <v>30.66826</v>
+        <v>31.06964</v>
       </c>
       <c r="F79">
-        <v>30.90626</v>
+        <v>31.30764</v>
       </c>
       <c r="G79">
         <v>69.3</v>
@@ -7765,45 +7765,45 @@
         <v>4.71</v>
       </c>
       <c r="M79">
-        <v>2.342694508</v>
+        <v>2.8176876</v>
       </c>
       <c r="N79">
-        <v>2.367305492</v>
+        <v>1.8923124</v>
       </c>
       <c r="O79">
-        <v>0.591826373</v>
+        <v>0.4730781000000001</v>
       </c>
       <c r="P79">
-        <v>1.775479119</v>
+        <v>1.4192343</v>
       </c>
       <c r="Q79">
-        <v>5.115479119000001</v>
+        <v>4.759234300000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2712656919851949</v>
+        <v>0.2807843674137846</v>
       </c>
       <c r="T79">
-        <v>3.280800539974876</v>
+        <v>3.41930886561412</v>
       </c>
       <c r="U79">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V79">
         <v>0.25</v>
       </c>
       <c r="W79">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.010505417550584</v>
+        <v>1.671583464398254</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1144225608310326</v>
+        <v>0.1144790125054704</v>
       </c>
       <c r="C80">
-        <v>10.72389696140466</v>
+        <v>10.34493065580294</v>
       </c>
       <c r="D80">
-        <v>-27.26846303859535</v>
+        <v>-27.24604934419705</v>
       </c>
       <c r="E80">
-        <v>31.06964</v>
+        <v>31.47102</v>
       </c>
       <c r="F80">
-        <v>31.30764</v>
+        <v>31.70902</v>
       </c>
       <c r="G80">
         <v>69.3</v>
@@ -7847,28 +7847,28 @@
         <v>4.71</v>
       </c>
       <c r="M80">
-        <v>2.8176876</v>
+        <v>2.8538118</v>
       </c>
       <c r="N80">
-        <v>1.8923124</v>
+        <v>1.8561882</v>
       </c>
       <c r="O80">
-        <v>0.4730781000000001</v>
+        <v>0.46404705</v>
       </c>
       <c r="P80">
-        <v>1.4192343</v>
+        <v>1.39214115</v>
       </c>
       <c r="Q80">
-        <v>4.759234300000001</v>
+        <v>4.73214115</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2807843674137846</v>
+        <v>0.2912095833593829</v>
       </c>
       <c r="T80">
-        <v>3.41930886561412</v>
+        <v>3.571008460361862</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.671583464398254</v>
+        <v>1.650424180038782</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1144790125054704</v>
+        <v>0.1145354641799082</v>
       </c>
       <c r="C81">
-        <v>10.34493065580294</v>
+        <v>9.965927533963963</v>
       </c>
       <c r="D81">
-        <v>-27.24604934419705</v>
+        <v>-27.22367246603604</v>
       </c>
       <c r="E81">
-        <v>31.47102</v>
+        <v>31.8724</v>
       </c>
       <c r="F81">
-        <v>31.70902</v>
+        <v>32.1104</v>
       </c>
       <c r="G81">
         <v>69.3</v>
@@ -7929,28 +7929,28 @@
         <v>4.71</v>
       </c>
       <c r="M81">
-        <v>2.8538118</v>
+        <v>2.889936</v>
       </c>
       <c r="N81">
-        <v>1.8561882</v>
+        <v>1.820064</v>
       </c>
       <c r="O81">
-        <v>0.46404705</v>
+        <v>0.4550160000000001</v>
       </c>
       <c r="P81">
-        <v>1.39214115</v>
+        <v>1.365048</v>
       </c>
       <c r="Q81">
-        <v>4.73214115</v>
+        <v>4.705048000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2912095833593829</v>
+        <v>0.302677320899541</v>
       </c>
       <c r="T81">
-        <v>3.571008460361862</v>
+        <v>3.73787801458438</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.650424180038782</v>
+        <v>1.629793877788297</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1145354641799082</v>
+        <v>0.114591915854346</v>
       </c>
       <c r="C82">
-        <v>9.965927533963963</v>
+        <v>9.586887686523553</v>
       </c>
       <c r="D82">
-        <v>-27.22367246603604</v>
+        <v>-27.20133231347644</v>
       </c>
       <c r="E82">
-        <v>31.8724</v>
+        <v>32.27378</v>
       </c>
       <c r="F82">
-        <v>32.1104</v>
+        <v>32.51178</v>
       </c>
       <c r="G82">
         <v>69.3</v>
@@ -8011,28 +8011,28 @@
         <v>4.71</v>
       </c>
       <c r="M82">
-        <v>2.889936</v>
+        <v>2.9260602</v>
       </c>
       <c r="N82">
-        <v>1.820064</v>
+        <v>1.7839398</v>
       </c>
       <c r="O82">
-        <v>0.4550160000000001</v>
+        <v>0.4459849499999999</v>
       </c>
       <c r="P82">
-        <v>1.365048</v>
+        <v>1.33795485</v>
       </c>
       <c r="Q82">
-        <v>4.705048000000001</v>
+        <v>4.677954850000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.302677320899541</v>
+        <v>0.3153521887070841</v>
       </c>
       <c r="T82">
-        <v>3.73787801458438</v>
+        <v>3.922312785040846</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.629793877788297</v>
+        <v>1.609672965716836</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.114591915854346</v>
+        <v>0.1146483675287838</v>
       </c>
       <c r="C83">
-        <v>9.586887686523553</v>
+        <v>9.207811203820363</v>
       </c>
       <c r="D83">
-        <v>-27.20133231347644</v>
+        <v>-27.17902879617964</v>
       </c>
       <c r="E83">
-        <v>32.27378</v>
+        <v>32.67516</v>
       </c>
       <c r="F83">
-        <v>32.51178</v>
+        <v>32.91316</v>
       </c>
       <c r="G83">
         <v>69.3</v>
@@ -8093,28 +8093,28 @@
         <v>4.71</v>
       </c>
       <c r="M83">
-        <v>2.9260602</v>
+        <v>2.962184399999999</v>
       </c>
       <c r="N83">
-        <v>1.7839398</v>
+        <v>1.7478156</v>
       </c>
       <c r="O83">
-        <v>0.4459849499999999</v>
+        <v>0.4369539000000001</v>
       </c>
       <c r="P83">
-        <v>1.33795485</v>
+        <v>1.3108617</v>
       </c>
       <c r="Q83">
-        <v>4.677954850000001</v>
+        <v>4.650861700000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3153521887070841</v>
+        <v>0.3294353751599098</v>
       </c>
       <c r="T83">
-        <v>3.922312785040846</v>
+        <v>4.127240307770252</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.609672965716836</v>
+        <v>1.590042807598339</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1146483675287838</v>
+        <v>0.1147048192032216</v>
       </c>
       <c r="C84">
-        <v>9.207811203820363</v>
+        <v>8.828698175896896</v>
       </c>
       <c r="D84">
-        <v>-27.17902879617964</v>
+        <v>-27.1567618241031</v>
       </c>
       <c r="E84">
-        <v>32.67516</v>
+        <v>33.07654</v>
       </c>
       <c r="F84">
-        <v>32.91316</v>
+        <v>33.31454</v>
       </c>
       <c r="G84">
         <v>69.3</v>
@@ -8175,28 +8175,28 @@
         <v>4.71</v>
       </c>
       <c r="M84">
-        <v>2.962184399999999</v>
+        <v>2.9983086</v>
       </c>
       <c r="N84">
-        <v>1.7478156</v>
+        <v>1.7116914</v>
       </c>
       <c r="O84">
-        <v>0.4369539000000001</v>
+        <v>0.42792285</v>
       </c>
       <c r="P84">
-        <v>1.3108617</v>
+        <v>1.28376855</v>
       </c>
       <c r="Q84">
-        <v>4.650861700000001</v>
+        <v>4.623768550000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3294353751599098</v>
+        <v>0.3451754070777739</v>
       </c>
       <c r="T84">
-        <v>4.127240307770252</v>
+        <v>4.356276950820767</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.590042807598339</v>
+        <v>1.570885665338118</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1147048192032216</v>
+        <v>0.1147612708776593</v>
       </c>
       <c r="C85">
-        <v>8.828698175896896</v>
+        <v>8.449548692500898</v>
       </c>
       <c r="D85">
-        <v>-27.1567618241031</v>
+        <v>-27.1345313074991</v>
       </c>
       <c r="E85">
-        <v>33.07654</v>
+        <v>33.47792</v>
       </c>
       <c r="F85">
-        <v>33.31454</v>
+        <v>33.71592</v>
       </c>
       <c r="G85">
         <v>69.3</v>
@@ -8257,28 +8257,28 @@
         <v>4.71</v>
       </c>
       <c r="M85">
-        <v>2.9983086</v>
+        <v>3.0344328</v>
       </c>
       <c r="N85">
-        <v>1.7116914</v>
+        <v>1.6755672</v>
       </c>
       <c r="O85">
-        <v>0.42792285</v>
+        <v>0.4188917999999999</v>
       </c>
       <c r="P85">
-        <v>1.28376855</v>
+        <v>1.2566754</v>
       </c>
       <c r="Q85">
-        <v>4.623768550000001</v>
+        <v>4.596675400000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3451754070777739</v>
+        <v>0.362882942985371</v>
       </c>
       <c r="T85">
-        <v>4.356276950820767</v>
+        <v>4.613943174252595</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.570885665338118</v>
+        <v>1.552184645512664</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1147612708776593</v>
+        <v>0.1148177225520971</v>
       </c>
       <c r="C86">
-        <v>8.449548692500898</v>
+        <v>8.070362843086443</v>
       </c>
       <c r="D86">
-        <v>-27.1345313074991</v>
+        <v>-27.11233715691355</v>
       </c>
       <c r="E86">
-        <v>33.47792</v>
+        <v>33.8793</v>
       </c>
       <c r="F86">
-        <v>33.71592</v>
+        <v>34.1173</v>
       </c>
       <c r="G86">
         <v>69.3</v>
@@ -8339,28 +8339,28 @@
         <v>4.71</v>
       </c>
       <c r="M86">
-        <v>3.0344328</v>
+        <v>3.070557</v>
       </c>
       <c r="N86">
-        <v>1.6755672</v>
+        <v>1.639443</v>
       </c>
       <c r="O86">
-        <v>0.4188918</v>
+        <v>0.40986075</v>
       </c>
       <c r="P86">
-        <v>1.2566754</v>
+        <v>1.22958225</v>
       </c>
       <c r="Q86">
-        <v>4.596675400000001</v>
+        <v>4.569582250000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3628829429853708</v>
+        <v>0.3829514836806475</v>
       </c>
       <c r="T86">
-        <v>4.613943174252592</v>
+        <v>4.905964894141997</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.552184645512664</v>
+        <v>1.533923649683103</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1148177225520971</v>
+        <v>0.1148741742265349</v>
       </c>
       <c r="C87">
-        <v>8.070362843086443</v>
+        <v>7.691140716815205</v>
       </c>
       <c r="D87">
-        <v>-27.11233715691355</v>
+        <v>-27.0901792831848</v>
       </c>
       <c r="E87">
-        <v>33.8793</v>
+        <v>34.28068</v>
       </c>
       <c r="F87">
-        <v>34.1173</v>
+        <v>34.51868</v>
       </c>
       <c r="G87">
         <v>69.3</v>
@@ -8421,28 +8421,28 @@
         <v>4.71</v>
       </c>
       <c r="M87">
-        <v>3.070557</v>
+        <v>3.1066812</v>
       </c>
       <c r="N87">
-        <v>1.639443</v>
+        <v>1.6033188</v>
       </c>
       <c r="O87">
-        <v>0.40986075</v>
+        <v>0.4008297000000001</v>
       </c>
       <c r="P87">
-        <v>1.22958225</v>
+        <v>1.2024891</v>
       </c>
       <c r="Q87">
-        <v>4.569582250000001</v>
+        <v>4.542489100000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3829514836806475</v>
+        <v>0.4058869587609636</v>
       </c>
       <c r="T87">
-        <v>4.905964894141997</v>
+        <v>5.239704002587031</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.533923649683103</v>
+        <v>1.51608732817516</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1148741742265349</v>
+        <v>0.1557195466763901</v>
       </c>
       <c r="C88">
-        <v>7.691140716815205</v>
+        <v>17.35629115668922</v>
       </c>
       <c r="D88">
-        <v>-27.0901792831848</v>
+        <v>-17.02364884331078</v>
       </c>
       <c r="E88">
-        <v>34.28068</v>
+        <v>34.68206</v>
       </c>
       <c r="F88">
-        <v>34.51868</v>
+        <v>34.92006</v>
       </c>
       <c r="G88">
         <v>69.3</v>
@@ -8503,45 +8503,45 @@
         <v>4.71</v>
       </c>
       <c r="M88">
-        <v>3.1066812</v>
+        <v>5.126264808</v>
       </c>
       <c r="N88">
-        <v>1.6033188</v>
+        <v>-0.4162648080000002</v>
       </c>
       <c r="O88">
-        <v>0.4008297000000001</v>
+        <v>-0.1040662020000001</v>
       </c>
       <c r="P88">
-        <v>1.2024891</v>
+        <v>-0.3121986060000002</v>
       </c>
       <c r="Q88">
-        <v>4.542489100000001</v>
+        <v>3.027801394000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4058869587609636</v>
+        <v>0.4410756652044571</v>
       </c>
       <c r="T88">
-        <v>5.239704002587031</v>
+        <v>5.751742557474626</v>
       </c>
       <c r="U88">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.25</v>
+        <v>0.2296994096290938</v>
       </c>
       <c r="W88">
-        <v>0.0675</v>
+        <v>0.113080126666449</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>1.51608732817516</v>
+        <v>0.9187976385163753</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1557195466763901</v>
+        <v>0.1567295466763901</v>
       </c>
       <c r="C89">
-        <v>17.35629115668922</v>
+        <v>17.10990940419764</v>
       </c>
       <c r="D89">
-        <v>-17.02364884331078</v>
+        <v>-16.86865059580236</v>
       </c>
       <c r="E89">
-        <v>34.68206</v>
+        <v>35.08344</v>
       </c>
       <c r="F89">
-        <v>34.92006</v>
+        <v>35.32144</v>
       </c>
       <c r="G89">
         <v>69.3</v>
@@ -8585,37 +8585,37 @@
         <v>4.71</v>
       </c>
       <c r="M89">
-        <v>5.126264808</v>
+        <v>5.185187392</v>
       </c>
       <c r="N89">
-        <v>-0.4162648080000002</v>
+        <v>-0.4751873919999996</v>
       </c>
       <c r="O89">
-        <v>-0.1040662020000001</v>
+        <v>-0.1187968479999999</v>
       </c>
       <c r="P89">
-        <v>-0.3121986060000002</v>
+        <v>-0.3563905439999997</v>
       </c>
       <c r="Q89">
-        <v>3.027801394000001</v>
+        <v>2.983609456000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4410756652044571</v>
+        <v>0.4740153039714953</v>
       </c>
       <c r="T89">
-        <v>5.751742557474626</v>
+        <v>6.231054437264179</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2296994096290938</v>
+        <v>0.2270891890651269</v>
       </c>
       <c r="W89">
-        <v>0.113080126666449</v>
+        <v>0.1134633070452394</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9187976385163753</v>
+        <v>0.9083567562605075</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1567295466763901</v>
+        <v>0.1577395466763901</v>
       </c>
       <c r="C90">
-        <v>17.10990940419764</v>
+        <v>16.86073063787794</v>
       </c>
       <c r="D90">
-        <v>-16.86865059580236</v>
+        <v>-16.71644936212206</v>
       </c>
       <c r="E90">
-        <v>35.08344</v>
+        <v>35.48482</v>
       </c>
       <c r="F90">
-        <v>35.32144</v>
+        <v>35.72282</v>
       </c>
       <c r="G90">
         <v>69.3</v>
@@ -8667,37 +8667,37 @@
         <v>4.71</v>
       </c>
       <c r="M90">
-        <v>5.185187392</v>
+        <v>5.244109976000001</v>
       </c>
       <c r="N90">
-        <v>-0.4751873919999996</v>
+        <v>-0.5341099760000008</v>
       </c>
       <c r="O90">
-        <v>-0.1187968479999999</v>
+        <v>-0.1335274940000002</v>
       </c>
       <c r="P90">
-        <v>-0.3563905439999997</v>
+        <v>-0.4005824820000006</v>
       </c>
       <c r="Q90">
-        <v>2.983609456000001</v>
+        <v>2.939417518</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4740153039714953</v>
+        <v>0.512943967968904</v>
       </c>
       <c r="T90">
-        <v>6.231054437264179</v>
+        <v>6.797513931560923</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2270891890651269</v>
+        <v>0.2245376251430467</v>
       </c>
       <c r="W90">
-        <v>0.1134633070452394</v>
+        <v>0.1138378766290007</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9083567562605075</v>
+        <v>0.8981505005721869</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1577395466763901</v>
+        <v>0.1587495466763901</v>
       </c>
       <c r="C91">
-        <v>16.86073063787794</v>
+        <v>16.60882989080594</v>
       </c>
       <c r="D91">
-        <v>-16.71644936212206</v>
+        <v>-16.56697010919405</v>
       </c>
       <c r="E91">
-        <v>35.48482</v>
+        <v>35.8862</v>
       </c>
       <c r="F91">
-        <v>35.72282</v>
+        <v>36.1242</v>
       </c>
       <c r="G91">
         <v>69.3</v>
@@ -8749,37 +8749,37 @@
         <v>4.71</v>
       </c>
       <c r="M91">
-        <v>5.244109976000001</v>
+        <v>5.303032560000001</v>
       </c>
       <c r="N91">
-        <v>-0.5341099760000008</v>
+        <v>-0.593032560000001</v>
       </c>
       <c r="O91">
-        <v>-0.1335274940000002</v>
+        <v>-0.1482581400000003</v>
       </c>
       <c r="P91">
-        <v>-0.4005824820000006</v>
+        <v>-0.4447744200000008</v>
       </c>
       <c r="Q91">
-        <v>2.939417518</v>
+        <v>2.89522558</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.512943967968904</v>
+        <v>0.5596583647657943</v>
       </c>
       <c r="T91">
-        <v>6.797513931560923</v>
+        <v>7.477265324717016</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2245376251430467</v>
+        <v>0.2220427626414573</v>
       </c>
       <c r="W91">
-        <v>0.1138378766290007</v>
+        <v>0.1142041224442341</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8981505005721869</v>
+        <v>0.8881710505658292</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1587495466763901</v>
+        <v>0.1597595466763901</v>
       </c>
       <c r="C92">
-        <v>16.60882989080594</v>
+        <v>16.35427953604665</v>
       </c>
       <c r="D92">
-        <v>-16.56697010919405</v>
+        <v>-16.42014046395335</v>
       </c>
       <c r="E92">
-        <v>35.8862</v>
+        <v>36.28758</v>
       </c>
       <c r="F92">
-        <v>36.1242</v>
+        <v>36.52558</v>
       </c>
       <c r="G92">
         <v>69.3</v>
@@ -8831,37 +8831,37 @@
         <v>4.71</v>
       </c>
       <c r="M92">
-        <v>5.303032560000001</v>
+        <v>5.361955144</v>
       </c>
       <c r="N92">
-        <v>-0.593032560000001</v>
+        <v>-0.6519551440000004</v>
       </c>
       <c r="O92">
-        <v>-0.1482581400000003</v>
+        <v>-0.1629887860000001</v>
       </c>
       <c r="P92">
-        <v>-0.4447744200000008</v>
+        <v>-0.4889663580000003</v>
       </c>
       <c r="Q92">
-        <v>2.89522558</v>
+        <v>2.851033642</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5596583647657943</v>
+        <v>0.6167537386286605</v>
       </c>
       <c r="T92">
-        <v>7.477265324717016</v>
+        <v>8.308072583018907</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2220427626414573</v>
+        <v>0.21960273228276</v>
       </c>
       <c r="W92">
-        <v>0.1142041224442341</v>
+        <v>0.1145623189008908</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8881710505658292</v>
+        <v>0.87841092913104</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1597595466763901</v>
+        <v>0.1607695466763901</v>
       </c>
       <c r="C93">
-        <v>16.35427953604665</v>
+        <v>16.09714940349436</v>
       </c>
       <c r="D93">
-        <v>-16.42014046395335</v>
+        <v>-16.27589059650564</v>
       </c>
       <c r="E93">
-        <v>36.28758</v>
+        <v>36.68896</v>
       </c>
       <c r="F93">
-        <v>36.52558</v>
+        <v>36.92696</v>
       </c>
       <c r="G93">
         <v>69.3</v>
@@ -8913,37 +8913,37 @@
         <v>4.71</v>
       </c>
       <c r="M93">
-        <v>5.361955144</v>
+        <v>5.420877728000001</v>
       </c>
       <c r="N93">
-        <v>-0.6519551440000004</v>
+        <v>-0.7108777280000007</v>
       </c>
       <c r="O93">
-        <v>-0.1629887860000001</v>
+        <v>-0.1777194320000002</v>
       </c>
       <c r="P93">
-        <v>-0.4889663580000003</v>
+        <v>-0.5331582960000005</v>
       </c>
       <c r="Q93">
-        <v>2.851033642</v>
+        <v>2.806841704</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6167537386286605</v>
+        <v>0.6881229559572433</v>
       </c>
       <c r="T93">
-        <v>8.308072583018907</v>
+        <v>9.346581655896275</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.21960273228276</v>
+        <v>0.2172157460622952</v>
       </c>
       <c r="W93">
-        <v>0.1145623189008908</v>
+        <v>0.1149127284780551</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.87841092913104</v>
+        <v>0.8688629842491808</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1607695466763901</v>
+        <v>0.1617795466763901</v>
       </c>
       <c r="C94">
-        <v>16.09714940349436</v>
+        <v>15.83750689060783</v>
       </c>
       <c r="D94">
-        <v>-16.27589059650564</v>
+        <v>-16.13415310939217</v>
       </c>
       <c r="E94">
-        <v>36.68896</v>
+        <v>37.09034</v>
       </c>
       <c r="F94">
-        <v>36.92696</v>
+        <v>37.32834</v>
       </c>
       <c r="G94">
         <v>69.3</v>
@@ -8995,37 +8995,37 @@
         <v>4.71</v>
       </c>
       <c r="M94">
-        <v>5.420877728000001</v>
+        <v>5.479800312</v>
       </c>
       <c r="N94">
-        <v>-0.7108777280000007</v>
+        <v>-0.7698003120000001</v>
       </c>
       <c r="O94">
-        <v>-0.1777194320000002</v>
+        <v>-0.192450078</v>
       </c>
       <c r="P94">
-        <v>-0.5331582960000005</v>
+        <v>-0.5773502340000001</v>
       </c>
       <c r="Q94">
-        <v>2.806841704</v>
+        <v>2.762649766000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6881229559572433</v>
+        <v>0.7798833782368495</v>
       </c>
       <c r="T94">
-        <v>9.346581655896275</v>
+        <v>10.6818076067386</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2172157460622952</v>
+        <v>0.2148800928788297</v>
       </c>
       <c r="W94">
-        <v>0.1149127284780551</v>
+        <v>0.1152556023653878</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8688629842491808</v>
+        <v>0.8595203715153188</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1617795466763901</v>
+        <v>0.1627895466763901</v>
       </c>
       <c r="C95">
-        <v>15.83750689060783</v>
+        <v>15.57541706740936</v>
       </c>
       <c r="D95">
-        <v>-16.13415310939217</v>
+        <v>-15.99486293259063</v>
       </c>
       <c r="E95">
-        <v>37.09034</v>
+        <v>37.49172</v>
       </c>
       <c r="F95">
-        <v>37.32834</v>
+        <v>37.72972</v>
       </c>
       <c r="G95">
         <v>69.3</v>
@@ -9077,37 +9077,37 @@
         <v>4.71</v>
       </c>
       <c r="M95">
-        <v>5.479800312</v>
+        <v>5.538722896</v>
       </c>
       <c r="N95">
-        <v>-0.7698003120000001</v>
+        <v>-0.8287228960000004</v>
       </c>
       <c r="O95">
-        <v>-0.192450078</v>
+        <v>-0.2071807240000001</v>
       </c>
       <c r="P95">
-        <v>-0.5773502340000001</v>
+        <v>-0.6215421720000003</v>
       </c>
       <c r="Q95">
-        <v>2.762649766000001</v>
+        <v>2.718457828</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7798833782368495</v>
+        <v>0.9022306079429911</v>
       </c>
       <c r="T95">
-        <v>10.6818076067386</v>
+        <v>12.46210887452837</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2148800928788297</v>
+        <v>0.2125941344439485</v>
       </c>
       <c r="W95">
-        <v>0.1152556023653878</v>
+        <v>0.1155911810636284</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8595203715153188</v>
+        <v>0.8503765377757941</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1627895466763901</v>
+        <v>0.1637995466763901</v>
       </c>
       <c r="C96">
-        <v>15.57541706740936</v>
+        <v>15.31094277609163</v>
       </c>
       <c r="D96">
-        <v>-15.99486293259063</v>
+        <v>-15.85795722390836</v>
       </c>
       <c r="E96">
-        <v>37.49172</v>
+        <v>37.8931</v>
       </c>
       <c r="F96">
-        <v>37.72972</v>
+        <v>38.1311</v>
       </c>
       <c r="G96">
         <v>69.3</v>
@@ -9159,37 +9159,37 @@
         <v>4.71</v>
       </c>
       <c r="M96">
-        <v>5.538722896</v>
+        <v>5.597645480000001</v>
       </c>
       <c r="N96">
-        <v>-0.8287228960000004</v>
+        <v>-0.8876454800000007</v>
       </c>
       <c r="O96">
-        <v>-0.2071807240000001</v>
+        <v>-0.2219113700000002</v>
       </c>
       <c r="P96">
-        <v>-0.6215421720000003</v>
+        <v>-0.6657341100000005</v>
       </c>
       <c r="Q96">
-        <v>2.718457828</v>
+        <v>2.67426589</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9022306079429911</v>
+        <v>1.07351672953159</v>
       </c>
       <c r="T96">
-        <v>12.46210887452837</v>
+        <v>14.95453064943405</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2125941344439485</v>
+        <v>0.2103563014498017</v>
       </c>
       <c r="W96">
-        <v>0.1155911810636284</v>
+        <v>0.1159196949471691</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8503765377757941</v>
+        <v>0.8414252057992068</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1637995466763901</v>
+        <v>0.1648095466763901</v>
       </c>
       <c r="C97">
-        <v>15.31094277609163</v>
+        <v>15.04414472555236</v>
       </c>
       <c r="D97">
-        <v>-15.85795722390836</v>
+        <v>-15.72337527444763</v>
       </c>
       <c r="E97">
-        <v>37.8931</v>
+        <v>38.29448</v>
       </c>
       <c r="F97">
-        <v>38.1311</v>
+        <v>38.53248</v>
       </c>
       <c r="G97">
         <v>69.3</v>
@@ -9241,37 +9241,37 @@
         <v>4.71</v>
       </c>
       <c r="M97">
-        <v>5.597645480000001</v>
+        <v>5.656568064000001</v>
       </c>
       <c r="N97">
-        <v>-0.8876454800000007</v>
+        <v>-0.9465680640000009</v>
       </c>
       <c r="O97">
-        <v>-0.2219113700000002</v>
+        <v>-0.2366420160000002</v>
       </c>
       <c r="P97">
-        <v>-0.6657341100000005</v>
+        <v>-0.7099260480000007</v>
       </c>
       <c r="Q97">
-        <v>2.67426589</v>
+        <v>2.630073952</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.07351672953159</v>
+        <v>1.330445911914488</v>
       </c>
       <c r="T97">
-        <v>14.95453064943405</v>
+        <v>18.69316331179257</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2103563014498017</v>
+        <v>0.2081650899763662</v>
       </c>
       <c r="W97">
-        <v>0.1159196949471691</v>
+        <v>0.1162413647914694</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8414252057992068</v>
+        <v>0.8326603599054649</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1648095466763901</v>
+        <v>0.1658195466763901</v>
       </c>
       <c r="C98">
-        <v>15.04414472555236</v>
+        <v>14.77508158115599</v>
       </c>
       <c r="D98">
-        <v>-15.72337527444763</v>
+        <v>-15.59105841884401</v>
       </c>
       <c r="E98">
-        <v>38.29448</v>
+        <v>38.69586</v>
       </c>
       <c r="F98">
-        <v>38.53248</v>
+        <v>38.93386</v>
       </c>
       <c r="G98">
         <v>69.3</v>
@@ -9323,37 +9323,37 @@
         <v>4.71</v>
       </c>
       <c r="M98">
-        <v>5.656568064000001</v>
+        <v>5.715490648</v>
       </c>
       <c r="N98">
-        <v>-0.9465680640000009</v>
+        <v>-1.005490648</v>
       </c>
       <c r="O98">
-        <v>-0.2366420160000002</v>
+        <v>-0.2513726620000001</v>
       </c>
       <c r="P98">
-        <v>-0.7099260480000007</v>
+        <v>-0.7541179860000002</v>
       </c>
       <c r="Q98">
-        <v>2.630073952</v>
+        <v>2.585882014000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.330445911914485</v>
+        <v>1.75866121588598</v>
       </c>
       <c r="T98">
-        <v>18.69316331179252</v>
+        <v>24.9242177490567</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2081650899763662</v>
+        <v>0.2060190581209398</v>
       </c>
       <c r="W98">
-        <v>0.1162413647914694</v>
+        <v>0.1165564022678461</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8326603599054649</v>
+        <v>0.8240762324837593</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1658195466763901</v>
+        <v>0.1668295466763901</v>
       </c>
       <c r="C99">
-        <v>14.77508158115599</v>
+        <v>14.50381005000069</v>
       </c>
       <c r="D99">
-        <v>-15.59105841884401</v>
+        <v>-15.46094994999931</v>
       </c>
       <c r="E99">
-        <v>38.69586</v>
+        <v>39.09724</v>
       </c>
       <c r="F99">
-        <v>38.93386</v>
+        <v>39.33524</v>
       </c>
       <c r="G99">
         <v>69.3</v>
@@ -9405,37 +9405,37 @@
         <v>4.71</v>
       </c>
       <c r="M99">
-        <v>5.715490648</v>
+        <v>5.774413232000001</v>
       </c>
       <c r="N99">
-        <v>-1.005490648</v>
+        <v>-1.064413232000001</v>
       </c>
       <c r="O99">
-        <v>-0.2513726620000001</v>
+        <v>-0.2661033080000001</v>
       </c>
       <c r="P99">
-        <v>-0.7541179860000002</v>
+        <v>-0.7983099240000004</v>
       </c>
       <c r="Q99">
-        <v>2.585882014000001</v>
+        <v>2.541690076</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.75866121588598</v>
+        <v>2.615091823828969</v>
       </c>
       <c r="T99">
-        <v>24.9242177490567</v>
+        <v>37.38632662358504</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2060190581209398</v>
+        <v>0.2039168228339914</v>
       </c>
       <c r="W99">
-        <v>0.1165564022678461</v>
+        <v>0.1168650104079701</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8240762324837593</v>
+        <v>0.8156672913359657</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1668295466763901</v>
+        <v>0.1678395466763901</v>
       </c>
       <c r="C100">
-        <v>14.50381005000069</v>
+        <v>14.23038496195154</v>
       </c>
       <c r="D100">
-        <v>-15.46094994999931</v>
+        <v>-15.33299503804847</v>
       </c>
       <c r="E100">
-        <v>39.09724</v>
+        <v>39.49862</v>
       </c>
       <c r="F100">
-        <v>39.33524</v>
+        <v>39.73661999999999</v>
       </c>
       <c r="G100">
         <v>69.3</v>
@@ -9487,37 +9487,37 @@
         <v>4.71</v>
       </c>
       <c r="M100">
-        <v>5.774413232000001</v>
+        <v>5.833335816</v>
       </c>
       <c r="N100">
-        <v>-1.064413232000001</v>
+        <v>-1.123335816</v>
       </c>
       <c r="O100">
-        <v>-0.2661033080000001</v>
+        <v>-0.280833954</v>
       </c>
       <c r="P100">
-        <v>-0.7983099240000004</v>
+        <v>-0.842501862</v>
       </c>
       <c r="Q100">
-        <v>2.541690076</v>
+        <v>2.497498138000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.615091823828969</v>
+        <v>5.184383647657937</v>
       </c>
       <c r="T100">
-        <v>37.38632662358504</v>
+        <v>74.77265324717007</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2039168228339914</v>
+        <v>0.2018570569467794</v>
       </c>
       <c r="W100">
-        <v>0.1168650104079701</v>
+        <v>0.1171673840402128</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8156672913359657</v>
+        <v>0.8074282277871176</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1678395466763901</v>
-      </c>
-      <c r="C101">
-        <v>14.23038496195154</v>
-      </c>
-      <c r="D101">
-        <v>-15.33299503804847</v>
-      </c>
-      <c r="E101">
-        <v>39.49862</v>
-      </c>
-      <c r="F101">
-        <v>39.73661999999999</v>
-      </c>
-      <c r="G101">
-        <v>69.3</v>
-      </c>
-      <c r="H101">
-        <v>39.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="K101">
-        <v>3.340000000000001</v>
-      </c>
-      <c r="L101">
-        <v>4.71</v>
-      </c>
-      <c r="M101">
-        <v>5.833335816</v>
-      </c>
-      <c r="N101">
-        <v>-1.123335816</v>
-      </c>
-      <c r="O101">
-        <v>-0.280833954</v>
-      </c>
-      <c r="P101">
-        <v>-0.842501862</v>
-      </c>
-      <c r="Q101">
-        <v>2.497498138000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.184383647657937</v>
-      </c>
-      <c r="T101">
-        <v>74.77265324717007</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2018570569467794</v>
-      </c>
-      <c r="W101">
-        <v>0.1171673840402128</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8074282277871176</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
